--- a/ssp_modeling/transformations/templates/calibrated/uganda/model_input_variables_uganda_ip_calibrated.xlsx
+++ b/ssp_modeling/transformations/templates/calibrated/uganda/model_input_variables_uganda_ip_calibrated.xlsx
@@ -1115,112 +1115,112 @@
         <v>1</v>
       </c>
       <c r="J2">
-        <v>3</v>
+        <v>2.557745092854062</v>
       </c>
       <c r="K2">
-        <v>3</v>
+        <v>2.557745092854062</v>
       </c>
       <c r="L2">
-        <v>3</v>
+        <v>2.557745092854062</v>
       </c>
       <c r="M2">
-        <v>3</v>
+        <v>2.557745092854062</v>
       </c>
       <c r="N2">
-        <v>3</v>
+        <v>2.557745092854062</v>
       </c>
       <c r="O2">
-        <v>3</v>
+        <v>2.557745092854062</v>
       </c>
       <c r="P2">
-        <v>3</v>
+        <v>2.557745092854062</v>
       </c>
       <c r="Q2">
-        <v>3</v>
+        <v>2.557745092854062</v>
       </c>
       <c r="R2">
-        <v>3</v>
+        <v>2.557745092854062</v>
       </c>
       <c r="S2">
-        <v>3</v>
+        <v>2.557745092854062</v>
       </c>
       <c r="T2">
-        <v>3</v>
+        <v>2.557745092854062</v>
       </c>
       <c r="U2">
-        <v>3</v>
+        <v>2.557745092854062</v>
       </c>
       <c r="V2">
-        <v>3</v>
+        <v>2.557745092854062</v>
       </c>
       <c r="W2">
-        <v>3</v>
+        <v>2.557745092854062</v>
       </c>
       <c r="X2">
-        <v>3</v>
+        <v>2.557745092854062</v>
       </c>
       <c r="Y2">
-        <v>3</v>
+        <v>2.557745092854062</v>
       </c>
       <c r="Z2">
-        <v>3</v>
+        <v>2.557745092854062</v>
       </c>
       <c r="AA2">
-        <v>3</v>
+        <v>2.557745092854062</v>
       </c>
       <c r="AB2">
-        <v>3</v>
+        <v>2.557745092854062</v>
       </c>
       <c r="AC2">
-        <v>3</v>
+        <v>2.557745092854062</v>
       </c>
       <c r="AD2">
-        <v>3</v>
+        <v>2.557745092854062</v>
       </c>
       <c r="AE2">
-        <v>3</v>
+        <v>2.557745092854062</v>
       </c>
       <c r="AF2">
-        <v>3</v>
+        <v>2.557745092854062</v>
       </c>
       <c r="AG2">
-        <v>3</v>
+        <v>2.557745092854062</v>
       </c>
       <c r="AH2">
-        <v>3</v>
+        <v>2.557745092854062</v>
       </c>
       <c r="AI2">
-        <v>3</v>
+        <v>2.557745092854062</v>
       </c>
       <c r="AJ2">
-        <v>3</v>
+        <v>2.557745092854062</v>
       </c>
       <c r="AK2">
-        <v>3</v>
+        <v>2.557745092854062</v>
       </c>
       <c r="AL2">
-        <v>3</v>
+        <v>2.557745092854062</v>
       </c>
       <c r="AM2">
-        <v>3</v>
+        <v>2.557745092854062</v>
       </c>
       <c r="AN2">
-        <v>3</v>
+        <v>2.557745092854062</v>
       </c>
       <c r="AO2">
-        <v>3</v>
+        <v>2.557745092854062</v>
       </c>
       <c r="AP2">
-        <v>3</v>
+        <v>2.557745092854062</v>
       </c>
       <c r="AQ2">
-        <v>3</v>
+        <v>2.557745092854062</v>
       </c>
       <c r="AR2">
-        <v>3</v>
+        <v>2.557745092854062</v>
       </c>
       <c r="AS2">
-        <v>3</v>
+        <v>2.557745092854062</v>
       </c>
     </row>
     <row r="3" spans="1:45">
@@ -1237,112 +1237,112 @@
         <v>1</v>
       </c>
       <c r="J3">
-        <v>0.4</v>
+        <v>0.4214071206531637</v>
       </c>
       <c r="K3">
-        <v>0.4</v>
+        <v>0.4214071206531637</v>
       </c>
       <c r="L3">
-        <v>0.4</v>
+        <v>0.4214071206531637</v>
       </c>
       <c r="M3">
-        <v>0.4</v>
+        <v>0.4214071206531637</v>
       </c>
       <c r="N3">
-        <v>0.4</v>
+        <v>0.4214071206531637</v>
       </c>
       <c r="O3">
-        <v>0.4</v>
+        <v>0.4214071206531637</v>
       </c>
       <c r="P3">
-        <v>0.4</v>
+        <v>0.4214071206531637</v>
       </c>
       <c r="Q3">
-        <v>0.4</v>
+        <v>0.4214071206531637</v>
       </c>
       <c r="R3">
-        <v>0.4</v>
+        <v>0.4214071206531637</v>
       </c>
       <c r="S3">
-        <v>0.4</v>
+        <v>0.4214071206531637</v>
       </c>
       <c r="T3">
-        <v>0.4</v>
+        <v>0.4214071206531637</v>
       </c>
       <c r="U3">
-        <v>0.4</v>
+        <v>0.4214071206531637</v>
       </c>
       <c r="V3">
-        <v>0.4</v>
+        <v>0.4214071206531637</v>
       </c>
       <c r="W3">
-        <v>0.4</v>
+        <v>0.4214071206531637</v>
       </c>
       <c r="X3">
-        <v>0.4</v>
+        <v>0.4214071206531637</v>
       </c>
       <c r="Y3">
-        <v>0.4</v>
+        <v>0.4214071206531637</v>
       </c>
       <c r="Z3">
-        <v>0.4</v>
+        <v>0.4214071206531637</v>
       </c>
       <c r="AA3">
-        <v>0.4</v>
+        <v>0.4214071206531637</v>
       </c>
       <c r="AB3">
-        <v>0.4</v>
+        <v>0.4214071206531637</v>
       </c>
       <c r="AC3">
-        <v>0.4</v>
+        <v>0.4214071206531637</v>
       </c>
       <c r="AD3">
-        <v>0.4</v>
+        <v>0.4214071206531637</v>
       </c>
       <c r="AE3">
-        <v>0.4</v>
+        <v>0.4214071206531637</v>
       </c>
       <c r="AF3">
-        <v>0.4</v>
+        <v>0.4214071206531637</v>
       </c>
       <c r="AG3">
-        <v>0.4</v>
+        <v>0.4214071206531637</v>
       </c>
       <c r="AH3">
-        <v>0.4</v>
+        <v>0.4214071206531637</v>
       </c>
       <c r="AI3">
-        <v>0.4</v>
+        <v>0.4214071206531637</v>
       </c>
       <c r="AJ3">
-        <v>0.4</v>
+        <v>0.4214071206531637</v>
       </c>
       <c r="AK3">
-        <v>0.4</v>
+        <v>0.4214071206531637</v>
       </c>
       <c r="AL3">
-        <v>0.4</v>
+        <v>0.4214071206531637</v>
       </c>
       <c r="AM3">
-        <v>0.4</v>
+        <v>0.4214071206531637</v>
       </c>
       <c r="AN3">
-        <v>0.4</v>
+        <v>0.4214071206531637</v>
       </c>
       <c r="AO3">
-        <v>0.4</v>
+        <v>0.4214071206531637</v>
       </c>
       <c r="AP3">
-        <v>0.4</v>
+        <v>0.4214071206531637</v>
       </c>
       <c r="AQ3">
-        <v>0.4</v>
+        <v>0.4214071206531637</v>
       </c>
       <c r="AR3">
-        <v>0.4</v>
+        <v>0.4214071206531637</v>
       </c>
       <c r="AS3">
-        <v>0.4</v>
+        <v>0.4214071206531637</v>
       </c>
     </row>
     <row r="4" spans="1:45">
@@ -6332,112 +6332,112 @@
         <v>1</v>
       </c>
       <c r="J44">
-        <v>2E-06</v>
+        <v>2.190818243968932E-06</v>
       </c>
       <c r="K44">
-        <v>2E-06</v>
+        <v>2.190818243968932E-06</v>
       </c>
       <c r="L44">
-        <v>2E-06</v>
+        <v>2.190818243968932E-06</v>
       </c>
       <c r="M44">
-        <v>2E-06</v>
+        <v>2.190818243968932E-06</v>
       </c>
       <c r="N44">
-        <v>2E-06</v>
+        <v>2.190818243968932E-06</v>
       </c>
       <c r="O44">
-        <v>2E-06</v>
+        <v>2.190818243968932E-06</v>
       </c>
       <c r="P44">
-        <v>2E-06</v>
+        <v>2.190818243968932E-06</v>
       </c>
       <c r="Q44">
-        <v>2E-06</v>
+        <v>2.190818243968932E-06</v>
       </c>
       <c r="R44">
-        <v>2E-06</v>
+        <v>2.190818243968932E-06</v>
       </c>
       <c r="S44">
-        <v>2E-06</v>
+        <v>2.190818243968932E-06</v>
       </c>
       <c r="T44">
-        <v>2E-06</v>
+        <v>2.190818243968932E-06</v>
       </c>
       <c r="U44">
-        <v>2E-06</v>
+        <v>2.190818243968932E-06</v>
       </c>
       <c r="V44">
-        <v>2E-06</v>
+        <v>2.190818243968932E-06</v>
       </c>
       <c r="W44">
-        <v>2E-06</v>
+        <v>2.190818243968932E-06</v>
       </c>
       <c r="X44">
-        <v>2E-06</v>
+        <v>2.190818243968932E-06</v>
       </c>
       <c r="Y44">
-        <v>2E-06</v>
+        <v>2.190818243968932E-06</v>
       </c>
       <c r="Z44">
-        <v>2E-06</v>
+        <v>2.190818243968932E-06</v>
       </c>
       <c r="AA44">
-        <v>2E-06</v>
+        <v>2.190818243968932E-06</v>
       </c>
       <c r="AB44">
-        <v>2E-06</v>
+        <v>2.190818243968932E-06</v>
       </c>
       <c r="AC44">
-        <v>2E-06</v>
+        <v>2.190818243968932E-06</v>
       </c>
       <c r="AD44">
-        <v>2E-06</v>
+        <v>2.190818243968932E-06</v>
       </c>
       <c r="AE44">
-        <v>2E-06</v>
+        <v>2.190818243968932E-06</v>
       </c>
       <c r="AF44">
-        <v>2E-06</v>
+        <v>2.190818243968932E-06</v>
       </c>
       <c r="AG44">
-        <v>2E-06</v>
+        <v>2.190818243968932E-06</v>
       </c>
       <c r="AH44">
-        <v>2E-06</v>
+        <v>2.190818243968932E-06</v>
       </c>
       <c r="AI44">
-        <v>2E-06</v>
+        <v>2.190818243968932E-06</v>
       </c>
       <c r="AJ44">
-        <v>2E-06</v>
+        <v>2.190818243968932E-06</v>
       </c>
       <c r="AK44">
-        <v>2E-06</v>
+        <v>2.190818243968932E-06</v>
       </c>
       <c r="AL44">
-        <v>2E-06</v>
+        <v>2.190818243968932E-06</v>
       </c>
       <c r="AM44">
-        <v>2E-06</v>
+        <v>2.190818243968932E-06</v>
       </c>
       <c r="AN44">
-        <v>2E-06</v>
+        <v>2.190818243968932E-06</v>
       </c>
       <c r="AO44">
-        <v>2E-06</v>
+        <v>2.190818243968932E-06</v>
       </c>
       <c r="AP44">
-        <v>2E-06</v>
+        <v>2.190818243968932E-06</v>
       </c>
       <c r="AQ44">
-        <v>2E-06</v>
+        <v>2.190818243968932E-06</v>
       </c>
       <c r="AR44">
-        <v>2E-06</v>
+        <v>2.190818243968932E-06</v>
       </c>
       <c r="AS44">
-        <v>2E-06</v>
+        <v>2.190818243968932E-06</v>
       </c>
     </row>
     <row r="45" spans="1:45">
@@ -6457,112 +6457,112 @@
         <v>1</v>
       </c>
       <c r="J45">
-        <v>4E-08</v>
+        <v>3.623394131474849E-08</v>
       </c>
       <c r="K45">
-        <v>4E-08</v>
+        <v>3.623394131474849E-08</v>
       </c>
       <c r="L45">
-        <v>4E-08</v>
+        <v>3.623394131474849E-08</v>
       </c>
       <c r="M45">
-        <v>4E-08</v>
+        <v>3.623394131474849E-08</v>
       </c>
       <c r="N45">
-        <v>4E-08</v>
+        <v>3.623394131474849E-08</v>
       </c>
       <c r="O45">
-        <v>4E-08</v>
+        <v>3.623394131474849E-08</v>
       </c>
       <c r="P45">
-        <v>4E-08</v>
+        <v>3.623394131474849E-08</v>
       </c>
       <c r="Q45">
-        <v>4E-08</v>
+        <v>3.623394131474849E-08</v>
       </c>
       <c r="R45">
-        <v>4E-08</v>
+        <v>3.623394131474849E-08</v>
       </c>
       <c r="S45">
-        <v>4E-08</v>
+        <v>3.623394131474849E-08</v>
       </c>
       <c r="T45">
-        <v>4E-08</v>
+        <v>3.623394131474849E-08</v>
       </c>
       <c r="U45">
-        <v>4E-08</v>
+        <v>3.623394131474849E-08</v>
       </c>
       <c r="V45">
-        <v>4E-08</v>
+        <v>3.623394131474849E-08</v>
       </c>
       <c r="W45">
-        <v>4E-08</v>
+        <v>3.623394131474849E-08</v>
       </c>
       <c r="X45">
-        <v>4E-08</v>
+        <v>3.623394131474849E-08</v>
       </c>
       <c r="Y45">
-        <v>4E-08</v>
+        <v>3.623394131474849E-08</v>
       </c>
       <c r="Z45">
-        <v>4E-08</v>
+        <v>3.623394131474849E-08</v>
       </c>
       <c r="AA45">
-        <v>4E-08</v>
+        <v>3.623394131474849E-08</v>
       </c>
       <c r="AB45">
-        <v>4E-08</v>
+        <v>3.623394131474849E-08</v>
       </c>
       <c r="AC45">
-        <v>4E-08</v>
+        <v>3.623394131474849E-08</v>
       </c>
       <c r="AD45">
-        <v>4E-08</v>
+        <v>3.623394131474849E-08</v>
       </c>
       <c r="AE45">
-        <v>4E-08</v>
+        <v>3.623394131474849E-08</v>
       </c>
       <c r="AF45">
-        <v>4E-08</v>
+        <v>3.623394131474849E-08</v>
       </c>
       <c r="AG45">
-        <v>4E-08</v>
+        <v>3.623394131474849E-08</v>
       </c>
       <c r="AH45">
-        <v>4E-08</v>
+        <v>3.623394131474849E-08</v>
       </c>
       <c r="AI45">
-        <v>4E-08</v>
+        <v>3.623394131474849E-08</v>
       </c>
       <c r="AJ45">
-        <v>4E-08</v>
+        <v>3.623394131474849E-08</v>
       </c>
       <c r="AK45">
-        <v>4E-08</v>
+        <v>3.623394131474849E-08</v>
       </c>
       <c r="AL45">
-        <v>4E-08</v>
+        <v>3.623394131474849E-08</v>
       </c>
       <c r="AM45">
-        <v>4E-08</v>
+        <v>3.623394131474849E-08</v>
       </c>
       <c r="AN45">
-        <v>4E-08</v>
+        <v>3.623394131474849E-08</v>
       </c>
       <c r="AO45">
-        <v>4E-08</v>
+        <v>3.623394131474849E-08</v>
       </c>
       <c r="AP45">
-        <v>4E-08</v>
+        <v>3.623394131474849E-08</v>
       </c>
       <c r="AQ45">
-        <v>4E-08</v>
+        <v>3.623394131474849E-08</v>
       </c>
       <c r="AR45">
-        <v>4E-08</v>
+        <v>3.623394131474849E-08</v>
       </c>
       <c r="AS45">
-        <v>4E-08</v>
+        <v>3.623394131474849E-08</v>
       </c>
     </row>
     <row r="46" spans="1:45">
@@ -6951,112 +6951,112 @@
         <v>1</v>
       </c>
       <c r="J49">
-        <v>6E-07</v>
+        <v>6.572454731906799E-07</v>
       </c>
       <c r="K49">
-        <v>6E-07</v>
+        <v>6.572454731906799E-07</v>
       </c>
       <c r="L49">
-        <v>6E-07</v>
+        <v>6.572454731906799E-07</v>
       </c>
       <c r="M49">
-        <v>6E-07</v>
+        <v>6.572454731906799E-07</v>
       </c>
       <c r="N49">
-        <v>6E-07</v>
+        <v>6.572454731906799E-07</v>
       </c>
       <c r="O49">
-        <v>6E-07</v>
+        <v>6.572454731906799E-07</v>
       </c>
       <c r="P49">
-        <v>6E-07</v>
+        <v>6.572454731906799E-07</v>
       </c>
       <c r="Q49">
-        <v>6E-07</v>
+        <v>6.572454731906799E-07</v>
       </c>
       <c r="R49">
-        <v>6E-07</v>
+        <v>6.572454731906799E-07</v>
       </c>
       <c r="S49">
-        <v>6E-07</v>
+        <v>6.572454731906799E-07</v>
       </c>
       <c r="T49">
-        <v>6E-07</v>
+        <v>6.572454731906799E-07</v>
       </c>
       <c r="U49">
-        <v>6E-07</v>
+        <v>6.572454731906799E-07</v>
       </c>
       <c r="V49">
-        <v>6E-07</v>
+        <v>6.572454731906799E-07</v>
       </c>
       <c r="W49">
-        <v>6E-07</v>
+        <v>6.572454731906799E-07</v>
       </c>
       <c r="X49">
-        <v>6E-07</v>
+        <v>6.572454731906799E-07</v>
       </c>
       <c r="Y49">
-        <v>6E-07</v>
+        <v>6.572454731906799E-07</v>
       </c>
       <c r="Z49">
-        <v>6E-07</v>
+        <v>6.572454731906799E-07</v>
       </c>
       <c r="AA49">
-        <v>6E-07</v>
+        <v>6.572454731906799E-07</v>
       </c>
       <c r="AB49">
-        <v>6E-07</v>
+        <v>6.572454731906799E-07</v>
       </c>
       <c r="AC49">
-        <v>6E-07</v>
+        <v>6.572454731906799E-07</v>
       </c>
       <c r="AD49">
-        <v>6E-07</v>
+        <v>6.572454731906799E-07</v>
       </c>
       <c r="AE49">
-        <v>6E-07</v>
+        <v>6.572454731906799E-07</v>
       </c>
       <c r="AF49">
-        <v>6E-07</v>
+        <v>6.572454731906799E-07</v>
       </c>
       <c r="AG49">
-        <v>6E-07</v>
+        <v>6.572454731906799E-07</v>
       </c>
       <c r="AH49">
-        <v>6E-07</v>
+        <v>6.572454731906799E-07</v>
       </c>
       <c r="AI49">
-        <v>6E-07</v>
+        <v>6.572454731906799E-07</v>
       </c>
       <c r="AJ49">
-        <v>6E-07</v>
+        <v>6.572454731906799E-07</v>
       </c>
       <c r="AK49">
-        <v>6E-07</v>
+        <v>6.572454731906799E-07</v>
       </c>
       <c r="AL49">
-        <v>6E-07</v>
+        <v>6.572454731906799E-07</v>
       </c>
       <c r="AM49">
-        <v>6E-07</v>
+        <v>6.572454731906799E-07</v>
       </c>
       <c r="AN49">
-        <v>6E-07</v>
+        <v>6.572454731906799E-07</v>
       </c>
       <c r="AO49">
-        <v>6E-07</v>
+        <v>6.572454731906799E-07</v>
       </c>
       <c r="AP49">
-        <v>6E-07</v>
+        <v>6.572454731906799E-07</v>
       </c>
       <c r="AQ49">
-        <v>6E-07</v>
+        <v>6.572454731906799E-07</v>
       </c>
       <c r="AR49">
-        <v>6E-07</v>
+        <v>6.572454731906799E-07</v>
       </c>
       <c r="AS49">
-        <v>6E-07</v>
+        <v>6.572454731906799E-07</v>
       </c>
     </row>
     <row r="50" spans="1:45">
@@ -9403,112 +9403,112 @@
         <v>1</v>
       </c>
       <c r="J69">
-        <v>0.00116</v>
+        <v>0.001293497558415</v>
       </c>
       <c r="K69">
-        <v>0.00116</v>
+        <v>0.001293497558415</v>
       </c>
       <c r="L69">
-        <v>0.00116</v>
+        <v>0.001293497558415</v>
       </c>
       <c r="M69">
-        <v>0.00116</v>
+        <v>0.001293497558415</v>
       </c>
       <c r="N69">
-        <v>0.00116</v>
+        <v>0.001293497558415</v>
       </c>
       <c r="O69">
-        <v>0.00116</v>
+        <v>0.001293497558415</v>
       </c>
       <c r="P69">
-        <v>0.00116</v>
+        <v>0.001293497558415</v>
       </c>
       <c r="Q69">
-        <v>0.00116</v>
+        <v>0.001293497558415</v>
       </c>
       <c r="R69">
-        <v>0.00116</v>
+        <v>0.001293497558415</v>
       </c>
       <c r="S69">
-        <v>0.00116</v>
+        <v>0.001293497558415</v>
       </c>
       <c r="T69">
-        <v>0.00116</v>
+        <v>0.001293497558415</v>
       </c>
       <c r="U69">
-        <v>0.00116</v>
+        <v>0.001293497558415</v>
       </c>
       <c r="V69">
-        <v>0.00116</v>
+        <v>0.001293497558415</v>
       </c>
       <c r="W69">
-        <v>0.00116</v>
+        <v>0.001293497558415</v>
       </c>
       <c r="X69">
-        <v>0.00116</v>
+        <v>0.001293497558415</v>
       </c>
       <c r="Y69">
-        <v>0.00116</v>
+        <v>0.001293497558415</v>
       </c>
       <c r="Z69">
-        <v>0.00116</v>
+        <v>0.001293497558415</v>
       </c>
       <c r="AA69">
-        <v>0.00116</v>
+        <v>0.001293497558415</v>
       </c>
       <c r="AB69">
-        <v>0.00116</v>
+        <v>0.001293497558415</v>
       </c>
       <c r="AC69">
-        <v>0.00116</v>
+        <v>0.001293497558415</v>
       </c>
       <c r="AD69">
-        <v>0.00116</v>
+        <v>0.001293497558415</v>
       </c>
       <c r="AE69">
-        <v>0.00116</v>
+        <v>0.001293497558415</v>
       </c>
       <c r="AF69">
-        <v>0.00116</v>
+        <v>0.001293497558415</v>
       </c>
       <c r="AG69">
-        <v>0.00116</v>
+        <v>0.001293497558415</v>
       </c>
       <c r="AH69">
-        <v>0.00116</v>
+        <v>0.001293497558415</v>
       </c>
       <c r="AI69">
-        <v>0.00116</v>
+        <v>0.001293497558415</v>
       </c>
       <c r="AJ69">
-        <v>0.00116</v>
+        <v>0.001293497558415</v>
       </c>
       <c r="AK69">
-        <v>0.00116</v>
+        <v>0.001293497558415</v>
       </c>
       <c r="AL69">
-        <v>0.00116</v>
+        <v>0.001293497558415</v>
       </c>
       <c r="AM69">
-        <v>0.00116</v>
+        <v>0.001293497558415</v>
       </c>
       <c r="AN69">
-        <v>0.00116</v>
+        <v>0.001293497558415</v>
       </c>
       <c r="AO69">
-        <v>0.00116</v>
+        <v>0.001293497558415</v>
       </c>
       <c r="AP69">
-        <v>0.00116</v>
+        <v>0.001293497558415</v>
       </c>
       <c r="AQ69">
-        <v>0.00116</v>
+        <v>0.001293497558415</v>
       </c>
       <c r="AR69">
-        <v>0.00116</v>
+        <v>0.001293497558415</v>
       </c>
       <c r="AS69">
-        <v>0.00116</v>
+        <v>0.001293497558415</v>
       </c>
     </row>
     <row r="70" spans="1:45">
@@ -9525,112 +9525,112 @@
         <v>1</v>
       </c>
       <c r="J70">
-        <v>0.000173571</v>
+        <v>0.0001935462626824</v>
       </c>
       <c r="K70">
-        <v>0.000173571</v>
+        <v>0.0001935462626824</v>
       </c>
       <c r="L70">
-        <v>0.000173571</v>
+        <v>0.0001935462626824</v>
       </c>
       <c r="M70">
-        <v>0.000173571</v>
+        <v>0.0001935462626824</v>
       </c>
       <c r="N70">
-        <v>0.000173571</v>
+        <v>0.0001935462626824</v>
       </c>
       <c r="O70">
-        <v>0.000173571</v>
+        <v>0.0001935462626824</v>
       </c>
       <c r="P70">
-        <v>0.000173571</v>
+        <v>0.0001935462626824</v>
       </c>
       <c r="Q70">
-        <v>0.000173571</v>
+        <v>0.0001935462626824</v>
       </c>
       <c r="R70">
-        <v>0.000173571</v>
+        <v>0.0001935462626824</v>
       </c>
       <c r="S70">
-        <v>0.000173571</v>
+        <v>0.0001935462626824</v>
       </c>
       <c r="T70">
-        <v>0.000173571</v>
+        <v>0.0001935462626824</v>
       </c>
       <c r="U70">
-        <v>0.000173571</v>
+        <v>0.0001935462626824</v>
       </c>
       <c r="V70">
-        <v>0.000173571</v>
+        <v>0.0001935462626824</v>
       </c>
       <c r="W70">
-        <v>0.000173571</v>
+        <v>0.0001935462626824</v>
       </c>
       <c r="X70">
-        <v>0.000173571</v>
+        <v>0.0001935462626824</v>
       </c>
       <c r="Y70">
-        <v>0.000173571</v>
+        <v>0.0001935462626824</v>
       </c>
       <c r="Z70">
-        <v>0.000173571</v>
+        <v>0.0001935462626824</v>
       </c>
       <c r="AA70">
-        <v>0.000173571</v>
+        <v>0.0001935462626824</v>
       </c>
       <c r="AB70">
-        <v>0.000173571</v>
+        <v>0.0001935462626824</v>
       </c>
       <c r="AC70">
-        <v>0.000173571</v>
+        <v>0.0001935462626824</v>
       </c>
       <c r="AD70">
-        <v>0.000173571</v>
+        <v>0.0001935462626824</v>
       </c>
       <c r="AE70">
-        <v>0.000173571</v>
+        <v>0.0001935462626824</v>
       </c>
       <c r="AF70">
-        <v>0.000173571</v>
+        <v>0.0001935462626824</v>
       </c>
       <c r="AG70">
-        <v>0.000173571</v>
+        <v>0.0001935462626824</v>
       </c>
       <c r="AH70">
-        <v>0.000173571</v>
+        <v>0.0001935462626824</v>
       </c>
       <c r="AI70">
-        <v>0.000173571</v>
+        <v>0.0001935462626824</v>
       </c>
       <c r="AJ70">
-        <v>0.000173571</v>
+        <v>0.0001935462626824</v>
       </c>
       <c r="AK70">
-        <v>0.000173571</v>
+        <v>0.0001935462626824</v>
       </c>
       <c r="AL70">
-        <v>0.000173571</v>
+        <v>0.0001935462626824</v>
       </c>
       <c r="AM70">
-        <v>0.000173571</v>
+        <v>0.0001935462626824</v>
       </c>
       <c r="AN70">
-        <v>0.000173571</v>
+        <v>0.0001935462626824</v>
       </c>
       <c r="AO70">
-        <v>0.000173571</v>
+        <v>0.0001935462626824</v>
       </c>
       <c r="AP70">
-        <v>0.000173571</v>
+        <v>0.0001935462626824</v>
       </c>
       <c r="AQ70">
-        <v>0.000173571</v>
+        <v>0.0001935462626824</v>
       </c>
       <c r="AR70">
-        <v>0.000173571</v>
+        <v>0.0001935462626824</v>
       </c>
       <c r="AS70">
-        <v>0.000173571</v>
+        <v>0.0001935462626824</v>
       </c>
     </row>
     <row r="71" spans="1:45">
@@ -9647,112 +9647,112 @@
         <v>1</v>
       </c>
       <c r="J71">
-        <v>0.00396543</v>
+        <v>0.0044217879509189</v>
       </c>
       <c r="K71">
-        <v>0.00396543</v>
+        <v>0.0044217879509189</v>
       </c>
       <c r="L71">
-        <v>0.00396543</v>
+        <v>0.0044217879509189</v>
       </c>
       <c r="M71">
-        <v>0.00396543</v>
+        <v>0.0044217879509189</v>
       </c>
       <c r="N71">
-        <v>0.00396543</v>
+        <v>0.0044217879509189</v>
       </c>
       <c r="O71">
-        <v>0.00396543</v>
+        <v>0.0044217879509189</v>
       </c>
       <c r="P71">
-        <v>0.00396543</v>
+        <v>0.0044217879509189</v>
       </c>
       <c r="Q71">
-        <v>0.00396543</v>
+        <v>0.0044217879509189</v>
       </c>
       <c r="R71">
-        <v>0.00396543</v>
+        <v>0.0044217879509189</v>
       </c>
       <c r="S71">
-        <v>0.00396543</v>
+        <v>0.0044217879509189</v>
       </c>
       <c r="T71">
-        <v>0.00396543</v>
+        <v>0.0044217879509189</v>
       </c>
       <c r="U71">
-        <v>0.00396543</v>
+        <v>0.0044217879509189</v>
       </c>
       <c r="V71">
-        <v>0.00396543</v>
+        <v>0.0044217879509189</v>
       </c>
       <c r="W71">
-        <v>0.00396543</v>
+        <v>0.0044217879509189</v>
       </c>
       <c r="X71">
-        <v>0.00396543</v>
+        <v>0.0044217879509189</v>
       </c>
       <c r="Y71">
-        <v>0.00396543</v>
+        <v>0.0044217879509189</v>
       </c>
       <c r="Z71">
-        <v>0.00396543</v>
+        <v>0.0044217879509189</v>
       </c>
       <c r="AA71">
-        <v>0.00396543</v>
+        <v>0.0044217879509189</v>
       </c>
       <c r="AB71">
-        <v>0.00396543</v>
+        <v>0.0044217879509189</v>
       </c>
       <c r="AC71">
-        <v>0.00396543</v>
+        <v>0.0044217879509189</v>
       </c>
       <c r="AD71">
-        <v>0.00396543</v>
+        <v>0.0044217879509189</v>
       </c>
       <c r="AE71">
-        <v>0.00396543</v>
+        <v>0.0044217879509189</v>
       </c>
       <c r="AF71">
-        <v>0.00396543</v>
+        <v>0.0044217879509189</v>
       </c>
       <c r="AG71">
-        <v>0.00396543</v>
+        <v>0.0044217879509189</v>
       </c>
       <c r="AH71">
-        <v>0.00396543</v>
+        <v>0.0044217879509189</v>
       </c>
       <c r="AI71">
-        <v>0.00396543</v>
+        <v>0.0044217879509189</v>
       </c>
       <c r="AJ71">
-        <v>0.00396543</v>
+        <v>0.0044217879509189</v>
       </c>
       <c r="AK71">
-        <v>0.00396543</v>
+        <v>0.0044217879509189</v>
       </c>
       <c r="AL71">
-        <v>0.00396543</v>
+        <v>0.0044217879509189</v>
       </c>
       <c r="AM71">
-        <v>0.00396543</v>
+        <v>0.0044217879509189</v>
       </c>
       <c r="AN71">
-        <v>0.00396543</v>
+        <v>0.0044217879509189</v>
       </c>
       <c r="AO71">
-        <v>0.00396543</v>
+        <v>0.0044217879509189</v>
       </c>
       <c r="AP71">
-        <v>0.00396543</v>
+        <v>0.0044217879509189</v>
       </c>
       <c r="AQ71">
-        <v>0.00396543</v>
+        <v>0.0044217879509189</v>
       </c>
       <c r="AR71">
-        <v>0.00396543</v>
+        <v>0.0044217879509189</v>
       </c>
       <c r="AS71">
-        <v>0.00396543</v>
+        <v>0.0044217879509189</v>
       </c>
     </row>
     <row r="72" spans="1:45">
@@ -10754,112 +10754,112 @@
         <v>1</v>
       </c>
       <c r="J80">
-        <v>3.15</v>
+        <v>2.276699079970339</v>
       </c>
       <c r="K80">
-        <v>3.15</v>
+        <v>2.276699079970339</v>
       </c>
       <c r="L80">
-        <v>3.15</v>
+        <v>2.276699079970339</v>
       </c>
       <c r="M80">
-        <v>3.15</v>
+        <v>2.276699079970339</v>
       </c>
       <c r="N80">
-        <v>3.15</v>
+        <v>2.276699079970339</v>
       </c>
       <c r="O80">
-        <v>3.15</v>
+        <v>2.276699079970339</v>
       </c>
       <c r="P80">
-        <v>3.15</v>
+        <v>2.276699079970339</v>
       </c>
       <c r="Q80">
-        <v>3.15</v>
+        <v>2.276699079970339</v>
       </c>
       <c r="R80">
-        <v>3.15</v>
+        <v>2.276699079970339</v>
       </c>
       <c r="S80">
-        <v>3.15</v>
+        <v>2.276699079970339</v>
       </c>
       <c r="T80">
-        <v>3.15</v>
+        <v>2.276699079970339</v>
       </c>
       <c r="U80">
-        <v>3.15</v>
+        <v>2.276699079970339</v>
       </c>
       <c r="V80">
-        <v>3.15</v>
+        <v>2.276699079970339</v>
       </c>
       <c r="W80">
-        <v>3.15</v>
+        <v>2.276699079970339</v>
       </c>
       <c r="X80">
-        <v>3.15</v>
+        <v>2.276699079970339</v>
       </c>
       <c r="Y80">
-        <v>3.15</v>
+        <v>2.276699079970339</v>
       </c>
       <c r="Z80">
-        <v>3.15</v>
+        <v>2.276699079970339</v>
       </c>
       <c r="AA80">
-        <v>3.15</v>
+        <v>2.276699079970339</v>
       </c>
       <c r="AB80">
-        <v>3.15</v>
+        <v>2.276699079970339</v>
       </c>
       <c r="AC80">
-        <v>3.15</v>
+        <v>2.276699079970339</v>
       </c>
       <c r="AD80">
-        <v>3.15</v>
+        <v>2.276699079970339</v>
       </c>
       <c r="AE80">
-        <v>3.15</v>
+        <v>2.276699079970339</v>
       </c>
       <c r="AF80">
-        <v>3.15</v>
+        <v>2.276699079970339</v>
       </c>
       <c r="AG80">
-        <v>3.15</v>
+        <v>2.276699079970339</v>
       </c>
       <c r="AH80">
-        <v>3.15</v>
+        <v>2.276699079970339</v>
       </c>
       <c r="AI80">
-        <v>3.15</v>
+        <v>2.276699079970339</v>
       </c>
       <c r="AJ80">
-        <v>3.15</v>
+        <v>2.276699079970339</v>
       </c>
       <c r="AK80">
-        <v>3.15</v>
+        <v>2.276699079970339</v>
       </c>
       <c r="AL80">
-        <v>3.15</v>
+        <v>2.276699079970339</v>
       </c>
       <c r="AM80">
-        <v>3.15</v>
+        <v>2.276699079970339</v>
       </c>
       <c r="AN80">
-        <v>3.15</v>
+        <v>2.276699079970339</v>
       </c>
       <c r="AO80">
-        <v>3.15</v>
+        <v>2.276699079970339</v>
       </c>
       <c r="AP80">
-        <v>3.15</v>
+        <v>2.276699079970339</v>
       </c>
       <c r="AQ80">
-        <v>3.15</v>
+        <v>2.276699079970339</v>
       </c>
       <c r="AR80">
-        <v>3.15</v>
+        <v>2.276699079970339</v>
       </c>
       <c r="AS80">
-        <v>3.15</v>
+        <v>2.276699079970339</v>
       </c>
     </row>
     <row r="81" spans="1:45">
@@ -10876,112 +10876,112 @@
         <v>1</v>
       </c>
       <c r="J81">
-        <v>3.08</v>
+        <v>2.22610576708211</v>
       </c>
       <c r="K81">
-        <v>3.08</v>
+        <v>2.22610576708211</v>
       </c>
       <c r="L81">
-        <v>3.08</v>
+        <v>2.22610576708211</v>
       </c>
       <c r="M81">
-        <v>3.08</v>
+        <v>2.22610576708211</v>
       </c>
       <c r="N81">
-        <v>3.08</v>
+        <v>2.22610576708211</v>
       </c>
       <c r="O81">
-        <v>3.08</v>
+        <v>2.22610576708211</v>
       </c>
       <c r="P81">
-        <v>3.08</v>
+        <v>2.22610576708211</v>
       </c>
       <c r="Q81">
-        <v>3.08</v>
+        <v>2.22610576708211</v>
       </c>
       <c r="R81">
-        <v>3.08</v>
+        <v>2.22610576708211</v>
       </c>
       <c r="S81">
-        <v>3.08</v>
+        <v>2.22610576708211</v>
       </c>
       <c r="T81">
-        <v>3.08</v>
+        <v>2.22610576708211</v>
       </c>
       <c r="U81">
-        <v>3.08</v>
+        <v>2.22610576708211</v>
       </c>
       <c r="V81">
-        <v>3.08</v>
+        <v>2.22610576708211</v>
       </c>
       <c r="W81">
-        <v>3.08</v>
+        <v>2.22610576708211</v>
       </c>
       <c r="X81">
-        <v>3.08</v>
+        <v>2.22610576708211</v>
       </c>
       <c r="Y81">
-        <v>3.08</v>
+        <v>2.22610576708211</v>
       </c>
       <c r="Z81">
-        <v>3.08</v>
+        <v>2.22610576708211</v>
       </c>
       <c r="AA81">
-        <v>3.08</v>
+        <v>2.22610576708211</v>
       </c>
       <c r="AB81">
-        <v>3.08</v>
+        <v>2.22610576708211</v>
       </c>
       <c r="AC81">
-        <v>3.08</v>
+        <v>2.22610576708211</v>
       </c>
       <c r="AD81">
-        <v>3.08</v>
+        <v>2.22610576708211</v>
       </c>
       <c r="AE81">
-        <v>3.08</v>
+        <v>2.22610576708211</v>
       </c>
       <c r="AF81">
-        <v>3.08</v>
+        <v>2.22610576708211</v>
       </c>
       <c r="AG81">
-        <v>3.08</v>
+        <v>2.22610576708211</v>
       </c>
       <c r="AH81">
-        <v>3.08</v>
+        <v>2.22610576708211</v>
       </c>
       <c r="AI81">
-        <v>3.08</v>
+        <v>2.22610576708211</v>
       </c>
       <c r="AJ81">
-        <v>3.08</v>
+        <v>2.22610576708211</v>
       </c>
       <c r="AK81">
-        <v>3.08</v>
+        <v>2.22610576708211</v>
       </c>
       <c r="AL81">
-        <v>3.08</v>
+        <v>2.22610576708211</v>
       </c>
       <c r="AM81">
-        <v>3.08</v>
+        <v>2.22610576708211</v>
       </c>
       <c r="AN81">
-        <v>3.08</v>
+        <v>2.22610576708211</v>
       </c>
       <c r="AO81">
-        <v>3.08</v>
+        <v>2.22610576708211</v>
       </c>
       <c r="AP81">
-        <v>3.08</v>
+        <v>2.22610576708211</v>
       </c>
       <c r="AQ81">
-        <v>3.08</v>
+        <v>2.22610576708211</v>
       </c>
       <c r="AR81">
-        <v>3.08</v>
+        <v>2.22610576708211</v>
       </c>
       <c r="AS81">
-        <v>3.08</v>
+        <v>2.22610576708211</v>
       </c>
     </row>
     <row r="82" spans="1:45">
@@ -10998,112 +10998,112 @@
         <v>1</v>
       </c>
       <c r="J82">
-        <v>0.52</v>
+        <v>0.3758360385982783</v>
       </c>
       <c r="K82">
-        <v>0.52</v>
+        <v>0.3758360385982783</v>
       </c>
       <c r="L82">
-        <v>0.52</v>
+        <v>0.3758360385982783</v>
       </c>
       <c r="M82">
-        <v>0.52</v>
+        <v>0.3758360385982783</v>
       </c>
       <c r="N82">
-        <v>0.52</v>
+        <v>0.3758360385982783</v>
       </c>
       <c r="O82">
-        <v>0.52</v>
+        <v>0.3758360385982783</v>
       </c>
       <c r="P82">
-        <v>0.52</v>
+        <v>0.3758360385982783</v>
       </c>
       <c r="Q82">
-        <v>0.52</v>
+        <v>0.3758360385982783</v>
       </c>
       <c r="R82">
-        <v>0.52</v>
+        <v>0.3758360385982783</v>
       </c>
       <c r="S82">
-        <v>0.52</v>
+        <v>0.3758360385982783</v>
       </c>
       <c r="T82">
-        <v>0.52</v>
+        <v>0.3758360385982783</v>
       </c>
       <c r="U82">
-        <v>0.52</v>
+        <v>0.3758360385982783</v>
       </c>
       <c r="V82">
-        <v>0.52</v>
+        <v>0.3758360385982783</v>
       </c>
       <c r="W82">
-        <v>0.52</v>
+        <v>0.3758360385982783</v>
       </c>
       <c r="X82">
-        <v>0.52</v>
+        <v>0.3758360385982783</v>
       </c>
       <c r="Y82">
-        <v>0.52</v>
+        <v>0.3758360385982783</v>
       </c>
       <c r="Z82">
-        <v>0.52</v>
+        <v>0.3758360385982783</v>
       </c>
       <c r="AA82">
-        <v>0.52</v>
+        <v>0.3758360385982783</v>
       </c>
       <c r="AB82">
-        <v>0.52</v>
+        <v>0.3758360385982783</v>
       </c>
       <c r="AC82">
-        <v>0.52</v>
+        <v>0.3758360385982783</v>
       </c>
       <c r="AD82">
-        <v>0.52</v>
+        <v>0.3758360385982783</v>
       </c>
       <c r="AE82">
-        <v>0.52</v>
+        <v>0.3758360385982783</v>
       </c>
       <c r="AF82">
-        <v>0.52</v>
+        <v>0.3758360385982783</v>
       </c>
       <c r="AG82">
-        <v>0.52</v>
+        <v>0.3758360385982783</v>
       </c>
       <c r="AH82">
-        <v>0.52</v>
+        <v>0.3758360385982783</v>
       </c>
       <c r="AI82">
-        <v>0.52</v>
+        <v>0.3758360385982783</v>
       </c>
       <c r="AJ82">
-        <v>0.52</v>
+        <v>0.3758360385982783</v>
       </c>
       <c r="AK82">
-        <v>0.52</v>
+        <v>0.3758360385982783</v>
       </c>
       <c r="AL82">
-        <v>0.52</v>
+        <v>0.3758360385982783</v>
       </c>
       <c r="AM82">
-        <v>0.52</v>
+        <v>0.3758360385982783</v>
       </c>
       <c r="AN82">
-        <v>0.52</v>
+        <v>0.3758360385982783</v>
       </c>
       <c r="AO82">
-        <v>0.52</v>
+        <v>0.3758360385982783</v>
       </c>
       <c r="AP82">
-        <v>0.52</v>
+        <v>0.3758360385982783</v>
       </c>
       <c r="AQ82">
-        <v>0.52</v>
+        <v>0.3758360385982783</v>
       </c>
       <c r="AR82">
-        <v>0.52</v>
+        <v>0.3758360385982783</v>
       </c>
       <c r="AS82">
-        <v>0.52</v>
+        <v>0.3758360385982783</v>
       </c>
     </row>
     <row r="83" spans="1:45">
@@ -11120,112 +11120,112 @@
         <v>1</v>
       </c>
       <c r="J83">
-        <v>0.848907407</v>
+        <v>0.6135576865069545</v>
       </c>
       <c r="K83">
-        <v>0.848907407</v>
+        <v>0.6135576865069545</v>
       </c>
       <c r="L83">
-        <v>0.848907407</v>
+        <v>0.6135576865069545</v>
       </c>
       <c r="M83">
-        <v>0.848907407</v>
+        <v>0.6135576865069545</v>
       </c>
       <c r="N83">
-        <v>0.848907407</v>
+        <v>0.6135576865069545</v>
       </c>
       <c r="O83">
-        <v>0.848907407</v>
+        <v>0.6135576865069545</v>
       </c>
       <c r="P83">
-        <v>0.848907407</v>
+        <v>0.6135576865069545</v>
       </c>
       <c r="Q83">
-        <v>0.848907407</v>
+        <v>0.6135576865069545</v>
       </c>
       <c r="R83">
-        <v>0.848907407</v>
+        <v>0.6135576865069545</v>
       </c>
       <c r="S83">
-        <v>0.848907407</v>
+        <v>0.6135576865069545</v>
       </c>
       <c r="T83">
-        <v>0.848907407</v>
+        <v>0.6135576865069545</v>
       </c>
       <c r="U83">
-        <v>0.848907407</v>
+        <v>0.6135576865069545</v>
       </c>
       <c r="V83">
-        <v>0.848907407</v>
+        <v>0.6135576865069545</v>
       </c>
       <c r="W83">
-        <v>0.848907407</v>
+        <v>0.6135576865069545</v>
       </c>
       <c r="X83">
-        <v>0.848907407</v>
+        <v>0.6135576865069545</v>
       </c>
       <c r="Y83">
-        <v>0.848907407</v>
+        <v>0.6135576865069545</v>
       </c>
       <c r="Z83">
-        <v>0.848907407</v>
+        <v>0.6135576865069545</v>
       </c>
       <c r="AA83">
-        <v>0.848907407</v>
+        <v>0.6135576865069545</v>
       </c>
       <c r="AB83">
-        <v>0.848907407</v>
+        <v>0.6135576865069545</v>
       </c>
       <c r="AC83">
-        <v>0.848907407</v>
+        <v>0.6135576865069545</v>
       </c>
       <c r="AD83">
-        <v>0.848907407</v>
+        <v>0.6135576865069545</v>
       </c>
       <c r="AE83">
-        <v>0.848907407</v>
+        <v>0.6135576865069545</v>
       </c>
       <c r="AF83">
-        <v>0.848907407</v>
+        <v>0.6135576865069545</v>
       </c>
       <c r="AG83">
-        <v>0.848907407</v>
+        <v>0.6135576865069545</v>
       </c>
       <c r="AH83">
-        <v>0.848907407</v>
+        <v>0.6135576865069545</v>
       </c>
       <c r="AI83">
-        <v>0.848907407</v>
+        <v>0.6135576865069545</v>
       </c>
       <c r="AJ83">
-        <v>0.848907407</v>
+        <v>0.6135576865069545</v>
       </c>
       <c r="AK83">
-        <v>0.848907407</v>
+        <v>0.6135576865069545</v>
       </c>
       <c r="AL83">
-        <v>0.848907407</v>
+        <v>0.6135576865069545</v>
       </c>
       <c r="AM83">
-        <v>0.848907407</v>
+        <v>0.6135576865069545</v>
       </c>
       <c r="AN83">
-        <v>0.848907407</v>
+        <v>0.6135576865069545</v>
       </c>
       <c r="AO83">
-        <v>0.848907407</v>
+        <v>0.6135576865069545</v>
       </c>
       <c r="AP83">
-        <v>0.848907407</v>
+        <v>0.6135576865069545</v>
       </c>
       <c r="AQ83">
-        <v>0.848907407</v>
+        <v>0.6135576865069545</v>
       </c>
       <c r="AR83">
-        <v>0.848907407</v>
+        <v>0.6135576865069545</v>
       </c>
       <c r="AS83">
-        <v>0.848907407</v>
+        <v>0.6135576865069545</v>
       </c>
     </row>
     <row r="84" spans="1:45">
@@ -11242,112 +11242,112 @@
         <v>1</v>
       </c>
       <c r="J84">
-        <v>0.2</v>
+        <v>0.1445523225377993</v>
       </c>
       <c r="K84">
-        <v>0.2</v>
+        <v>0.1445523225377993</v>
       </c>
       <c r="L84">
-        <v>0.2</v>
+        <v>0.1445523225377993</v>
       </c>
       <c r="M84">
-        <v>0.2</v>
+        <v>0.1445523225377993</v>
       </c>
       <c r="N84">
-        <v>0.2</v>
+        <v>0.1445523225377993</v>
       </c>
       <c r="O84">
-        <v>0.2</v>
+        <v>0.1445523225377993</v>
       </c>
       <c r="P84">
-        <v>0.2</v>
+        <v>0.1445523225377993</v>
       </c>
       <c r="Q84">
-        <v>0.2</v>
+        <v>0.1445523225377993</v>
       </c>
       <c r="R84">
-        <v>0.2</v>
+        <v>0.1445523225377993</v>
       </c>
       <c r="S84">
-        <v>0.2</v>
+        <v>0.1445523225377993</v>
       </c>
       <c r="T84">
-        <v>0.2</v>
+        <v>0.1445523225377993</v>
       </c>
       <c r="U84">
-        <v>0.2</v>
+        <v>0.1445523225377993</v>
       </c>
       <c r="V84">
-        <v>0.2</v>
+        <v>0.1445523225377993</v>
       </c>
       <c r="W84">
-        <v>0.2</v>
+        <v>0.1445523225377993</v>
       </c>
       <c r="X84">
-        <v>0.2</v>
+        <v>0.1445523225377993</v>
       </c>
       <c r="Y84">
-        <v>0.2</v>
+        <v>0.1445523225377993</v>
       </c>
       <c r="Z84">
-        <v>0.2</v>
+        <v>0.1445523225377993</v>
       </c>
       <c r="AA84">
-        <v>0.2</v>
+        <v>0.1445523225377993</v>
       </c>
       <c r="AB84">
-        <v>0.2</v>
+        <v>0.1445523225377993</v>
       </c>
       <c r="AC84">
-        <v>0.2</v>
+        <v>0.1445523225377993</v>
       </c>
       <c r="AD84">
-        <v>0.2</v>
+        <v>0.1445523225377993</v>
       </c>
       <c r="AE84">
-        <v>0.2</v>
+        <v>0.1445523225377993</v>
       </c>
       <c r="AF84">
-        <v>0.2</v>
+        <v>0.1445523225377993</v>
       </c>
       <c r="AG84">
-        <v>0.2</v>
+        <v>0.1445523225377993</v>
       </c>
       <c r="AH84">
-        <v>0.2</v>
+        <v>0.1445523225377993</v>
       </c>
       <c r="AI84">
-        <v>0.2</v>
+        <v>0.1445523225377993</v>
       </c>
       <c r="AJ84">
-        <v>0.2</v>
+        <v>0.1445523225377993</v>
       </c>
       <c r="AK84">
-        <v>0.2</v>
+        <v>0.1445523225377993</v>
       </c>
       <c r="AL84">
-        <v>0.2</v>
+        <v>0.1445523225377993</v>
       </c>
       <c r="AM84">
-        <v>0.2</v>
+        <v>0.1445523225377993</v>
       </c>
       <c r="AN84">
-        <v>0.2</v>
+        <v>0.1445523225377993</v>
       </c>
       <c r="AO84">
-        <v>0.2</v>
+        <v>0.1445523225377993</v>
       </c>
       <c r="AP84">
-        <v>0.2</v>
+        <v>0.1445523225377993</v>
       </c>
       <c r="AQ84">
-        <v>0.2</v>
+        <v>0.1445523225377993</v>
       </c>
       <c r="AR84">
-        <v>0.2</v>
+        <v>0.1445523225377993</v>
       </c>
       <c r="AS84">
-        <v>0.2</v>
+        <v>0.1445523225377993</v>
       </c>
     </row>
     <row r="85" spans="1:45">
@@ -11364,112 +11364,112 @@
         <v>1</v>
       </c>
       <c r="J85">
-        <v>0.75</v>
+        <v>0.5420712095167476</v>
       </c>
       <c r="K85">
-        <v>0.75</v>
+        <v>0.5420712095167476</v>
       </c>
       <c r="L85">
-        <v>0.75</v>
+        <v>0.5420712095167476</v>
       </c>
       <c r="M85">
-        <v>0.75</v>
+        <v>0.5420712095167476</v>
       </c>
       <c r="N85">
-        <v>0.75</v>
+        <v>0.5420712095167476</v>
       </c>
       <c r="O85">
-        <v>0.75</v>
+        <v>0.5420712095167476</v>
       </c>
       <c r="P85">
-        <v>0.75</v>
+        <v>0.5420712095167476</v>
       </c>
       <c r="Q85">
-        <v>0.75</v>
+        <v>0.5420712095167476</v>
       </c>
       <c r="R85">
-        <v>0.75</v>
+        <v>0.5420712095167476</v>
       </c>
       <c r="S85">
-        <v>0.75</v>
+        <v>0.5420712095167476</v>
       </c>
       <c r="T85">
-        <v>0.75</v>
+        <v>0.5420712095167476</v>
       </c>
       <c r="U85">
-        <v>0.75</v>
+        <v>0.5420712095167476</v>
       </c>
       <c r="V85">
-        <v>0.75</v>
+        <v>0.5420712095167476</v>
       </c>
       <c r="W85">
-        <v>0.75</v>
+        <v>0.5420712095167476</v>
       </c>
       <c r="X85">
-        <v>0.75</v>
+        <v>0.5420712095167476</v>
       </c>
       <c r="Y85">
-        <v>0.75</v>
+        <v>0.5420712095167476</v>
       </c>
       <c r="Z85">
-        <v>0.75</v>
+        <v>0.5420712095167476</v>
       </c>
       <c r="AA85">
-        <v>0.75</v>
+        <v>0.5420712095167476</v>
       </c>
       <c r="AB85">
-        <v>0.75</v>
+        <v>0.5420712095167476</v>
       </c>
       <c r="AC85">
-        <v>0.75</v>
+        <v>0.5420712095167476</v>
       </c>
       <c r="AD85">
-        <v>0.75</v>
+        <v>0.5420712095167476</v>
       </c>
       <c r="AE85">
-        <v>0.75</v>
+        <v>0.5420712095167476</v>
       </c>
       <c r="AF85">
-        <v>0.75</v>
+        <v>0.5420712095167476</v>
       </c>
       <c r="AG85">
-        <v>0.75</v>
+        <v>0.5420712095167476</v>
       </c>
       <c r="AH85">
-        <v>0.75</v>
+        <v>0.5420712095167476</v>
       </c>
       <c r="AI85">
-        <v>0.75</v>
+        <v>0.5420712095167476</v>
       </c>
       <c r="AJ85">
-        <v>0.75</v>
+        <v>0.5420712095167476</v>
       </c>
       <c r="AK85">
-        <v>0.75</v>
+        <v>0.5420712095167476</v>
       </c>
       <c r="AL85">
-        <v>0.75</v>
+        <v>0.5420712095167476</v>
       </c>
       <c r="AM85">
-        <v>0.75</v>
+        <v>0.5420712095167476</v>
       </c>
       <c r="AN85">
-        <v>0.75</v>
+        <v>0.5420712095167476</v>
       </c>
       <c r="AO85">
-        <v>0.75</v>
+        <v>0.5420712095167476</v>
       </c>
       <c r="AP85">
-        <v>0.75</v>
+        <v>0.5420712095167476</v>
       </c>
       <c r="AQ85">
-        <v>0.75</v>
+        <v>0.5420712095167476</v>
       </c>
       <c r="AR85">
-        <v>0.75</v>
+        <v>0.5420712095167476</v>
       </c>
       <c r="AS85">
-        <v>0.75</v>
+        <v>0.5420712095167476</v>
       </c>
     </row>
     <row r="86" spans="1:45">
@@ -11486,112 +11486,112 @@
         <v>1</v>
       </c>
       <c r="J86">
-        <v>1.866738095</v>
+        <v>1.349206636010186</v>
       </c>
       <c r="K86">
-        <v>1.866738095</v>
+        <v>1.349206636010186</v>
       </c>
       <c r="L86">
-        <v>1.866738095</v>
+        <v>1.349206636010186</v>
       </c>
       <c r="M86">
-        <v>1.866738095</v>
+        <v>1.349206636010186</v>
       </c>
       <c r="N86">
-        <v>1.866738095</v>
+        <v>1.349206636010186</v>
       </c>
       <c r="O86">
-        <v>1.866738095</v>
+        <v>1.349206636010186</v>
       </c>
       <c r="P86">
-        <v>1.866738095</v>
+        <v>1.349206636010186</v>
       </c>
       <c r="Q86">
-        <v>1.866738095</v>
+        <v>1.349206636010186</v>
       </c>
       <c r="R86">
-        <v>1.866738095</v>
+        <v>1.349206636010186</v>
       </c>
       <c r="S86">
-        <v>1.866738095</v>
+        <v>1.349206636010186</v>
       </c>
       <c r="T86">
-        <v>1.866738095</v>
+        <v>1.349206636010186</v>
       </c>
       <c r="U86">
-        <v>1.866738095</v>
+        <v>1.349206636010186</v>
       </c>
       <c r="V86">
-        <v>1.866738095</v>
+        <v>1.349206636010186</v>
       </c>
       <c r="W86">
-        <v>1.866738095</v>
+        <v>1.349206636010186</v>
       </c>
       <c r="X86">
-        <v>1.866738095</v>
+        <v>1.349206636010186</v>
       </c>
       <c r="Y86">
-        <v>1.866738095</v>
+        <v>1.349206636010186</v>
       </c>
       <c r="Z86">
-        <v>1.866738095</v>
+        <v>1.349206636010186</v>
       </c>
       <c r="AA86">
-        <v>1.866738095</v>
+        <v>1.349206636010186</v>
       </c>
       <c r="AB86">
-        <v>1.866738095</v>
+        <v>1.349206636010186</v>
       </c>
       <c r="AC86">
-        <v>1.866738095</v>
+        <v>1.349206636010186</v>
       </c>
       <c r="AD86">
-        <v>1.866738095</v>
+        <v>1.349206636010186</v>
       </c>
       <c r="AE86">
-        <v>1.866738095</v>
+        <v>1.349206636010186</v>
       </c>
       <c r="AF86">
-        <v>1.866738095</v>
+        <v>1.349206636010186</v>
       </c>
       <c r="AG86">
-        <v>1.866738095</v>
+        <v>1.349206636010186</v>
       </c>
       <c r="AH86">
-        <v>1.866738095</v>
+        <v>1.349206636010186</v>
       </c>
       <c r="AI86">
-        <v>1.866738095</v>
+        <v>1.349206636010186</v>
       </c>
       <c r="AJ86">
-        <v>1.866738095</v>
+        <v>1.349206636010186</v>
       </c>
       <c r="AK86">
-        <v>1.866738095</v>
+        <v>1.349206636010186</v>
       </c>
       <c r="AL86">
-        <v>1.866738095</v>
+        <v>1.349206636010186</v>
       </c>
       <c r="AM86">
-        <v>1.866738095</v>
+        <v>1.349206636010186</v>
       </c>
       <c r="AN86">
-        <v>1.866738095</v>
+        <v>1.349206636010186</v>
       </c>
       <c r="AO86">
-        <v>1.866738095</v>
+        <v>1.349206636010186</v>
       </c>
       <c r="AP86">
-        <v>1.866738095</v>
+        <v>1.349206636010186</v>
       </c>
       <c r="AQ86">
-        <v>1.866738095</v>
+        <v>1.349206636010186</v>
       </c>
       <c r="AR86">
-        <v>1.866738095</v>
+        <v>1.349206636010186</v>
       </c>
       <c r="AS86">
-        <v>1.866738095</v>
+        <v>1.349206636010186</v>
       </c>
     </row>
     <row r="87" spans="1:45">
@@ -11608,112 +11608,112 @@
         <v>1</v>
       </c>
       <c r="J87">
-        <v>1.43807229</v>
+        <v>1.039383447483759</v>
       </c>
       <c r="K87">
-        <v>1.43807229</v>
+        <v>1.039383447483759</v>
       </c>
       <c r="L87">
-        <v>1.43807229</v>
+        <v>1.039383447483759</v>
       </c>
       <c r="M87">
-        <v>1.43807229</v>
+        <v>1.039383447483759</v>
       </c>
       <c r="N87">
-        <v>1.43807229</v>
+        <v>1.039383447483759</v>
       </c>
       <c r="O87">
-        <v>1.43807229</v>
+        <v>1.039383447483759</v>
       </c>
       <c r="P87">
-        <v>1.43807229</v>
+        <v>1.039383447483759</v>
       </c>
       <c r="Q87">
-        <v>1.43807229</v>
+        <v>1.039383447483759</v>
       </c>
       <c r="R87">
-        <v>1.43807229</v>
+        <v>1.039383447483759</v>
       </c>
       <c r="S87">
-        <v>1.43807229</v>
+        <v>1.039383447483759</v>
       </c>
       <c r="T87">
-        <v>1.43807229</v>
+        <v>1.039383447483759</v>
       </c>
       <c r="U87">
-        <v>1.43807229</v>
+        <v>1.039383447483759</v>
       </c>
       <c r="V87">
-        <v>1.43807229</v>
+        <v>1.039383447483759</v>
       </c>
       <c r="W87">
-        <v>1.43807229</v>
+        <v>1.039383447483759</v>
       </c>
       <c r="X87">
-        <v>1.43807229</v>
+        <v>1.039383447483759</v>
       </c>
       <c r="Y87">
-        <v>1.43807229</v>
+        <v>1.039383447483759</v>
       </c>
       <c r="Z87">
-        <v>1.43807229</v>
+        <v>1.039383447483759</v>
       </c>
       <c r="AA87">
-        <v>1.43807229</v>
+        <v>1.039383447483759</v>
       </c>
       <c r="AB87">
-        <v>1.43807229</v>
+        <v>1.039383447483759</v>
       </c>
       <c r="AC87">
-        <v>1.43807229</v>
+        <v>1.039383447483759</v>
       </c>
       <c r="AD87">
-        <v>1.43807229</v>
+        <v>1.039383447483759</v>
       </c>
       <c r="AE87">
-        <v>1.43807229</v>
+        <v>1.039383447483759</v>
       </c>
       <c r="AF87">
-        <v>1.43807229</v>
+        <v>1.039383447483759</v>
       </c>
       <c r="AG87">
-        <v>1.43807229</v>
+        <v>1.039383447483759</v>
       </c>
       <c r="AH87">
-        <v>1.43807229</v>
+        <v>1.039383447483759</v>
       </c>
       <c r="AI87">
-        <v>1.43807229</v>
+        <v>1.039383447483759</v>
       </c>
       <c r="AJ87">
-        <v>1.43807229</v>
+        <v>1.039383447483759</v>
       </c>
       <c r="AK87">
-        <v>1.43807229</v>
+        <v>1.039383447483759</v>
       </c>
       <c r="AL87">
-        <v>1.43807229</v>
+        <v>1.039383447483759</v>
       </c>
       <c r="AM87">
-        <v>1.43807229</v>
+        <v>1.039383447483759</v>
       </c>
       <c r="AN87">
-        <v>1.43807229</v>
+        <v>1.039383447483759</v>
       </c>
       <c r="AO87">
-        <v>1.43807229</v>
+        <v>1.039383447483759</v>
       </c>
       <c r="AP87">
-        <v>1.43807229</v>
+        <v>1.039383447483759</v>
       </c>
       <c r="AQ87">
-        <v>1.43807229</v>
+        <v>1.039383447483759</v>
       </c>
       <c r="AR87">
-        <v>1.43807229</v>
+        <v>1.039383447483759</v>
       </c>
       <c r="AS87">
-        <v>1.43807229</v>
+        <v>1.039383447483759</v>
       </c>
     </row>
     <row r="88" spans="1:45">
@@ -11733,112 +11733,112 @@
         <v>1</v>
       </c>
       <c r="J88">
-        <v>1</v>
+        <v>0.733243641135974</v>
       </c>
       <c r="K88">
-        <v>1</v>
+        <v>0.733243641135974</v>
       </c>
       <c r="L88">
-        <v>1</v>
+        <v>0.733243641135974</v>
       </c>
       <c r="M88">
-        <v>1</v>
+        <v>0.733243641135974</v>
       </c>
       <c r="N88">
-        <v>1</v>
+        <v>0.733243641135974</v>
       </c>
       <c r="O88">
-        <v>1</v>
+        <v>0.733243641135974</v>
       </c>
       <c r="P88">
-        <v>1</v>
+        <v>0.733243641135974</v>
       </c>
       <c r="Q88">
-        <v>1</v>
+        <v>0.733243641135974</v>
       </c>
       <c r="R88">
-        <v>1</v>
+        <v>0.733243641135974</v>
       </c>
       <c r="S88">
-        <v>1</v>
+        <v>0.733243641135974</v>
       </c>
       <c r="T88">
-        <v>1</v>
+        <v>0.733243641135974</v>
       </c>
       <c r="U88">
-        <v>1</v>
+        <v>0.733243641135974</v>
       </c>
       <c r="V88">
-        <v>1</v>
+        <v>0.733243641135974</v>
       </c>
       <c r="W88">
-        <v>1</v>
+        <v>0.733243641135974</v>
       </c>
       <c r="X88">
-        <v>1</v>
+        <v>0.733243641135974</v>
       </c>
       <c r="Y88">
-        <v>1</v>
+        <v>0.733243641135974</v>
       </c>
       <c r="Z88">
-        <v>1</v>
+        <v>0.733243641135974</v>
       </c>
       <c r="AA88">
-        <v>1</v>
+        <v>0.733243641135974</v>
       </c>
       <c r="AB88">
-        <v>1</v>
+        <v>0.733243641135974</v>
       </c>
       <c r="AC88">
-        <v>1</v>
+        <v>0.733243641135974</v>
       </c>
       <c r="AD88">
-        <v>1</v>
+        <v>0.733243641135974</v>
       </c>
       <c r="AE88">
-        <v>1</v>
+        <v>0.733243641135974</v>
       </c>
       <c r="AF88">
-        <v>1</v>
+        <v>0.733243641135974</v>
       </c>
       <c r="AG88">
-        <v>1</v>
+        <v>0.733243641135974</v>
       </c>
       <c r="AH88">
-        <v>1</v>
+        <v>0.733243641135974</v>
       </c>
       <c r="AI88">
-        <v>1</v>
+        <v>0.733243641135974</v>
       </c>
       <c r="AJ88">
-        <v>1</v>
+        <v>0.733243641135974</v>
       </c>
       <c r="AK88">
-        <v>1</v>
+        <v>0.733243641135974</v>
       </c>
       <c r="AL88">
-        <v>1</v>
+        <v>0.733243641135974</v>
       </c>
       <c r="AM88">
-        <v>1</v>
+        <v>0.733243641135974</v>
       </c>
       <c r="AN88">
-        <v>1</v>
+        <v>0.733243641135974</v>
       </c>
       <c r="AO88">
-        <v>1</v>
+        <v>0.733243641135974</v>
       </c>
       <c r="AP88">
-        <v>1</v>
+        <v>0.733243641135974</v>
       </c>
       <c r="AQ88">
-        <v>1</v>
+        <v>0.733243641135974</v>
       </c>
       <c r="AR88">
-        <v>1</v>
+        <v>0.733243641135974</v>
       </c>
       <c r="AS88">
-        <v>1</v>
+        <v>0.733243641135974</v>
       </c>
     </row>
     <row r="89" spans="1:45">
@@ -11858,112 +11858,112 @@
         <v>1</v>
       </c>
       <c r="J89">
-        <v>0.03741</v>
+        <v>0.0274306446148967</v>
       </c>
       <c r="K89">
-        <v>0.03741</v>
+        <v>0.0274306446148967</v>
       </c>
       <c r="L89">
-        <v>0.03741</v>
+        <v>0.0274306446148967</v>
       </c>
       <c r="M89">
-        <v>0.03741</v>
+        <v>0.0274306446148967</v>
       </c>
       <c r="N89">
-        <v>0.03741</v>
+        <v>0.0274306446148967</v>
       </c>
       <c r="O89">
-        <v>0.03741</v>
+        <v>0.0274306446148967</v>
       </c>
       <c r="P89">
-        <v>0.03741</v>
+        <v>0.0274306446148967</v>
       </c>
       <c r="Q89">
-        <v>0.03741</v>
+        <v>0.0274306446148967</v>
       </c>
       <c r="R89">
-        <v>0.03741</v>
+        <v>0.0274306446148967</v>
       </c>
       <c r="S89">
-        <v>0.03741</v>
+        <v>0.0274306446148967</v>
       </c>
       <c r="T89">
-        <v>0.03741</v>
+        <v>0.0274306446148967</v>
       </c>
       <c r="U89">
-        <v>0.03741</v>
+        <v>0.0274306446148967</v>
       </c>
       <c r="V89">
-        <v>0.03741</v>
+        <v>0.0274306446148967</v>
       </c>
       <c r="W89">
-        <v>0.03741</v>
+        <v>0.0274306446148967</v>
       </c>
       <c r="X89">
-        <v>0.03741</v>
+        <v>0.0274306446148967</v>
       </c>
       <c r="Y89">
-        <v>0.03741</v>
+        <v>0.0274306446148967</v>
       </c>
       <c r="Z89">
-        <v>0.03741</v>
+        <v>0.0274306446148967</v>
       </c>
       <c r="AA89">
-        <v>0.03741</v>
+        <v>0.0274306446148967</v>
       </c>
       <c r="AB89">
-        <v>0.03741</v>
+        <v>0.0274306446148967</v>
       </c>
       <c r="AC89">
-        <v>0.03741</v>
+        <v>0.0274306446148967</v>
       </c>
       <c r="AD89">
-        <v>0.03741</v>
+        <v>0.0274306446148967</v>
       </c>
       <c r="AE89">
-        <v>0.03741</v>
+        <v>0.0274306446148967</v>
       </c>
       <c r="AF89">
-        <v>0.03741</v>
+        <v>0.0274306446148967</v>
       </c>
       <c r="AG89">
-        <v>0.03741</v>
+        <v>0.0274306446148967</v>
       </c>
       <c r="AH89">
-        <v>0.03741</v>
+        <v>0.0274306446148967</v>
       </c>
       <c r="AI89">
-        <v>0.03741</v>
+        <v>0.0274306446148967</v>
       </c>
       <c r="AJ89">
-        <v>0.03741</v>
+        <v>0.0274306446148967</v>
       </c>
       <c r="AK89">
-        <v>0.03741</v>
+        <v>0.0274306446148967</v>
       </c>
       <c r="AL89">
-        <v>0.03741</v>
+        <v>0.0274306446148967</v>
       </c>
       <c r="AM89">
-        <v>0.03741</v>
+        <v>0.0274306446148967</v>
       </c>
       <c r="AN89">
-        <v>0.03741</v>
+        <v>0.0274306446148967</v>
       </c>
       <c r="AO89">
-        <v>0.03741</v>
+        <v>0.0274306446148967</v>
       </c>
       <c r="AP89">
-        <v>0.03741</v>
+        <v>0.0274306446148967</v>
       </c>
       <c r="AQ89">
-        <v>0.03741</v>
+        <v>0.0274306446148967</v>
       </c>
       <c r="AR89">
-        <v>0.03741</v>
+        <v>0.0274306446148967</v>
       </c>
       <c r="AS89">
-        <v>0.03741</v>
+        <v>0.0274306446148967</v>
       </c>
     </row>
     <row r="90" spans="1:45">
@@ -11983,112 +11983,112 @@
         <v>1</v>
       </c>
       <c r="J90">
-        <v>0.0007</v>
+        <v>0.0005132705487951</v>
       </c>
       <c r="K90">
-        <v>0.0007</v>
+        <v>0.0005132705487951</v>
       </c>
       <c r="L90">
-        <v>0.0007</v>
+        <v>0.0005132705487951</v>
       </c>
       <c r="M90">
-        <v>0.0007</v>
+        <v>0.0005132705487951</v>
       </c>
       <c r="N90">
-        <v>0.0007</v>
+        <v>0.0005132705487951</v>
       </c>
       <c r="O90">
-        <v>0.0007</v>
+        <v>0.0005132705487951</v>
       </c>
       <c r="P90">
-        <v>0.0007</v>
+        <v>0.0005132705487951</v>
       </c>
       <c r="Q90">
-        <v>0.0007</v>
+        <v>0.0005132705487951</v>
       </c>
       <c r="R90">
-        <v>0.0007</v>
+        <v>0.0005132705487951</v>
       </c>
       <c r="S90">
-        <v>0.0007</v>
+        <v>0.0005132705487951</v>
       </c>
       <c r="T90">
-        <v>0.0007</v>
+        <v>0.0005132705487951</v>
       </c>
       <c r="U90">
-        <v>0.0007</v>
+        <v>0.0005132705487951</v>
       </c>
       <c r="V90">
-        <v>0.0007</v>
+        <v>0.0005132705487951</v>
       </c>
       <c r="W90">
-        <v>0.0007</v>
+        <v>0.0005132705487951</v>
       </c>
       <c r="X90">
-        <v>0.0007</v>
+        <v>0.0005132705487951</v>
       </c>
       <c r="Y90">
-        <v>0.0007</v>
+        <v>0.0005132705487951</v>
       </c>
       <c r="Z90">
-        <v>0.0007</v>
+        <v>0.0005132705487951</v>
       </c>
       <c r="AA90">
-        <v>0.0007</v>
+        <v>0.0005132705487951</v>
       </c>
       <c r="AB90">
-        <v>0.0007</v>
+        <v>0.0005132705487951</v>
       </c>
       <c r="AC90">
-        <v>0.0007</v>
+        <v>0.0005132705487951</v>
       </c>
       <c r="AD90">
-        <v>0.0007</v>
+        <v>0.0005132705487951</v>
       </c>
       <c r="AE90">
-        <v>0.0007</v>
+        <v>0.0005132705487951</v>
       </c>
       <c r="AF90">
-        <v>0.0007</v>
+        <v>0.0005132705487951</v>
       </c>
       <c r="AG90">
-        <v>0.0007</v>
+        <v>0.0005132705487951</v>
       </c>
       <c r="AH90">
-        <v>0.0007</v>
+        <v>0.0005132705487951</v>
       </c>
       <c r="AI90">
-        <v>0.0007</v>
+        <v>0.0005132705487951</v>
       </c>
       <c r="AJ90">
-        <v>0.0007</v>
+        <v>0.0005132705487951</v>
       </c>
       <c r="AK90">
-        <v>0.0007</v>
+        <v>0.0005132705487951</v>
       </c>
       <c r="AL90">
-        <v>0.0007</v>
+        <v>0.0005132705487951</v>
       </c>
       <c r="AM90">
-        <v>0.0007</v>
+        <v>0.0005132705487951</v>
       </c>
       <c r="AN90">
-        <v>0.0007</v>
+        <v>0.0005132705487951</v>
       </c>
       <c r="AO90">
-        <v>0.0007</v>
+        <v>0.0005132705487951</v>
       </c>
       <c r="AP90">
-        <v>0.0007</v>
+        <v>0.0005132705487951</v>
       </c>
       <c r="AQ90">
-        <v>0.0007</v>
+        <v>0.0005132705487951</v>
       </c>
       <c r="AR90">
-        <v>0.0007</v>
+        <v>0.0005132705487951</v>
       </c>
       <c r="AS90">
-        <v>0.0007</v>
+        <v>0.0005132705487951</v>
       </c>
     </row>
     <row r="91" spans="1:45">
@@ -12846,112 +12846,112 @@
         <v>1</v>
       </c>
       <c r="J97">
-        <v>0.056947488</v>
+        <v>0.0574027036298953</v>
       </c>
       <c r="K97">
-        <v>0.056947488</v>
+        <v>0.0574027036298953</v>
       </c>
       <c r="L97">
-        <v>0.056947488</v>
+        <v>0.0574027036298953</v>
       </c>
       <c r="M97">
-        <v>0.056947488</v>
+        <v>0.0574027036298953</v>
       </c>
       <c r="N97">
-        <v>0.056947488</v>
+        <v>0.0574027036298953</v>
       </c>
       <c r="O97">
-        <v>0.056947488</v>
+        <v>0.0574027036298953</v>
       </c>
       <c r="P97">
-        <v>0.056947488</v>
+        <v>0.0574027036298953</v>
       </c>
       <c r="Q97">
-        <v>0.056947488</v>
+        <v>0.0574027036298953</v>
       </c>
       <c r="R97">
-        <v>0.056947488</v>
+        <v>0.0574027036298953</v>
       </c>
       <c r="S97">
-        <v>0.056947488</v>
+        <v>0.0574027036298953</v>
       </c>
       <c r="T97">
-        <v>0.056947488</v>
+        <v>0.0574027036298953</v>
       </c>
       <c r="U97">
-        <v>0.056947488</v>
+        <v>0.0574027036298953</v>
       </c>
       <c r="V97">
-        <v>0.056947488</v>
+        <v>0.0574027036298953</v>
       </c>
       <c r="W97">
-        <v>0.056947488</v>
+        <v>0.0574027036298953</v>
       </c>
       <c r="X97">
-        <v>0.056947488</v>
+        <v>0.0574027036298953</v>
       </c>
       <c r="Y97">
-        <v>0.056947488</v>
+        <v>0.0574027036298953</v>
       </c>
       <c r="Z97">
-        <v>0.056947488</v>
+        <v>0.0574027036298953</v>
       </c>
       <c r="AA97">
-        <v>0.056947488</v>
+        <v>0.0574027036298953</v>
       </c>
       <c r="AB97">
-        <v>0.056947488</v>
+        <v>0.0574027036298953</v>
       </c>
       <c r="AC97">
-        <v>0.056947488</v>
+        <v>0.0574027036298953</v>
       </c>
       <c r="AD97">
-        <v>0.056947488</v>
+        <v>0.0574027036298953</v>
       </c>
       <c r="AE97">
-        <v>0.056947488</v>
+        <v>0.0574027036298953</v>
       </c>
       <c r="AF97">
-        <v>0.056947488</v>
+        <v>0.0574027036298953</v>
       </c>
       <c r="AG97">
-        <v>0.056947488</v>
+        <v>0.0574027036298953</v>
       </c>
       <c r="AH97">
-        <v>0.056947488</v>
+        <v>0.0574027036298953</v>
       </c>
       <c r="AI97">
-        <v>0.056947488</v>
+        <v>0.0574027036298953</v>
       </c>
       <c r="AJ97">
-        <v>0.056947488</v>
+        <v>0.0574027036298953</v>
       </c>
       <c r="AK97">
-        <v>0.056947488</v>
+        <v>0.0574027036298953</v>
       </c>
       <c r="AL97">
-        <v>0.056947488</v>
+        <v>0.0574027036298953</v>
       </c>
       <c r="AM97">
-        <v>0.056947488</v>
+        <v>0.0574027036298953</v>
       </c>
       <c r="AN97">
-        <v>0.056947488</v>
+        <v>0.0574027036298953</v>
       </c>
       <c r="AO97">
-        <v>0.056947488</v>
+        <v>0.0574027036298953</v>
       </c>
       <c r="AP97">
-        <v>0.056947488</v>
+        <v>0.0574027036298953</v>
       </c>
       <c r="AQ97">
-        <v>0.056947488</v>
+        <v>0.0574027036298953</v>
       </c>
       <c r="AR97">
-        <v>0.056947488</v>
+        <v>0.0574027036298953</v>
       </c>
       <c r="AS97">
-        <v>0.056947488</v>
+        <v>0.0574027036298953</v>
       </c>
     </row>
     <row r="98" spans="1:45">
@@ -12968,112 +12968,112 @@
         <v>1</v>
       </c>
       <c r="J98">
-        <v>0.109927729</v>
+        <v>0.1030926584509633</v>
       </c>
       <c r="K98">
-        <v>0.109927729</v>
+        <v>0.1030926584509633</v>
       </c>
       <c r="L98">
-        <v>0.109927729</v>
+        <v>0.1030926584509633</v>
       </c>
       <c r="M98">
-        <v>0.109927729</v>
+        <v>0.1030926584509633</v>
       </c>
       <c r="N98">
-        <v>0.109927729</v>
+        <v>0.1030926584509633</v>
       </c>
       <c r="O98">
-        <v>0.109927729</v>
+        <v>0.1030926584509633</v>
       </c>
       <c r="P98">
-        <v>0.109927729</v>
+        <v>0.1030926584509633</v>
       </c>
       <c r="Q98">
-        <v>0.109927729</v>
+        <v>0.1030926584509633</v>
       </c>
       <c r="R98">
-        <v>0.109927729</v>
+        <v>0.1030926584509633</v>
       </c>
       <c r="S98">
-        <v>0.109927729</v>
+        <v>0.1030926584509633</v>
       </c>
       <c r="T98">
-        <v>0.109927729</v>
+        <v>0.1030926584509633</v>
       </c>
       <c r="U98">
-        <v>0.109927729</v>
+        <v>0.1030926584509633</v>
       </c>
       <c r="V98">
-        <v>0.109927729</v>
+        <v>0.1030926584509633</v>
       </c>
       <c r="W98">
-        <v>0.109927729</v>
+        <v>0.1030926584509633</v>
       </c>
       <c r="X98">
-        <v>0.109927729</v>
+        <v>0.1030926584509633</v>
       </c>
       <c r="Y98">
-        <v>0.109927729</v>
+        <v>0.1030926584509633</v>
       </c>
       <c r="Z98">
-        <v>0.109927729</v>
+        <v>0.1030926584509633</v>
       </c>
       <c r="AA98">
-        <v>0.109927729</v>
+        <v>0.1030926584509633</v>
       </c>
       <c r="AB98">
-        <v>0.109927729</v>
+        <v>0.1030926584509633</v>
       </c>
       <c r="AC98">
-        <v>0.109927729</v>
+        <v>0.1030926584509633</v>
       </c>
       <c r="AD98">
-        <v>0.109927729</v>
+        <v>0.1030926584509633</v>
       </c>
       <c r="AE98">
-        <v>0.109927729</v>
+        <v>0.1030926584509633</v>
       </c>
       <c r="AF98">
-        <v>0.109927729</v>
+        <v>0.1030926584509633</v>
       </c>
       <c r="AG98">
-        <v>0.109927729</v>
+        <v>0.1030926584509633</v>
       </c>
       <c r="AH98">
-        <v>0.109927729</v>
+        <v>0.1030926584509633</v>
       </c>
       <c r="AI98">
-        <v>0.109927729</v>
+        <v>0.1030926584509633</v>
       </c>
       <c r="AJ98">
-        <v>0.109927729</v>
+        <v>0.1030926584509633</v>
       </c>
       <c r="AK98">
-        <v>0.109927729</v>
+        <v>0.1030926584509633</v>
       </c>
       <c r="AL98">
-        <v>0.109927729</v>
+        <v>0.1030926584509633</v>
       </c>
       <c r="AM98">
-        <v>0.109927729</v>
+        <v>0.1030926584509633</v>
       </c>
       <c r="AN98">
-        <v>0.109927729</v>
+        <v>0.1030926584509633</v>
       </c>
       <c r="AO98">
-        <v>0.109927729</v>
+        <v>0.1030926584509633</v>
       </c>
       <c r="AP98">
-        <v>0.109927729</v>
+        <v>0.1030926584509633</v>
       </c>
       <c r="AQ98">
-        <v>0.109927729</v>
+        <v>0.1030926584509633</v>
       </c>
       <c r="AR98">
-        <v>0.109927729</v>
+        <v>0.1030926584509633</v>
       </c>
       <c r="AS98">
-        <v>0.109927729</v>
+        <v>0.1030926584509633</v>
       </c>
     </row>
     <row r="99" spans="1:45">
@@ -13090,112 +13090,112 @@
         <v>1</v>
       </c>
       <c r="J99">
-        <v>0.046761621</v>
+        <v>0.06654342362501869</v>
       </c>
       <c r="K99">
-        <v>0.046761621</v>
+        <v>0.06654342362501869</v>
       </c>
       <c r="L99">
-        <v>0.046761621</v>
+        <v>0.06654342362501869</v>
       </c>
       <c r="M99">
-        <v>0.046761621</v>
+        <v>0.06654342362501869</v>
       </c>
       <c r="N99">
-        <v>0.046761621</v>
+        <v>0.06654342362501869</v>
       </c>
       <c r="O99">
-        <v>0.046761621</v>
+        <v>0.06654342362501869</v>
       </c>
       <c r="P99">
-        <v>0.046761621</v>
+        <v>0.06654342362501869</v>
       </c>
       <c r="Q99">
-        <v>0.046761621</v>
+        <v>0.06654342362501869</v>
       </c>
       <c r="R99">
-        <v>0.046761621</v>
+        <v>0.06654342362501869</v>
       </c>
       <c r="S99">
-        <v>0.046761621</v>
+        <v>0.06654342362501869</v>
       </c>
       <c r="T99">
-        <v>0.046761621</v>
+        <v>0.06654342362501869</v>
       </c>
       <c r="U99">
-        <v>0.046761621</v>
+        <v>0.06654342362501869</v>
       </c>
       <c r="V99">
-        <v>0.046761621</v>
+        <v>0.06654342362501869</v>
       </c>
       <c r="W99">
-        <v>0.046761621</v>
+        <v>0.06654342362501869</v>
       </c>
       <c r="X99">
-        <v>0.046761621</v>
+        <v>0.06654342362501869</v>
       </c>
       <c r="Y99">
-        <v>0.046761621</v>
+        <v>0.06654342362501869</v>
       </c>
       <c r="Z99">
-        <v>0.046761621</v>
+        <v>0.06654342362501869</v>
       </c>
       <c r="AA99">
-        <v>0.046761621</v>
+        <v>0.06654342362501869</v>
       </c>
       <c r="AB99">
-        <v>0.046761621</v>
+        <v>0.06654342362501869</v>
       </c>
       <c r="AC99">
-        <v>0.046761621</v>
+        <v>0.06654342362501869</v>
       </c>
       <c r="AD99">
-        <v>0.046761621</v>
+        <v>0.06654342362501869</v>
       </c>
       <c r="AE99">
-        <v>0.046761621</v>
+        <v>0.06654342362501869</v>
       </c>
       <c r="AF99">
-        <v>0.046761621</v>
+        <v>0.06654342362501869</v>
       </c>
       <c r="AG99">
-        <v>0.046761621</v>
+        <v>0.06654342362501869</v>
       </c>
       <c r="AH99">
-        <v>0.046761621</v>
+        <v>0.06654342362501869</v>
       </c>
       <c r="AI99">
-        <v>0.046761621</v>
+        <v>0.06654342362501869</v>
       </c>
       <c r="AJ99">
-        <v>0.046761621</v>
+        <v>0.06654342362501869</v>
       </c>
       <c r="AK99">
-        <v>0.046761621</v>
+        <v>0.06654342362501869</v>
       </c>
       <c r="AL99">
-        <v>0.046761621</v>
+        <v>0.06654342362501869</v>
       </c>
       <c r="AM99">
-        <v>0.046761621</v>
+        <v>0.06654342362501869</v>
       </c>
       <c r="AN99">
-        <v>0.046761621</v>
+        <v>0.06654342362501869</v>
       </c>
       <c r="AO99">
-        <v>0.046761621</v>
+        <v>0.06654342362501869</v>
       </c>
       <c r="AP99">
-        <v>0.046761621</v>
+        <v>0.06654342362501869</v>
       </c>
       <c r="AQ99">
-        <v>0.046761621</v>
+        <v>0.06654342362501869</v>
       </c>
       <c r="AR99">
-        <v>0.046761621</v>
+        <v>0.06654342362501869</v>
       </c>
       <c r="AS99">
-        <v>0.046761621</v>
+        <v>0.06654342362501869</v>
       </c>
     </row>
     <row r="100" spans="1:45">
@@ -13212,112 +13212,112 @@
         <v>1</v>
       </c>
       <c r="J100">
-        <v>0.040684382</v>
+        <v>0.0370019284421274</v>
       </c>
       <c r="K100">
-        <v>0.040684382</v>
+        <v>0.0370019284421274</v>
       </c>
       <c r="L100">
-        <v>0.040684382</v>
+        <v>0.0370019284421274</v>
       </c>
       <c r="M100">
-        <v>0.040684382</v>
+        <v>0.0370019284421274</v>
       </c>
       <c r="N100">
-        <v>0.040684382</v>
+        <v>0.0370019284421274</v>
       </c>
       <c r="O100">
-        <v>0.040684382</v>
+        <v>0.0370019284421274</v>
       </c>
       <c r="P100">
-        <v>0.040684382</v>
+        <v>0.0370019284421274</v>
       </c>
       <c r="Q100">
-        <v>0.040684382</v>
+        <v>0.0370019284421274</v>
       </c>
       <c r="R100">
-        <v>0.040684382</v>
+        <v>0.0370019284421274</v>
       </c>
       <c r="S100">
-        <v>0.040684382</v>
+        <v>0.0370019284421274</v>
       </c>
       <c r="T100">
-        <v>0.040684382</v>
+        <v>0.0370019284421274</v>
       </c>
       <c r="U100">
-        <v>0.040684382</v>
+        <v>0.0370019284421274</v>
       </c>
       <c r="V100">
-        <v>0.040684382</v>
+        <v>0.0370019284421274</v>
       </c>
       <c r="W100">
-        <v>0.040684382</v>
+        <v>0.0370019284421274</v>
       </c>
       <c r="X100">
-        <v>0.040684382</v>
+        <v>0.0370019284421274</v>
       </c>
       <c r="Y100">
-        <v>0.040684382</v>
+        <v>0.0370019284421274</v>
       </c>
       <c r="Z100">
-        <v>0.040684382</v>
+        <v>0.0370019284421274</v>
       </c>
       <c r="AA100">
-        <v>0.040684382</v>
+        <v>0.0370019284421274</v>
       </c>
       <c r="AB100">
-        <v>0.040684382</v>
+        <v>0.0370019284421274</v>
       </c>
       <c r="AC100">
-        <v>0.040684382</v>
+        <v>0.0370019284421274</v>
       </c>
       <c r="AD100">
-        <v>0.040684382</v>
+        <v>0.0370019284421274</v>
       </c>
       <c r="AE100">
-        <v>0.040684382</v>
+        <v>0.0370019284421274</v>
       </c>
       <c r="AF100">
-        <v>0.040684382</v>
+        <v>0.0370019284421274</v>
       </c>
       <c r="AG100">
-        <v>0.040684382</v>
+        <v>0.0370019284421274</v>
       </c>
       <c r="AH100">
-        <v>0.040684382</v>
+        <v>0.0370019284421274</v>
       </c>
       <c r="AI100">
-        <v>0.040684382</v>
+        <v>0.0370019284421274</v>
       </c>
       <c r="AJ100">
-        <v>0.040684382</v>
+        <v>0.0370019284421274</v>
       </c>
       <c r="AK100">
-        <v>0.040684382</v>
+        <v>0.0370019284421274</v>
       </c>
       <c r="AL100">
-        <v>0.040684382</v>
+        <v>0.0370019284421274</v>
       </c>
       <c r="AM100">
-        <v>0.040684382</v>
+        <v>0.0370019284421274</v>
       </c>
       <c r="AN100">
-        <v>0.040684382</v>
+        <v>0.0370019284421274</v>
       </c>
       <c r="AO100">
-        <v>0.040684382</v>
+        <v>0.0370019284421274</v>
       </c>
       <c r="AP100">
-        <v>0.040684382</v>
+        <v>0.0370019284421274</v>
       </c>
       <c r="AQ100">
-        <v>0.040684382</v>
+        <v>0.0370019284421274</v>
       </c>
       <c r="AR100">
-        <v>0.040684382</v>
+        <v>0.0370019284421274</v>
       </c>
       <c r="AS100">
-        <v>0.040684382</v>
+        <v>0.0370019284421274</v>
       </c>
     </row>
     <row r="101" spans="1:45">
@@ -13334,112 +13334,112 @@
         <v>1</v>
       </c>
       <c r="J101">
-        <v>0.024031253</v>
+        <v>0.0355904848617472</v>
       </c>
       <c r="K101">
-        <v>0.024031253</v>
+        <v>0.0355904848617472</v>
       </c>
       <c r="L101">
-        <v>0.024031253</v>
+        <v>0.0355904848617472</v>
       </c>
       <c r="M101">
-        <v>0.024031253</v>
+        <v>0.0355904848617472</v>
       </c>
       <c r="N101">
-        <v>0.024031253</v>
+        <v>0.0355904848617472</v>
       </c>
       <c r="O101">
-        <v>0.024031253</v>
+        <v>0.0355904848617472</v>
       </c>
       <c r="P101">
-        <v>0.024031253</v>
+        <v>0.0355904848617472</v>
       </c>
       <c r="Q101">
-        <v>0.024031253</v>
+        <v>0.0355904848617472</v>
       </c>
       <c r="R101">
-        <v>0.024031253</v>
+        <v>0.0355904848617472</v>
       </c>
       <c r="S101">
-        <v>0.024031253</v>
+        <v>0.0355904848617472</v>
       </c>
       <c r="T101">
-        <v>0.024031253</v>
+        <v>0.0355904848617472</v>
       </c>
       <c r="U101">
-        <v>0.024031253</v>
+        <v>0.0355904848617472</v>
       </c>
       <c r="V101">
-        <v>0.024031253</v>
+        <v>0.0355904848617472</v>
       </c>
       <c r="W101">
-        <v>0.024031253</v>
+        <v>0.0355904848617472</v>
       </c>
       <c r="X101">
-        <v>0.024031253</v>
+        <v>0.0355904848617472</v>
       </c>
       <c r="Y101">
-        <v>0.024031253</v>
+        <v>0.0355904848617472</v>
       </c>
       <c r="Z101">
-        <v>0.024031253</v>
+        <v>0.0355904848617472</v>
       </c>
       <c r="AA101">
-        <v>0.024031253</v>
+        <v>0.0355904848617472</v>
       </c>
       <c r="AB101">
-        <v>0.024031253</v>
+        <v>0.0355904848617472</v>
       </c>
       <c r="AC101">
-        <v>0.024031253</v>
+        <v>0.0355904848617472</v>
       </c>
       <c r="AD101">
-        <v>0.024031253</v>
+        <v>0.0355904848617472</v>
       </c>
       <c r="AE101">
-        <v>0.024031253</v>
+        <v>0.0355904848617472</v>
       </c>
       <c r="AF101">
-        <v>0.024031253</v>
+        <v>0.0355904848617472</v>
       </c>
       <c r="AG101">
-        <v>0.024031253</v>
+        <v>0.0355904848617472</v>
       </c>
       <c r="AH101">
-        <v>0.024031253</v>
+        <v>0.0355904848617472</v>
       </c>
       <c r="AI101">
-        <v>0.024031253</v>
+        <v>0.0355904848617472</v>
       </c>
       <c r="AJ101">
-        <v>0.024031253</v>
+        <v>0.0355904848617472</v>
       </c>
       <c r="AK101">
-        <v>0.024031253</v>
+        <v>0.0355904848617472</v>
       </c>
       <c r="AL101">
-        <v>0.024031253</v>
+        <v>0.0355904848617472</v>
       </c>
       <c r="AM101">
-        <v>0.024031253</v>
+        <v>0.0355904848617472</v>
       </c>
       <c r="AN101">
-        <v>0.024031253</v>
+        <v>0.0355904848617472</v>
       </c>
       <c r="AO101">
-        <v>0.024031253</v>
+        <v>0.0355904848617472</v>
       </c>
       <c r="AP101">
-        <v>0.024031253</v>
+        <v>0.0355904848617472</v>
       </c>
       <c r="AQ101">
-        <v>0.024031253</v>
+        <v>0.0355904848617472</v>
       </c>
       <c r="AR101">
-        <v>0.024031253</v>
+        <v>0.0355904848617472</v>
       </c>
       <c r="AS101">
-        <v>0.024031253</v>
+        <v>0.0355904848617472</v>
       </c>
     </row>
     <row r="102" spans="1:45">
@@ -13456,112 +13456,112 @@
         <v>1</v>
       </c>
       <c r="J102">
-        <v>0.046135175</v>
+        <v>0.0494351203362323</v>
       </c>
       <c r="K102">
-        <v>0.046135175</v>
+        <v>0.0494351203362323</v>
       </c>
       <c r="L102">
-        <v>0.046135175</v>
+        <v>0.0494351203362323</v>
       </c>
       <c r="M102">
-        <v>0.046135175</v>
+        <v>0.0494351203362323</v>
       </c>
       <c r="N102">
-        <v>0.046135175</v>
+        <v>0.0494351203362323</v>
       </c>
       <c r="O102">
-        <v>0.046135175</v>
+        <v>0.0494351203362323</v>
       </c>
       <c r="P102">
-        <v>0.046135175</v>
+        <v>0.0494351203362323</v>
       </c>
       <c r="Q102">
-        <v>0.046135175</v>
+        <v>0.0494351203362323</v>
       </c>
       <c r="R102">
-        <v>0.046135175</v>
+        <v>0.0494351203362323</v>
       </c>
       <c r="S102">
-        <v>0.046135175</v>
+        <v>0.0494351203362323</v>
       </c>
       <c r="T102">
-        <v>0.046135175</v>
+        <v>0.0494351203362323</v>
       </c>
       <c r="U102">
-        <v>0.046135175</v>
+        <v>0.0494351203362323</v>
       </c>
       <c r="V102">
-        <v>0.046135175</v>
+        <v>0.0494351203362323</v>
       </c>
       <c r="W102">
-        <v>0.046135175</v>
+        <v>0.0494351203362323</v>
       </c>
       <c r="X102">
-        <v>0.046135175</v>
+        <v>0.0494351203362323</v>
       </c>
       <c r="Y102">
-        <v>0.046135175</v>
+        <v>0.0494351203362323</v>
       </c>
       <c r="Z102">
-        <v>0.046135175</v>
+        <v>0.0494351203362323</v>
       </c>
       <c r="AA102">
-        <v>0.046135175</v>
+        <v>0.0494351203362323</v>
       </c>
       <c r="AB102">
-        <v>0.046135175</v>
+        <v>0.0494351203362323</v>
       </c>
       <c r="AC102">
-        <v>0.046135175</v>
+        <v>0.0494351203362323</v>
       </c>
       <c r="AD102">
-        <v>0.046135175</v>
+        <v>0.0494351203362323</v>
       </c>
       <c r="AE102">
-        <v>0.046135175</v>
+        <v>0.0494351203362323</v>
       </c>
       <c r="AF102">
-        <v>0.046135175</v>
+        <v>0.0494351203362323</v>
       </c>
       <c r="AG102">
-        <v>0.046135175</v>
+        <v>0.0494351203362323</v>
       </c>
       <c r="AH102">
-        <v>0.046135175</v>
+        <v>0.0494351203362323</v>
       </c>
       <c r="AI102">
-        <v>0.046135175</v>
+        <v>0.0494351203362323</v>
       </c>
       <c r="AJ102">
-        <v>0.046135175</v>
+        <v>0.0494351203362323</v>
       </c>
       <c r="AK102">
-        <v>0.046135175</v>
+        <v>0.0494351203362323</v>
       </c>
       <c r="AL102">
-        <v>0.046135175</v>
+        <v>0.0494351203362323</v>
       </c>
       <c r="AM102">
-        <v>0.046135175</v>
+        <v>0.0494351203362323</v>
       </c>
       <c r="AN102">
-        <v>0.046135175</v>
+        <v>0.0494351203362323</v>
       </c>
       <c r="AO102">
-        <v>0.046135175</v>
+        <v>0.0494351203362323</v>
       </c>
       <c r="AP102">
-        <v>0.046135175</v>
+        <v>0.0494351203362323</v>
       </c>
       <c r="AQ102">
-        <v>0.046135175</v>
+        <v>0.0494351203362323</v>
       </c>
       <c r="AR102">
-        <v>0.046135175</v>
+        <v>0.0494351203362323</v>
       </c>
       <c r="AS102">
-        <v>0.046135175</v>
+        <v>0.0494351203362323</v>
       </c>
     </row>
     <row r="103" spans="1:45">
@@ -13578,112 +13578,112 @@
         <v>1</v>
       </c>
       <c r="J103">
-        <v>0.5</v>
+        <v>0.5288481253571714</v>
       </c>
       <c r="K103">
-        <v>0.5</v>
+        <v>0.5288481253571714</v>
       </c>
       <c r="L103">
-        <v>0.5</v>
+        <v>0.5288481253571714</v>
       </c>
       <c r="M103">
-        <v>0.5</v>
+        <v>0.5288481253571714</v>
       </c>
       <c r="N103">
-        <v>0.5</v>
+        <v>0.5288481253571714</v>
       </c>
       <c r="O103">
-        <v>0.5</v>
+        <v>0.5288481253571714</v>
       </c>
       <c r="P103">
-        <v>0.5</v>
+        <v>0.5288481253571714</v>
       </c>
       <c r="Q103">
-        <v>0.5</v>
+        <v>0.5288481253571714</v>
       </c>
       <c r="R103">
-        <v>0.5</v>
+        <v>0.5288481253571714</v>
       </c>
       <c r="S103">
-        <v>0.5</v>
+        <v>0.5288481253571714</v>
       </c>
       <c r="T103">
-        <v>0.5</v>
+        <v>0.5288481253571714</v>
       </c>
       <c r="U103">
-        <v>0.5</v>
+        <v>0.5288481253571714</v>
       </c>
       <c r="V103">
-        <v>0.5</v>
+        <v>0.5288481253571714</v>
       </c>
       <c r="W103">
-        <v>0.5</v>
+        <v>0.5288481253571714</v>
       </c>
       <c r="X103">
-        <v>0.5</v>
+        <v>0.5288481253571714</v>
       </c>
       <c r="Y103">
-        <v>0.5</v>
+        <v>0.5288481253571714</v>
       </c>
       <c r="Z103">
-        <v>0.5</v>
+        <v>0.5288481253571714</v>
       </c>
       <c r="AA103">
-        <v>0.5</v>
+        <v>0.5288481253571714</v>
       </c>
       <c r="AB103">
-        <v>0.5</v>
+        <v>0.5288481253571714</v>
       </c>
       <c r="AC103">
-        <v>0.5</v>
+        <v>0.5288481253571714</v>
       </c>
       <c r="AD103">
-        <v>0.5</v>
+        <v>0.5288481253571714</v>
       </c>
       <c r="AE103">
-        <v>0.5</v>
+        <v>0.5288481253571714</v>
       </c>
       <c r="AF103">
-        <v>0.5</v>
+        <v>0.5288481253571714</v>
       </c>
       <c r="AG103">
-        <v>0.5</v>
+        <v>0.5288481253571714</v>
       </c>
       <c r="AH103">
-        <v>0.5</v>
+        <v>0.5288481253571714</v>
       </c>
       <c r="AI103">
-        <v>0.5</v>
+        <v>0.5288481253571714</v>
       </c>
       <c r="AJ103">
-        <v>0.5</v>
+        <v>0.5288481253571714</v>
       </c>
       <c r="AK103">
-        <v>0.5</v>
+        <v>0.5288481253571714</v>
       </c>
       <c r="AL103">
-        <v>0.5</v>
+        <v>0.5288481253571714</v>
       </c>
       <c r="AM103">
-        <v>0.5</v>
+        <v>0.5288481253571714</v>
       </c>
       <c r="AN103">
-        <v>0.5</v>
+        <v>0.5288481253571714</v>
       </c>
       <c r="AO103">
-        <v>0.5</v>
+        <v>0.5288481253571714</v>
       </c>
       <c r="AP103">
-        <v>0.5</v>
+        <v>0.5288481253571714</v>
       </c>
       <c r="AQ103">
-        <v>0.5</v>
+        <v>0.5288481253571714</v>
       </c>
       <c r="AR103">
-        <v>0.5</v>
+        <v>0.5288481253571714</v>
       </c>
       <c r="AS103">
-        <v>0.5</v>
+        <v>0.5288481253571714</v>
       </c>
     </row>
     <row r="104" spans="1:45">
@@ -13700,112 +13700,112 @@
         <v>1</v>
       </c>
       <c r="J104">
-        <v>0.105163772</v>
+        <v>0.1179700383169837</v>
       </c>
       <c r="K104">
-        <v>0.105163772</v>
+        <v>0.1179700383169837</v>
       </c>
       <c r="L104">
-        <v>0.105163772</v>
+        <v>0.1179700383169837</v>
       </c>
       <c r="M104">
-        <v>0.105163772</v>
+        <v>0.1179700383169837</v>
       </c>
       <c r="N104">
-        <v>0.105163772</v>
+        <v>0.1179700383169837</v>
       </c>
       <c r="O104">
-        <v>0.105163772</v>
+        <v>0.1179700383169837</v>
       </c>
       <c r="P104">
-        <v>0.105163772</v>
+        <v>0.1179700383169837</v>
       </c>
       <c r="Q104">
-        <v>0.105163772</v>
+        <v>0.1179700383169837</v>
       </c>
       <c r="R104">
-        <v>0.105163772</v>
+        <v>0.1179700383169837</v>
       </c>
       <c r="S104">
-        <v>0.105163772</v>
+        <v>0.1179700383169837</v>
       </c>
       <c r="T104">
-        <v>0.105163772</v>
+        <v>0.1179700383169837</v>
       </c>
       <c r="U104">
-        <v>0.105163772</v>
+        <v>0.1179700383169837</v>
       </c>
       <c r="V104">
-        <v>0.105163772</v>
+        <v>0.1179700383169837</v>
       </c>
       <c r="W104">
-        <v>0.105163772</v>
+        <v>0.1179700383169837</v>
       </c>
       <c r="X104">
-        <v>0.105163772</v>
+        <v>0.1179700383169837</v>
       </c>
       <c r="Y104">
-        <v>0.105163772</v>
+        <v>0.1179700383169837</v>
       </c>
       <c r="Z104">
-        <v>0.105163772</v>
+        <v>0.1179700383169837</v>
       </c>
       <c r="AA104">
-        <v>0.105163772</v>
+        <v>0.1179700383169837</v>
       </c>
       <c r="AB104">
-        <v>0.105163772</v>
+        <v>0.1179700383169837</v>
       </c>
       <c r="AC104">
-        <v>0.105163772</v>
+        <v>0.1179700383169837</v>
       </c>
       <c r="AD104">
-        <v>0.105163772</v>
+        <v>0.1179700383169837</v>
       </c>
       <c r="AE104">
-        <v>0.105163772</v>
+        <v>0.1179700383169837</v>
       </c>
       <c r="AF104">
-        <v>0.105163772</v>
+        <v>0.1179700383169837</v>
       </c>
       <c r="AG104">
-        <v>0.105163772</v>
+        <v>0.1179700383169837</v>
       </c>
       <c r="AH104">
-        <v>0.105163772</v>
+        <v>0.1179700383169837</v>
       </c>
       <c r="AI104">
-        <v>0.105163772</v>
+        <v>0.1179700383169837</v>
       </c>
       <c r="AJ104">
-        <v>0.105163772</v>
+        <v>0.1179700383169837</v>
       </c>
       <c r="AK104">
-        <v>0.105163772</v>
+        <v>0.1179700383169837</v>
       </c>
       <c r="AL104">
-        <v>0.105163772</v>
+        <v>0.1179700383169837</v>
       </c>
       <c r="AM104">
-        <v>0.105163772</v>
+        <v>0.1179700383169837</v>
       </c>
       <c r="AN104">
-        <v>0.105163772</v>
+        <v>0.1179700383169837</v>
       </c>
       <c r="AO104">
-        <v>0.105163772</v>
+        <v>0.1179700383169837</v>
       </c>
       <c r="AP104">
-        <v>0.105163772</v>
+        <v>0.1179700383169837</v>
       </c>
       <c r="AQ104">
-        <v>0.105163772</v>
+        <v>0.1179700383169837</v>
       </c>
       <c r="AR104">
-        <v>0.105163772</v>
+        <v>0.1179700383169837</v>
       </c>
       <c r="AS104">
-        <v>0.105163772</v>
+        <v>0.1179700383169837</v>
       </c>
     </row>
     <row r="105" spans="1:45">
@@ -13822,112 +13822,112 @@
         <v>1</v>
       </c>
       <c r="J105">
-        <v>0.055121623</v>
+        <v>0.0512555863144109</v>
       </c>
       <c r="K105">
-        <v>0.055121623</v>
+        <v>0.0512555863144109</v>
       </c>
       <c r="L105">
-        <v>0.055121623</v>
+        <v>0.0512555863144109</v>
       </c>
       <c r="M105">
-        <v>0.055121623</v>
+        <v>0.0512555863144109</v>
       </c>
       <c r="N105">
-        <v>0.055121623</v>
+        <v>0.0512555863144109</v>
       </c>
       <c r="O105">
-        <v>0.055121623</v>
+        <v>0.0512555863144109</v>
       </c>
       <c r="P105">
-        <v>0.055121623</v>
+        <v>0.0512555863144109</v>
       </c>
       <c r="Q105">
-        <v>0.055121623</v>
+        <v>0.0512555863144109</v>
       </c>
       <c r="R105">
-        <v>0.055121623</v>
+        <v>0.0512555863144109</v>
       </c>
       <c r="S105">
-        <v>0.055121623</v>
+        <v>0.0512555863144109</v>
       </c>
       <c r="T105">
-        <v>0.055121623</v>
+        <v>0.0512555863144109</v>
       </c>
       <c r="U105">
-        <v>0.055121623</v>
+        <v>0.0512555863144109</v>
       </c>
       <c r="V105">
-        <v>0.055121623</v>
+        <v>0.0512555863144109</v>
       </c>
       <c r="W105">
-        <v>0.055121623</v>
+        <v>0.0512555863144109</v>
       </c>
       <c r="X105">
-        <v>0.055121623</v>
+        <v>0.0512555863144109</v>
       </c>
       <c r="Y105">
-        <v>0.055121623</v>
+        <v>0.0512555863144109</v>
       </c>
       <c r="Z105">
-        <v>0.055121623</v>
+        <v>0.0512555863144109</v>
       </c>
       <c r="AA105">
-        <v>0.055121623</v>
+        <v>0.0512555863144109</v>
       </c>
       <c r="AB105">
-        <v>0.055121623</v>
+        <v>0.0512555863144109</v>
       </c>
       <c r="AC105">
-        <v>0.055121623</v>
+        <v>0.0512555863144109</v>
       </c>
       <c r="AD105">
-        <v>0.055121623</v>
+        <v>0.0512555863144109</v>
       </c>
       <c r="AE105">
-        <v>0.055121623</v>
+        <v>0.0512555863144109</v>
       </c>
       <c r="AF105">
-        <v>0.055121623</v>
+        <v>0.0512555863144109</v>
       </c>
       <c r="AG105">
-        <v>0.055121623</v>
+        <v>0.0512555863144109</v>
       </c>
       <c r="AH105">
-        <v>0.055121623</v>
+        <v>0.0512555863144109</v>
       </c>
       <c r="AI105">
-        <v>0.055121623</v>
+        <v>0.0512555863144109</v>
       </c>
       <c r="AJ105">
-        <v>0.055121623</v>
+        <v>0.0512555863144109</v>
       </c>
       <c r="AK105">
-        <v>0.055121623</v>
+        <v>0.0512555863144109</v>
       </c>
       <c r="AL105">
-        <v>0.055121623</v>
+        <v>0.0512555863144109</v>
       </c>
       <c r="AM105">
-        <v>0.055121623</v>
+        <v>0.0512555863144109</v>
       </c>
       <c r="AN105">
-        <v>0.055121623</v>
+        <v>0.0512555863144109</v>
       </c>
       <c r="AO105">
-        <v>0.055121623</v>
+        <v>0.0512555863144109</v>
       </c>
       <c r="AP105">
-        <v>0.055121623</v>
+        <v>0.0512555863144109</v>
       </c>
       <c r="AQ105">
-        <v>0.055121623</v>
+        <v>0.0512555863144109</v>
       </c>
       <c r="AR105">
-        <v>0.055121623</v>
+        <v>0.0512555863144109</v>
       </c>
       <c r="AS105">
-        <v>0.055121623</v>
+        <v>0.0512555863144109</v>
       </c>
     </row>
     <row r="106" spans="1:45">
@@ -13944,112 +13944,112 @@
         <v>1</v>
       </c>
       <c r="J106">
-        <v>0.01</v>
+        <v>0.0093623697294671</v>
       </c>
       <c r="K106">
-        <v>0.01</v>
+        <v>0.0093623697294671</v>
       </c>
       <c r="L106">
-        <v>0.01</v>
+        <v>0.0093623697294671</v>
       </c>
       <c r="M106">
-        <v>0.01</v>
+        <v>0.0093623697294671</v>
       </c>
       <c r="N106">
-        <v>0.01</v>
+        <v>0.0093623697294671</v>
       </c>
       <c r="O106">
-        <v>0.01</v>
+        <v>0.0093623697294671</v>
       </c>
       <c r="P106">
-        <v>0.01</v>
+        <v>0.0093623697294671</v>
       </c>
       <c r="Q106">
-        <v>0.01</v>
+        <v>0.0093623697294671</v>
       </c>
       <c r="R106">
-        <v>0.01</v>
+        <v>0.0093623697294671</v>
       </c>
       <c r="S106">
-        <v>0.01</v>
+        <v>0.0093623697294671</v>
       </c>
       <c r="T106">
-        <v>0.01</v>
+        <v>0.0093623697294671</v>
       </c>
       <c r="U106">
-        <v>0.01</v>
+        <v>0.0093623697294671</v>
       </c>
       <c r="V106">
-        <v>0.01</v>
+        <v>0.0093623697294671</v>
       </c>
       <c r="W106">
-        <v>0.01</v>
+        <v>0.0093623697294671</v>
       </c>
       <c r="X106">
-        <v>0.01</v>
+        <v>0.0093623697294671</v>
       </c>
       <c r="Y106">
-        <v>0.01</v>
+        <v>0.0093623697294671</v>
       </c>
       <c r="Z106">
-        <v>0.01</v>
+        <v>0.0093623697294671</v>
       </c>
       <c r="AA106">
-        <v>0.01</v>
+        <v>0.0093623697294671</v>
       </c>
       <c r="AB106">
-        <v>0.01</v>
+        <v>0.0093623697294671</v>
       </c>
       <c r="AC106">
-        <v>0.01</v>
+        <v>0.0093623697294671</v>
       </c>
       <c r="AD106">
-        <v>0.01</v>
+        <v>0.0093623697294671</v>
       </c>
       <c r="AE106">
-        <v>0.01</v>
+        <v>0.0093623697294671</v>
       </c>
       <c r="AF106">
-        <v>0.01</v>
+        <v>0.0093623697294671</v>
       </c>
       <c r="AG106">
-        <v>0.01</v>
+        <v>0.0093623697294671</v>
       </c>
       <c r="AH106">
-        <v>0.01</v>
+        <v>0.0093623697294671</v>
       </c>
       <c r="AI106">
-        <v>0.01</v>
+        <v>0.0093623697294671</v>
       </c>
       <c r="AJ106">
-        <v>0.01</v>
+        <v>0.0093623697294671</v>
       </c>
       <c r="AK106">
-        <v>0.01</v>
+        <v>0.0093623697294671</v>
       </c>
       <c r="AL106">
-        <v>0.01</v>
+        <v>0.0093623697294671</v>
       </c>
       <c r="AM106">
-        <v>0.01</v>
+        <v>0.0093623697294671</v>
       </c>
       <c r="AN106">
-        <v>0.01</v>
+        <v>0.0093623697294671</v>
       </c>
       <c r="AO106">
-        <v>0.01</v>
+        <v>0.0093623697294671</v>
       </c>
       <c r="AP106">
-        <v>0.01</v>
+        <v>0.0093623697294671</v>
       </c>
       <c r="AQ106">
-        <v>0.01</v>
+        <v>0.0093623697294671</v>
       </c>
       <c r="AR106">
-        <v>0.01</v>
+        <v>0.0093623697294671</v>
       </c>
       <c r="AS106">
-        <v>0.01</v>
+        <v>0.0093623697294671</v>
       </c>
     </row>
     <row r="107" spans="1:45">
@@ -14066,112 +14066,112 @@
         <v>1</v>
       </c>
       <c r="J107">
-        <v>0.01</v>
+        <v>0.015</v>
       </c>
       <c r="K107">
-        <v>0.01</v>
+        <v>0.015</v>
       </c>
       <c r="L107">
-        <v>0.01</v>
+        <v>0.015</v>
       </c>
       <c r="M107">
-        <v>0.01</v>
+        <v>0.015</v>
       </c>
       <c r="N107">
-        <v>0.01</v>
+        <v>0.015</v>
       </c>
       <c r="O107">
-        <v>0.01</v>
+        <v>0.015</v>
       </c>
       <c r="P107">
-        <v>0.01</v>
+        <v>0.015</v>
       </c>
       <c r="Q107">
-        <v>0.01</v>
+        <v>0.015</v>
       </c>
       <c r="R107">
-        <v>0.01</v>
+        <v>0.015</v>
       </c>
       <c r="S107">
-        <v>0.01</v>
+        <v>0.015</v>
       </c>
       <c r="T107">
-        <v>0.01</v>
+        <v>0.015</v>
       </c>
       <c r="U107">
-        <v>0.01</v>
+        <v>0.015</v>
       </c>
       <c r="V107">
-        <v>0.01</v>
+        <v>0.015</v>
       </c>
       <c r="W107">
-        <v>0.01</v>
+        <v>0.015</v>
       </c>
       <c r="X107">
-        <v>0.01</v>
+        <v>0.015</v>
       </c>
       <c r="Y107">
-        <v>0.01</v>
+        <v>0.015</v>
       </c>
       <c r="Z107">
-        <v>0.01</v>
+        <v>0.015</v>
       </c>
       <c r="AA107">
-        <v>0.01</v>
+        <v>0.015</v>
       </c>
       <c r="AB107">
-        <v>0.01</v>
+        <v>0.015</v>
       </c>
       <c r="AC107">
-        <v>0.01</v>
+        <v>0.015</v>
       </c>
       <c r="AD107">
-        <v>0.01</v>
+        <v>0.015</v>
       </c>
       <c r="AE107">
-        <v>0.01</v>
+        <v>0.015</v>
       </c>
       <c r="AF107">
-        <v>0.01</v>
+        <v>0.015</v>
       </c>
       <c r="AG107">
-        <v>0.01</v>
+        <v>0.015</v>
       </c>
       <c r="AH107">
-        <v>0.01</v>
+        <v>0.015</v>
       </c>
       <c r="AI107">
-        <v>0.01</v>
+        <v>0.015</v>
       </c>
       <c r="AJ107">
-        <v>0.01</v>
+        <v>0.015</v>
       </c>
       <c r="AK107">
-        <v>0.01</v>
+        <v>0.015</v>
       </c>
       <c r="AL107">
-        <v>0.01</v>
+        <v>0.015</v>
       </c>
       <c r="AM107">
-        <v>0.01</v>
+        <v>0.015</v>
       </c>
       <c r="AN107">
-        <v>0.01</v>
+        <v>0.015</v>
       </c>
       <c r="AO107">
-        <v>0.01</v>
+        <v>0.015</v>
       </c>
       <c r="AP107">
-        <v>0.01</v>
+        <v>0.015</v>
       </c>
       <c r="AQ107">
-        <v>0.01</v>
+        <v>0.015</v>
       </c>
       <c r="AR107">
-        <v>0.01</v>
+        <v>0.015</v>
       </c>
       <c r="AS107">
-        <v>0.01</v>
+        <v>0.015</v>
       </c>
     </row>
     <row r="108" spans="1:45">
@@ -14188,112 +14188,112 @@
         <v>1</v>
       </c>
       <c r="J108">
-        <v>0.01</v>
+        <v>0.0073620670127825</v>
       </c>
       <c r="K108">
-        <v>0.01</v>
+        <v>0.0073620670127825</v>
       </c>
       <c r="L108">
-        <v>0.01</v>
+        <v>0.0073620670127825</v>
       </c>
       <c r="M108">
-        <v>0.01</v>
+        <v>0.0073620670127825</v>
       </c>
       <c r="N108">
-        <v>0.01</v>
+        <v>0.0073620670127825</v>
       </c>
       <c r="O108">
-        <v>0.01</v>
+        <v>0.0073620670127825</v>
       </c>
       <c r="P108">
-        <v>0.01</v>
+        <v>0.0073620670127825</v>
       </c>
       <c r="Q108">
-        <v>0.01</v>
+        <v>0.0073620670127825</v>
       </c>
       <c r="R108">
-        <v>0.01</v>
+        <v>0.0073620670127825</v>
       </c>
       <c r="S108">
-        <v>0.01</v>
+        <v>0.0073620670127825</v>
       </c>
       <c r="T108">
-        <v>0.01</v>
+        <v>0.0073620670127825</v>
       </c>
       <c r="U108">
-        <v>0.01</v>
+        <v>0.0073620670127825</v>
       </c>
       <c r="V108">
-        <v>0.01</v>
+        <v>0.0073620670127825</v>
       </c>
       <c r="W108">
-        <v>0.01</v>
+        <v>0.0073620670127825</v>
       </c>
       <c r="X108">
-        <v>0.01</v>
+        <v>0.0073620670127825</v>
       </c>
       <c r="Y108">
-        <v>0.01</v>
+        <v>0.0073620670127825</v>
       </c>
       <c r="Z108">
-        <v>0.01</v>
+        <v>0.0073620670127825</v>
       </c>
       <c r="AA108">
-        <v>0.01</v>
+        <v>0.0073620670127825</v>
       </c>
       <c r="AB108">
-        <v>0.01</v>
+        <v>0.0073620670127825</v>
       </c>
       <c r="AC108">
-        <v>0.01</v>
+        <v>0.0073620670127825</v>
       </c>
       <c r="AD108">
-        <v>0.01</v>
+        <v>0.0073620670127825</v>
       </c>
       <c r="AE108">
-        <v>0.01</v>
+        <v>0.0073620670127825</v>
       </c>
       <c r="AF108">
-        <v>0.01</v>
+        <v>0.0073620670127825</v>
       </c>
       <c r="AG108">
-        <v>0.01</v>
+        <v>0.0073620670127825</v>
       </c>
       <c r="AH108">
-        <v>0.01</v>
+        <v>0.0073620670127825</v>
       </c>
       <c r="AI108">
-        <v>0.01</v>
+        <v>0.0073620670127825</v>
       </c>
       <c r="AJ108">
-        <v>0.01</v>
+        <v>0.0073620670127825</v>
       </c>
       <c r="AK108">
-        <v>0.01</v>
+        <v>0.0073620670127825</v>
       </c>
       <c r="AL108">
-        <v>0.01</v>
+        <v>0.0073620670127825</v>
       </c>
       <c r="AM108">
-        <v>0.01</v>
+        <v>0.0073620670127825</v>
       </c>
       <c r="AN108">
-        <v>0.01</v>
+        <v>0.0073620670127825</v>
       </c>
       <c r="AO108">
-        <v>0.01</v>
+        <v>0.0073620670127825</v>
       </c>
       <c r="AP108">
-        <v>0.01</v>
+        <v>0.0073620670127825</v>
       </c>
       <c r="AQ108">
-        <v>0.01</v>
+        <v>0.0073620670127825</v>
       </c>
       <c r="AR108">
-        <v>0.01</v>
+        <v>0.0073620670127825</v>
       </c>
       <c r="AS108">
-        <v>0.01</v>
+        <v>0.0073620670127825</v>
       </c>
     </row>
     <row r="109" spans="1:45">
@@ -14310,112 +14310,112 @@
         <v>1</v>
       </c>
       <c r="J109">
-        <v>0.01</v>
+        <v>0.0072387069976127</v>
       </c>
       <c r="K109">
-        <v>0.01</v>
+        <v>0.0072387069976127</v>
       </c>
       <c r="L109">
-        <v>0.01</v>
+        <v>0.0072387069976127</v>
       </c>
       <c r="M109">
-        <v>0.01</v>
+        <v>0.0072387069976127</v>
       </c>
       <c r="N109">
-        <v>0.01</v>
+        <v>0.0072387069976127</v>
       </c>
       <c r="O109">
-        <v>0.01</v>
+        <v>0.0072387069976127</v>
       </c>
       <c r="P109">
-        <v>0.01</v>
+        <v>0.0072387069976127</v>
       </c>
       <c r="Q109">
-        <v>0.01</v>
+        <v>0.0072387069976127</v>
       </c>
       <c r="R109">
-        <v>0.01</v>
+        <v>0.0072387069976127</v>
       </c>
       <c r="S109">
-        <v>0.01</v>
+        <v>0.0072387069976127</v>
       </c>
       <c r="T109">
-        <v>0.01</v>
+        <v>0.0072387069976127</v>
       </c>
       <c r="U109">
-        <v>0.01</v>
+        <v>0.0072387069976127</v>
       </c>
       <c r="V109">
-        <v>0.01</v>
+        <v>0.0072387069976127</v>
       </c>
       <c r="W109">
-        <v>0.01</v>
+        <v>0.0072387069976127</v>
       </c>
       <c r="X109">
-        <v>0.01</v>
+        <v>0.0072387069976127</v>
       </c>
       <c r="Y109">
-        <v>0.01</v>
+        <v>0.0072387069976127</v>
       </c>
       <c r="Z109">
-        <v>0.01</v>
+        <v>0.0072387069976127</v>
       </c>
       <c r="AA109">
-        <v>0.01</v>
+        <v>0.0072387069976127</v>
       </c>
       <c r="AB109">
-        <v>0.01</v>
+        <v>0.0072387069976127</v>
       </c>
       <c r="AC109">
-        <v>0.01</v>
+        <v>0.0072387069976127</v>
       </c>
       <c r="AD109">
-        <v>0.01</v>
+        <v>0.0072387069976127</v>
       </c>
       <c r="AE109">
-        <v>0.01</v>
+        <v>0.0072387069976127</v>
       </c>
       <c r="AF109">
-        <v>0.01</v>
+        <v>0.0072387069976127</v>
       </c>
       <c r="AG109">
-        <v>0.01</v>
+        <v>0.0072387069976127</v>
       </c>
       <c r="AH109">
-        <v>0.01</v>
+        <v>0.0072387069976127</v>
       </c>
       <c r="AI109">
-        <v>0.01</v>
+        <v>0.0072387069976127</v>
       </c>
       <c r="AJ109">
-        <v>0.01</v>
+        <v>0.0072387069976127</v>
       </c>
       <c r="AK109">
-        <v>0.01</v>
+        <v>0.0072387069976127</v>
       </c>
       <c r="AL109">
-        <v>0.01</v>
+        <v>0.0072387069976127</v>
       </c>
       <c r="AM109">
-        <v>0.01</v>
+        <v>0.0072387069976127</v>
       </c>
       <c r="AN109">
-        <v>0.01</v>
+        <v>0.0072387069976127</v>
       </c>
       <c r="AO109">
-        <v>0.01</v>
+        <v>0.0072387069976127</v>
       </c>
       <c r="AP109">
-        <v>0.01</v>
+        <v>0.0072387069976127</v>
       </c>
       <c r="AQ109">
-        <v>0.01</v>
+        <v>0.0072387069976127</v>
       </c>
       <c r="AR109">
-        <v>0.01</v>
+        <v>0.0072387069976127</v>
       </c>
       <c r="AS109">
-        <v>0.01</v>
+        <v>0.0072387069976127</v>
       </c>
     </row>
     <row r="110" spans="1:45">
@@ -14432,112 +14432,112 @@
         <v>1</v>
       </c>
       <c r="J110">
-        <v>0.013328111</v>
+        <v>0.0176549004068161</v>
       </c>
       <c r="K110">
-        <v>0.013328111</v>
+        <v>0.0176549004068161</v>
       </c>
       <c r="L110">
-        <v>0.013328111</v>
+        <v>0.0176549004068161</v>
       </c>
       <c r="M110">
-        <v>0.013328111</v>
+        <v>0.0176549004068161</v>
       </c>
       <c r="N110">
-        <v>0.013328111</v>
+        <v>0.0176549004068161</v>
       </c>
       <c r="O110">
-        <v>0.013328111</v>
+        <v>0.0176549004068161</v>
       </c>
       <c r="P110">
-        <v>0.013328111</v>
+        <v>0.0176549004068161</v>
       </c>
       <c r="Q110">
-        <v>0.013328111</v>
+        <v>0.0176549004068161</v>
       </c>
       <c r="R110">
-        <v>0.013328111</v>
+        <v>0.0176549004068161</v>
       </c>
       <c r="S110">
-        <v>0.013328111</v>
+        <v>0.0176549004068161</v>
       </c>
       <c r="T110">
-        <v>0.013328111</v>
+        <v>0.0176549004068161</v>
       </c>
       <c r="U110">
-        <v>0.013328111</v>
+        <v>0.0176549004068161</v>
       </c>
       <c r="V110">
-        <v>0.013328111</v>
+        <v>0.0176549004068161</v>
       </c>
       <c r="W110">
-        <v>0.013328111</v>
+        <v>0.0176549004068161</v>
       </c>
       <c r="X110">
-        <v>0.013328111</v>
+        <v>0.0176549004068161</v>
       </c>
       <c r="Y110">
-        <v>0.013328111</v>
+        <v>0.0176549004068161</v>
       </c>
       <c r="Z110">
-        <v>0.013328111</v>
+        <v>0.0176549004068161</v>
       </c>
       <c r="AA110">
-        <v>0.013328111</v>
+        <v>0.0176549004068161</v>
       </c>
       <c r="AB110">
-        <v>0.013328111</v>
+        <v>0.0176549004068161</v>
       </c>
       <c r="AC110">
-        <v>0.013328111</v>
+        <v>0.0176549004068161</v>
       </c>
       <c r="AD110">
-        <v>0.013328111</v>
+        <v>0.0176549004068161</v>
       </c>
       <c r="AE110">
-        <v>0.013328111</v>
+        <v>0.0176549004068161</v>
       </c>
       <c r="AF110">
-        <v>0.013328111</v>
+        <v>0.0176549004068161</v>
       </c>
       <c r="AG110">
-        <v>0.013328111</v>
+        <v>0.0176549004068161</v>
       </c>
       <c r="AH110">
-        <v>0.013328111</v>
+        <v>0.0176549004068161</v>
       </c>
       <c r="AI110">
-        <v>0.013328111</v>
+        <v>0.0176549004068161</v>
       </c>
       <c r="AJ110">
-        <v>0.013328111</v>
+        <v>0.0176549004068161</v>
       </c>
       <c r="AK110">
-        <v>0.013328111</v>
+        <v>0.0176549004068161</v>
       </c>
       <c r="AL110">
-        <v>0.013328111</v>
+        <v>0.0176549004068161</v>
       </c>
       <c r="AM110">
-        <v>0.013328111</v>
+        <v>0.0176549004068161</v>
       </c>
       <c r="AN110">
-        <v>0.013328111</v>
+        <v>0.0176549004068161</v>
       </c>
       <c r="AO110">
-        <v>0.013328111</v>
+        <v>0.0176549004068161</v>
       </c>
       <c r="AP110">
-        <v>0.013328111</v>
+        <v>0.0176549004068161</v>
       </c>
       <c r="AQ110">
-        <v>0.013328111</v>
+        <v>0.0176549004068161</v>
       </c>
       <c r="AR110">
-        <v>0.013328111</v>
+        <v>0.0176549004068161</v>
       </c>
       <c r="AS110">
-        <v>0.013328111</v>
+        <v>0.0176549004068161</v>
       </c>
     </row>
     <row r="111" spans="1:45">
@@ -14554,112 +14554,112 @@
         <v>1</v>
       </c>
       <c r="J111">
-        <v>0.014462372</v>
+        <v>0.0201070080319555</v>
       </c>
       <c r="K111">
-        <v>0.014462372</v>
+        <v>0.0201070080319555</v>
       </c>
       <c r="L111">
-        <v>0.014462372</v>
+        <v>0.0201070080319555</v>
       </c>
       <c r="M111">
-        <v>0.014462372</v>
+        <v>0.0201070080319555</v>
       </c>
       <c r="N111">
-        <v>0.014462372</v>
+        <v>0.0201070080319555</v>
       </c>
       <c r="O111">
-        <v>0.014462372</v>
+        <v>0.0201070080319555</v>
       </c>
       <c r="P111">
-        <v>0.014462372</v>
+        <v>0.0201070080319555</v>
       </c>
       <c r="Q111">
-        <v>0.014462372</v>
+        <v>0.0201070080319555</v>
       </c>
       <c r="R111">
-        <v>0.014462372</v>
+        <v>0.0201070080319555</v>
       </c>
       <c r="S111">
-        <v>0.014462372</v>
+        <v>0.0201070080319555</v>
       </c>
       <c r="T111">
-        <v>0.014462372</v>
+        <v>0.0201070080319555</v>
       </c>
       <c r="U111">
-        <v>0.014462372</v>
+        <v>0.0201070080319555</v>
       </c>
       <c r="V111">
-        <v>0.014462372</v>
+        <v>0.0201070080319555</v>
       </c>
       <c r="W111">
-        <v>0.014462372</v>
+        <v>0.0201070080319555</v>
       </c>
       <c r="X111">
-        <v>0.014462372</v>
+        <v>0.0201070080319555</v>
       </c>
       <c r="Y111">
-        <v>0.014462372</v>
+        <v>0.0201070080319555</v>
       </c>
       <c r="Z111">
-        <v>0.014462372</v>
+        <v>0.0201070080319555</v>
       </c>
       <c r="AA111">
-        <v>0.014462372</v>
+        <v>0.0201070080319555</v>
       </c>
       <c r="AB111">
-        <v>0.014462372</v>
+        <v>0.0201070080319555</v>
       </c>
       <c r="AC111">
-        <v>0.014462372</v>
+        <v>0.0201070080319555</v>
       </c>
       <c r="AD111">
-        <v>0.014462372</v>
+        <v>0.0201070080319555</v>
       </c>
       <c r="AE111">
-        <v>0.014462372</v>
+        <v>0.0201070080319555</v>
       </c>
       <c r="AF111">
-        <v>0.014462372</v>
+        <v>0.0201070080319555</v>
       </c>
       <c r="AG111">
-        <v>0.014462372</v>
+        <v>0.0201070080319555</v>
       </c>
       <c r="AH111">
-        <v>0.014462372</v>
+        <v>0.0201070080319555</v>
       </c>
       <c r="AI111">
-        <v>0.014462372</v>
+        <v>0.0201070080319555</v>
       </c>
       <c r="AJ111">
-        <v>0.014462372</v>
+        <v>0.0201070080319555</v>
       </c>
       <c r="AK111">
-        <v>0.014462372</v>
+        <v>0.0201070080319555</v>
       </c>
       <c r="AL111">
-        <v>0.014462372</v>
+        <v>0.0201070080319555</v>
       </c>
       <c r="AM111">
-        <v>0.014462372</v>
+        <v>0.0201070080319555</v>
       </c>
       <c r="AN111">
-        <v>0.014462372</v>
+        <v>0.0201070080319555</v>
       </c>
       <c r="AO111">
-        <v>0.014462372</v>
+        <v>0.0201070080319555</v>
       </c>
       <c r="AP111">
-        <v>0.014462372</v>
+        <v>0.0201070080319555</v>
       </c>
       <c r="AQ111">
-        <v>0.014462372</v>
+        <v>0.0201070080319555</v>
       </c>
       <c r="AR111">
-        <v>0.014462372</v>
+        <v>0.0201070080319555</v>
       </c>
       <c r="AS111">
-        <v>0.014462372</v>
+        <v>0.0201070080319555</v>
       </c>
     </row>
     <row r="112" spans="1:45">
@@ -14798,112 +14798,112 @@
         <v>1</v>
       </c>
       <c r="J113">
-        <v>1</v>
+        <v>0.5701398232390819</v>
       </c>
       <c r="K113">
-        <v>1</v>
+        <v>0.5701398232390819</v>
       </c>
       <c r="L113">
-        <v>1</v>
+        <v>0.5701398232390819</v>
       </c>
       <c r="M113">
-        <v>1</v>
+        <v>0.5701398232390819</v>
       </c>
       <c r="N113">
-        <v>1</v>
+        <v>0.5701398232390819</v>
       </c>
       <c r="O113">
-        <v>1</v>
+        <v>0.5701398232390819</v>
       </c>
       <c r="P113">
-        <v>1</v>
+        <v>0.5701398232390819</v>
       </c>
       <c r="Q113">
-        <v>1</v>
+        <v>0.5701398232390819</v>
       </c>
       <c r="R113">
-        <v>1</v>
+        <v>0.5701398232390819</v>
       </c>
       <c r="S113">
-        <v>1</v>
+        <v>0.5701398232390819</v>
       </c>
       <c r="T113">
-        <v>1</v>
+        <v>0.5701398232390819</v>
       </c>
       <c r="U113">
-        <v>1</v>
+        <v>0.5701398232390819</v>
       </c>
       <c r="V113">
-        <v>1</v>
+        <v>0.5701398232390819</v>
       </c>
       <c r="W113">
-        <v>1</v>
+        <v>0.5701398232390819</v>
       </c>
       <c r="X113">
-        <v>1</v>
+        <v>0.5701398232390819</v>
       </c>
       <c r="Y113">
-        <v>1</v>
+        <v>0.5701398232390819</v>
       </c>
       <c r="Z113">
-        <v>1</v>
+        <v>0.5701398232390819</v>
       </c>
       <c r="AA113">
-        <v>1</v>
+        <v>0.5701398232390819</v>
       </c>
       <c r="AB113">
-        <v>1</v>
+        <v>0.5701398232390819</v>
       </c>
       <c r="AC113">
-        <v>1</v>
+        <v>0.5701398232390819</v>
       </c>
       <c r="AD113">
-        <v>1</v>
+        <v>0.5701398232390819</v>
       </c>
       <c r="AE113">
-        <v>1</v>
+        <v>0.5701398232390819</v>
       </c>
       <c r="AF113">
-        <v>1</v>
+        <v>0.5701398232390819</v>
       </c>
       <c r="AG113">
-        <v>1</v>
+        <v>0.5701398232390819</v>
       </c>
       <c r="AH113">
-        <v>1</v>
+        <v>0.5701398232390819</v>
       </c>
       <c r="AI113">
-        <v>1</v>
+        <v>0.5701398232390819</v>
       </c>
       <c r="AJ113">
-        <v>1</v>
+        <v>0.5701398232390819</v>
       </c>
       <c r="AK113">
-        <v>1</v>
+        <v>0.5701398232390819</v>
       </c>
       <c r="AL113">
-        <v>1</v>
+        <v>0.5701398232390819</v>
       </c>
       <c r="AM113">
-        <v>1</v>
+        <v>0.5701398232390819</v>
       </c>
       <c r="AN113">
-        <v>1</v>
+        <v>0.5701398232390819</v>
       </c>
       <c r="AO113">
-        <v>1</v>
+        <v>0.5701398232390819</v>
       </c>
       <c r="AP113">
-        <v>1</v>
+        <v>0.5701398232390819</v>
       </c>
       <c r="AQ113">
-        <v>1</v>
+        <v>0.5701398232390819</v>
       </c>
       <c r="AR113">
-        <v>1</v>
+        <v>0.5701398232390819</v>
       </c>
       <c r="AS113">
-        <v>1</v>
+        <v>0.5701398232390819</v>
       </c>
     </row>
     <row r="114" spans="1:45">
@@ -16521,112 +16521,112 @@
         <v>1</v>
       </c>
       <c r="J127">
-        <v>0.8</v>
+        <v>0.6240120623501408</v>
       </c>
       <c r="K127">
-        <v>0.8</v>
+        <v>0.6240120623501408</v>
       </c>
       <c r="L127">
-        <v>0.8</v>
+        <v>0.6240120623501408</v>
       </c>
       <c r="M127">
-        <v>0.8</v>
+        <v>0.6240120623501408</v>
       </c>
       <c r="N127">
-        <v>0.8</v>
+        <v>0.6240120623501408</v>
       </c>
       <c r="O127">
-        <v>0.8</v>
+        <v>0.6240120623501408</v>
       </c>
       <c r="P127">
-        <v>0.8</v>
+        <v>0.6240120623501408</v>
       </c>
       <c r="Q127">
-        <v>0.8</v>
+        <v>0.6240120623501408</v>
       </c>
       <c r="R127">
-        <v>0.8</v>
+        <v>0.6240120623501408</v>
       </c>
       <c r="S127">
-        <v>0.8</v>
+        <v>0.6240120623501408</v>
       </c>
       <c r="T127">
-        <v>0.8</v>
+        <v>0.6240120623501408</v>
       </c>
       <c r="U127">
-        <v>0.8</v>
+        <v>0.6240120623501408</v>
       </c>
       <c r="V127">
-        <v>0.8</v>
+        <v>0.6240120623501408</v>
       </c>
       <c r="W127">
-        <v>0.8</v>
+        <v>0.6240120623501408</v>
       </c>
       <c r="X127">
-        <v>0.8</v>
+        <v>0.6240120623501408</v>
       </c>
       <c r="Y127">
-        <v>0.8</v>
+        <v>0.6240120623501408</v>
       </c>
       <c r="Z127">
-        <v>0.8</v>
+        <v>0.6240120623501408</v>
       </c>
       <c r="AA127">
-        <v>0.8</v>
+        <v>0.6240120623501408</v>
       </c>
       <c r="AB127">
-        <v>0.8</v>
+        <v>0.6240120623501408</v>
       </c>
       <c r="AC127">
-        <v>0.8</v>
+        <v>0.6240120623501408</v>
       </c>
       <c r="AD127">
-        <v>0.8</v>
+        <v>0.6240120623501408</v>
       </c>
       <c r="AE127">
-        <v>0.8</v>
+        <v>0.6240120623501408</v>
       </c>
       <c r="AF127">
-        <v>0.8</v>
+        <v>0.6240120623501408</v>
       </c>
       <c r="AG127">
-        <v>0.8</v>
+        <v>0.6240120623501408</v>
       </c>
       <c r="AH127">
-        <v>0.8</v>
+        <v>0.6240120623501408</v>
       </c>
       <c r="AI127">
-        <v>0.8</v>
+        <v>0.6240120623501408</v>
       </c>
       <c r="AJ127">
-        <v>0.8</v>
+        <v>0.6240120623501408</v>
       </c>
       <c r="AK127">
-        <v>0.8</v>
+        <v>0.6240120623501408</v>
       </c>
       <c r="AL127">
-        <v>0.8</v>
+        <v>0.6240120623501408</v>
       </c>
       <c r="AM127">
-        <v>0.8</v>
+        <v>0.6240120623501408</v>
       </c>
       <c r="AN127">
-        <v>0.8</v>
+        <v>0.6240120623501408</v>
       </c>
       <c r="AO127">
-        <v>0.8</v>
+        <v>0.6240120623501408</v>
       </c>
       <c r="AP127">
-        <v>0.8</v>
+        <v>0.6240120623501408</v>
       </c>
       <c r="AQ127">
-        <v>0.8</v>
+        <v>0.6240120623501408</v>
       </c>
       <c r="AR127">
-        <v>0.8</v>
+        <v>0.6240120623501408</v>
       </c>
       <c r="AS127">
-        <v>0.8</v>
+        <v>0.6240120623501408</v>
       </c>
     </row>
     <row r="128" spans="1:45">
@@ -16643,112 +16643,112 @@
         <v>1</v>
       </c>
       <c r="J128">
-        <v>0.6</v>
+        <v>0.4680090467626056</v>
       </c>
       <c r="K128">
-        <v>0.6</v>
+        <v>0.4680090467626056</v>
       </c>
       <c r="L128">
-        <v>0.6</v>
+        <v>0.4680090467626056</v>
       </c>
       <c r="M128">
-        <v>0.6</v>
+        <v>0.4680090467626056</v>
       </c>
       <c r="N128">
-        <v>0.6</v>
+        <v>0.4680090467626056</v>
       </c>
       <c r="O128">
-        <v>0.6</v>
+        <v>0.4680090467626056</v>
       </c>
       <c r="P128">
-        <v>0.6</v>
+        <v>0.4680090467626056</v>
       </c>
       <c r="Q128">
-        <v>0.6</v>
+        <v>0.4680090467626056</v>
       </c>
       <c r="R128">
-        <v>0.6</v>
+        <v>0.4680090467626056</v>
       </c>
       <c r="S128">
-        <v>0.6</v>
+        <v>0.4680090467626056</v>
       </c>
       <c r="T128">
-        <v>0.6</v>
+        <v>0.4680090467626056</v>
       </c>
       <c r="U128">
-        <v>0.6</v>
+        <v>0.4680090467626056</v>
       </c>
       <c r="V128">
-        <v>0.6</v>
+        <v>0.4680090467626056</v>
       </c>
       <c r="W128">
-        <v>0.6</v>
+        <v>0.4680090467626056</v>
       </c>
       <c r="X128">
-        <v>0.6</v>
+        <v>0.4680090467626056</v>
       </c>
       <c r="Y128">
-        <v>0.6</v>
+        <v>0.4680090467626056</v>
       </c>
       <c r="Z128">
-        <v>0.6</v>
+        <v>0.4680090467626056</v>
       </c>
       <c r="AA128">
-        <v>0.6</v>
+        <v>0.4680090467626056</v>
       </c>
       <c r="AB128">
-        <v>0.6</v>
+        <v>0.4680090467626056</v>
       </c>
       <c r="AC128">
-        <v>0.6</v>
+        <v>0.4680090467626056</v>
       </c>
       <c r="AD128">
-        <v>0.6</v>
+        <v>0.4680090467626056</v>
       </c>
       <c r="AE128">
-        <v>0.6</v>
+        <v>0.4680090467626056</v>
       </c>
       <c r="AF128">
-        <v>0.6</v>
+        <v>0.4680090467626056</v>
       </c>
       <c r="AG128">
-        <v>0.6</v>
+        <v>0.4680090467626056</v>
       </c>
       <c r="AH128">
-        <v>0.6</v>
+        <v>0.4680090467626056</v>
       </c>
       <c r="AI128">
-        <v>0.6</v>
+        <v>0.4680090467626056</v>
       </c>
       <c r="AJ128">
-        <v>0.6</v>
+        <v>0.4680090467626056</v>
       </c>
       <c r="AK128">
-        <v>0.6</v>
+        <v>0.4680090467626056</v>
       </c>
       <c r="AL128">
-        <v>0.6</v>
+        <v>0.4680090467626056</v>
       </c>
       <c r="AM128">
-        <v>0.6</v>
+        <v>0.4680090467626056</v>
       </c>
       <c r="AN128">
-        <v>0.6</v>
+        <v>0.4680090467626056</v>
       </c>
       <c r="AO128">
-        <v>0.6</v>
+        <v>0.4680090467626056</v>
       </c>
       <c r="AP128">
-        <v>0.6</v>
+        <v>0.4680090467626056</v>
       </c>
       <c r="AQ128">
-        <v>0.6</v>
+        <v>0.4680090467626056</v>
       </c>
       <c r="AR128">
-        <v>0.6</v>
+        <v>0.4680090467626056</v>
       </c>
       <c r="AS128">
-        <v>0.6</v>
+        <v>0.4680090467626056</v>
       </c>
     </row>
     <row r="129" spans="1:45">
@@ -16765,112 +16765,112 @@
         <v>1</v>
       </c>
       <c r="J129">
-        <v>0.9</v>
+        <v>0.7020135701439084</v>
       </c>
       <c r="K129">
-        <v>0.9</v>
+        <v>0.7020135701439084</v>
       </c>
       <c r="L129">
-        <v>0.9</v>
+        <v>0.7020135701439084</v>
       </c>
       <c r="M129">
-        <v>0.9</v>
+        <v>0.7020135701439084</v>
       </c>
       <c r="N129">
-        <v>0.9</v>
+        <v>0.7020135701439084</v>
       </c>
       <c r="O129">
-        <v>0.9</v>
+        <v>0.7020135701439084</v>
       </c>
       <c r="P129">
-        <v>0.9</v>
+        <v>0.7020135701439084</v>
       </c>
       <c r="Q129">
-        <v>0.9</v>
+        <v>0.7020135701439084</v>
       </c>
       <c r="R129">
-        <v>0.9</v>
+        <v>0.7020135701439084</v>
       </c>
       <c r="S129">
-        <v>0.9</v>
+        <v>0.7020135701439084</v>
       </c>
       <c r="T129">
-        <v>0.9</v>
+        <v>0.7020135701439084</v>
       </c>
       <c r="U129">
-        <v>0.9</v>
+        <v>0.7020135701439084</v>
       </c>
       <c r="V129">
-        <v>0.9</v>
+        <v>0.7020135701439084</v>
       </c>
       <c r="W129">
-        <v>0.9</v>
+        <v>0.7020135701439084</v>
       </c>
       <c r="X129">
-        <v>0.9</v>
+        <v>0.7020135701439084</v>
       </c>
       <c r="Y129">
-        <v>0.9</v>
+        <v>0.7020135701439084</v>
       </c>
       <c r="Z129">
-        <v>0.9</v>
+        <v>0.7020135701439084</v>
       </c>
       <c r="AA129">
-        <v>0.9</v>
+        <v>0.7020135701439084</v>
       </c>
       <c r="AB129">
-        <v>0.9</v>
+        <v>0.7020135701439084</v>
       </c>
       <c r="AC129">
-        <v>0.9</v>
+        <v>0.7020135701439084</v>
       </c>
       <c r="AD129">
-        <v>0.9</v>
+        <v>0.7020135701439084</v>
       </c>
       <c r="AE129">
-        <v>0.9</v>
+        <v>0.7020135701439084</v>
       </c>
       <c r="AF129">
-        <v>0.9</v>
+        <v>0.7020135701439084</v>
       </c>
       <c r="AG129">
-        <v>0.9</v>
+        <v>0.7020135701439084</v>
       </c>
       <c r="AH129">
-        <v>0.9</v>
+        <v>0.7020135701439084</v>
       </c>
       <c r="AI129">
-        <v>0.9</v>
+        <v>0.7020135701439084</v>
       </c>
       <c r="AJ129">
-        <v>0.9</v>
+        <v>0.7020135701439084</v>
       </c>
       <c r="AK129">
-        <v>0.9</v>
+        <v>0.7020135701439084</v>
       </c>
       <c r="AL129">
-        <v>0.9</v>
+        <v>0.7020135701439084</v>
       </c>
       <c r="AM129">
-        <v>0.9</v>
+        <v>0.7020135701439084</v>
       </c>
       <c r="AN129">
-        <v>0.9</v>
+        <v>0.7020135701439084</v>
       </c>
       <c r="AO129">
-        <v>0.9</v>
+        <v>0.7020135701439084</v>
       </c>
       <c r="AP129">
-        <v>0.9</v>
+        <v>0.7020135701439084</v>
       </c>
       <c r="AQ129">
-        <v>0.9</v>
+        <v>0.7020135701439084</v>
       </c>
       <c r="AR129">
-        <v>0.9</v>
+        <v>0.7020135701439084</v>
       </c>
       <c r="AS129">
-        <v>0.9</v>
+        <v>0.7020135701439084</v>
       </c>
     </row>
     <row r="130" spans="1:45">
@@ -16887,112 +16887,112 @@
         <v>1</v>
       </c>
       <c r="J130">
-        <v>0.45</v>
+        <v>0.3510067850719542</v>
       </c>
       <c r="K130">
-        <v>0.45</v>
+        <v>0.3510067850719542</v>
       </c>
       <c r="L130">
-        <v>0.45</v>
+        <v>0.3510067850719542</v>
       </c>
       <c r="M130">
-        <v>0.45</v>
+        <v>0.3510067850719542</v>
       </c>
       <c r="N130">
-        <v>0.45</v>
+        <v>0.3510067850719542</v>
       </c>
       <c r="O130">
-        <v>0.45</v>
+        <v>0.3510067850719542</v>
       </c>
       <c r="P130">
-        <v>0.45</v>
+        <v>0.3510067850719542</v>
       </c>
       <c r="Q130">
-        <v>0.45</v>
+        <v>0.3510067850719542</v>
       </c>
       <c r="R130">
-        <v>0.45</v>
+        <v>0.3510067850719542</v>
       </c>
       <c r="S130">
-        <v>0.45</v>
+        <v>0.3510067850719542</v>
       </c>
       <c r="T130">
-        <v>0.45</v>
+        <v>0.3510067850719542</v>
       </c>
       <c r="U130">
-        <v>0.45</v>
+        <v>0.3510067850719542</v>
       </c>
       <c r="V130">
-        <v>0.45</v>
+        <v>0.3510067850719542</v>
       </c>
       <c r="W130">
-        <v>0.45</v>
+        <v>0.3510067850719542</v>
       </c>
       <c r="X130">
-        <v>0.45</v>
+        <v>0.3510067850719542</v>
       </c>
       <c r="Y130">
-        <v>0.45</v>
+        <v>0.3510067850719542</v>
       </c>
       <c r="Z130">
-        <v>0.45</v>
+        <v>0.3510067850719542</v>
       </c>
       <c r="AA130">
-        <v>0.45</v>
+        <v>0.3510067850719542</v>
       </c>
       <c r="AB130">
-        <v>0.45</v>
+        <v>0.3510067850719542</v>
       </c>
       <c r="AC130">
-        <v>0.45</v>
+        <v>0.3510067850719542</v>
       </c>
       <c r="AD130">
-        <v>0.45</v>
+        <v>0.3510067850719542</v>
       </c>
       <c r="AE130">
-        <v>0.45</v>
+        <v>0.3510067850719542</v>
       </c>
       <c r="AF130">
-        <v>0.45</v>
+        <v>0.3510067850719542</v>
       </c>
       <c r="AG130">
-        <v>0.45</v>
+        <v>0.3510067850719542</v>
       </c>
       <c r="AH130">
-        <v>0.45</v>
+        <v>0.3510067850719542</v>
       </c>
       <c r="AI130">
-        <v>0.45</v>
+        <v>0.3510067850719542</v>
       </c>
       <c r="AJ130">
-        <v>0.45</v>
+        <v>0.3510067850719542</v>
       </c>
       <c r="AK130">
-        <v>0.45</v>
+        <v>0.3510067850719542</v>
       </c>
       <c r="AL130">
-        <v>0.45</v>
+        <v>0.3510067850719542</v>
       </c>
       <c r="AM130">
-        <v>0.45</v>
+        <v>0.3510067850719542</v>
       </c>
       <c r="AN130">
-        <v>0.45</v>
+        <v>0.3510067850719542</v>
       </c>
       <c r="AO130">
-        <v>0.45</v>
+        <v>0.3510067850719542</v>
       </c>
       <c r="AP130">
-        <v>0.45</v>
+        <v>0.3510067850719542</v>
       </c>
       <c r="AQ130">
-        <v>0.45</v>
+        <v>0.3510067850719542</v>
       </c>
       <c r="AR130">
-        <v>0.45</v>
+        <v>0.3510067850719542</v>
       </c>
       <c r="AS130">
-        <v>0.45</v>
+        <v>0.3510067850719542</v>
       </c>
     </row>
     <row r="131" spans="1:45">
@@ -17009,112 +17009,112 @@
         <v>1</v>
       </c>
       <c r="J131">
-        <v>1032688</v>
+        <v>885523.2084557209</v>
       </c>
       <c r="K131">
-        <v>1127940.64</v>
+        <v>967201.7245096284</v>
       </c>
       <c r="L131">
-        <v>1175874.855</v>
+        <v>1008305.000486115</v>
       </c>
       <c r="M131">
-        <v>1847974.46</v>
+        <v>1584626.01769695</v>
       </c>
       <c r="N131">
-        <v>1625748.2</v>
+        <v>1394068.452625684</v>
       </c>
       <c r="O131">
-        <v>1652780.05</v>
+        <v>1417248.087270895</v>
       </c>
       <c r="P131">
-        <v>1054087.225</v>
+        <v>903872.9039886078</v>
       </c>
       <c r="Q131">
-        <v>1054087.225</v>
+        <v>903872.9039886078</v>
       </c>
       <c r="R131">
-        <v>1054087.225</v>
+        <v>903872.9039886078</v>
       </c>
       <c r="S131">
-        <v>1054087.225</v>
+        <v>903872.9039886078</v>
       </c>
       <c r="T131">
-        <v>1054087.225</v>
+        <v>903872.9039886078</v>
       </c>
       <c r="U131">
-        <v>1054087.225</v>
+        <v>903872.9039886078</v>
       </c>
       <c r="V131">
-        <v>1054087.225</v>
+        <v>903872.9039886078</v>
       </c>
       <c r="W131">
-        <v>1054087.225</v>
+        <v>903872.9039886078</v>
       </c>
       <c r="X131">
-        <v>1054087.225</v>
+        <v>903872.9039886078</v>
       </c>
       <c r="Y131">
-        <v>1054087.225</v>
+        <v>903872.9039886078</v>
       </c>
       <c r="Z131">
-        <v>1054087.225</v>
+        <v>903872.9039886078</v>
       </c>
       <c r="AA131">
-        <v>1054087.225</v>
+        <v>903872.9039886078</v>
       </c>
       <c r="AB131">
-        <v>1054087.225</v>
+        <v>903872.9039886078</v>
       </c>
       <c r="AC131">
-        <v>1054087.225</v>
+        <v>903872.9039886078</v>
       </c>
       <c r="AD131">
-        <v>1054087.225</v>
+        <v>903872.9039886078</v>
       </c>
       <c r="AE131">
-        <v>1054087.225</v>
+        <v>903872.9039886078</v>
       </c>
       <c r="AF131">
-        <v>1054087.225</v>
+        <v>903872.9039886078</v>
       </c>
       <c r="AG131">
-        <v>1054087.225</v>
+        <v>903872.9039886078</v>
       </c>
       <c r="AH131">
-        <v>1054087.225</v>
+        <v>903872.9039886078</v>
       </c>
       <c r="AI131">
-        <v>1054087.225</v>
+        <v>903872.9039886078</v>
       </c>
       <c r="AJ131">
-        <v>1054087.225</v>
+        <v>903872.9039886078</v>
       </c>
       <c r="AK131">
-        <v>1054087.225</v>
+        <v>903872.9039886078</v>
       </c>
       <c r="AL131">
-        <v>1054087.225</v>
+        <v>903872.9039886078</v>
       </c>
       <c r="AM131">
-        <v>1054087.225</v>
+        <v>903872.9039886078</v>
       </c>
       <c r="AN131">
-        <v>1054087.225</v>
+        <v>903872.9039886078</v>
       </c>
       <c r="AO131">
-        <v>1054087.225</v>
+        <v>903872.9039886078</v>
       </c>
       <c r="AP131">
-        <v>1054087.225</v>
+        <v>903872.9039886078</v>
       </c>
       <c r="AQ131">
-        <v>1054087.225</v>
+        <v>903872.9039886078</v>
       </c>
       <c r="AR131">
-        <v>1054087.225</v>
+        <v>903872.9039886078</v>
       </c>
       <c r="AS131">
-        <v>1054087.225</v>
+        <v>903872.9039886078</v>
       </c>
     </row>
     <row r="132" spans="1:45">
@@ -17131,112 +17131,112 @@
         <v>1</v>
       </c>
       <c r="J132">
-        <v>26466237.38</v>
+        <v>2646623.738</v>
       </c>
       <c r="K132">
-        <v>23815432.61</v>
+        <v>2381543.261</v>
       </c>
       <c r="L132">
-        <v>15030268.09</v>
+        <v>1503026.809</v>
       </c>
       <c r="M132">
-        <v>15825335.83</v>
+        <v>1582533.583</v>
       </c>
       <c r="N132">
-        <v>13338189.99</v>
+        <v>1333818.999</v>
       </c>
       <c r="O132">
-        <v>14333453.86</v>
+        <v>1433345.386</v>
       </c>
       <c r="P132">
-        <v>14333450</v>
+        <v>1433345</v>
       </c>
       <c r="Q132">
-        <v>13923395.13</v>
+        <v>1392339.513000001</v>
       </c>
       <c r="R132">
-        <v>13525071.21</v>
+        <v>1352507.121000001</v>
       </c>
       <c r="S132">
-        <v>13138142.64</v>
+        <v>1313814.264</v>
       </c>
       <c r="T132">
-        <v>12762283.42</v>
+        <v>1276228.342</v>
       </c>
       <c r="U132">
-        <v>12397176.87</v>
+        <v>1239717.687</v>
       </c>
       <c r="V132">
-        <v>12042515.38</v>
+        <v>1204251.538</v>
       </c>
       <c r="W132">
-        <v>11698000.13</v>
+        <v>1169800.013</v>
       </c>
       <c r="X132">
-        <v>11363340.86</v>
+        <v>1136334.086</v>
       </c>
       <c r="Y132">
-        <v>11038255.61</v>
+        <v>1103825.561</v>
       </c>
       <c r="Z132">
-        <v>10722470.47</v>
+        <v>1072247.047</v>
       </c>
       <c r="AA132">
-        <v>10415719.39</v>
+        <v>1041571.939</v>
       </c>
       <c r="AB132">
-        <v>10117743.93</v>
+        <v>1011774.393</v>
       </c>
       <c r="AC132">
-        <v>9828293.016000001</v>
+        <v>982829.3016</v>
       </c>
       <c r="AD132">
-        <v>9547122.788000001</v>
+        <v>954712.2788</v>
       </c>
       <c r="AE132">
-        <v>9273996.346999999</v>
+        <v>927399.6347000001</v>
       </c>
       <c r="AF132">
-        <v>9008683.573999999</v>
+        <v>900868.3574</v>
       </c>
       <c r="AG132">
-        <v>8750960.935000001</v>
+        <v>875096.0935000001</v>
       </c>
       <c r="AH132">
-        <v>8500611.288000001</v>
+        <v>850061.1288000001</v>
       </c>
       <c r="AI132">
-        <v>8257423.706</v>
+        <v>825742.3706</v>
       </c>
       <c r="AJ132">
-        <v>8021193.294</v>
+        <v>802119.3294</v>
       </c>
       <c r="AK132">
-        <v>7791721.02</v>
+        <v>779172.102</v>
       </c>
       <c r="AL132">
-        <v>7568813.545</v>
+        <v>756881.3545</v>
       </c>
       <c r="AM132">
-        <v>7352283.062</v>
+        <v>735228.3062</v>
       </c>
       <c r="AN132">
-        <v>7141947.137</v>
+        <v>714194.7137000001</v>
       </c>
       <c r="AO132">
-        <v>6937628.553</v>
+        <v>693762.8553000001</v>
       </c>
       <c r="AP132">
-        <v>6739155.166</v>
+        <v>673915.5166000001</v>
       </c>
       <c r="AQ132">
-        <v>6546359.755</v>
+        <v>654635.9755000001</v>
       </c>
       <c r="AR132">
-        <v>6359079.882</v>
+        <v>635907.9882</v>
       </c>
       <c r="AS132">
-        <v>6177157.758</v>
+        <v>617715.7758000001</v>
       </c>
     </row>
     <row r="133" spans="1:45">
@@ -17253,112 +17253,112 @@
         <v>1</v>
       </c>
       <c r="J133">
-        <v>50906.96393</v>
+        <v>19563.14524515116</v>
       </c>
       <c r="K133">
-        <v>85320.09634</v>
+        <v>32787.84095875093</v>
       </c>
       <c r="L133">
-        <v>76640.83964000001</v>
+        <v>29452.47097527426</v>
       </c>
       <c r="M133">
-        <v>78776.01375</v>
+        <v>30273.00156702303</v>
       </c>
       <c r="N133">
-        <v>70335.72749999999</v>
+        <v>27029.46604511586</v>
       </c>
       <c r="O133">
-        <v>91462.62344</v>
+        <v>35148.36573871647</v>
       </c>
       <c r="P133">
-        <v>91462.62</v>
+        <v>35148.36441675157</v>
       </c>
       <c r="Q133">
-        <v>103676.6061</v>
+        <v>39842.10306565468</v>
       </c>
       <c r="R133">
-        <v>117521.657</v>
+        <v>45162.64706933262</v>
       </c>
       <c r="S133">
-        <v>133215.5863</v>
+        <v>51193.70047855197</v>
       </c>
       <c r="T133">
-        <v>151005.2945</v>
+        <v>58030.1452106324</v>
       </c>
       <c r="U133">
-        <v>171170.6536</v>
+        <v>65779.53387062768</v>
       </c>
       <c r="V133">
-        <v>194028.9097</v>
+        <v>74563.78163582656</v>
       </c>
       <c r="W133">
-        <v>219939.6742</v>
+        <v>84521.08433459717</v>
       </c>
       <c r="X133">
-        <v>249310.5815</v>
+        <v>95808.09265593137</v>
       </c>
       <c r="Y133">
-        <v>282603.7015</v>
+        <v>108602.3764226837</v>
       </c>
       <c r="Z133">
-        <v>320342.8094</v>
+        <v>123105.2183184474</v>
       </c>
       <c r="AA133">
-        <v>363121.6259</v>
+        <v>139544.780531506</v>
       </c>
       <c r="AB133">
-        <v>411613.1572</v>
+        <v>158179.6940432632</v>
       </c>
       <c r="AC133">
-        <v>466580.2836</v>
+        <v>179303.1277438159</v>
       </c>
       <c r="AD133">
-        <v>528887.7608</v>
+        <v>203247.4004370106</v>
       </c>
       <c r="AE133">
-        <v>599515.8247999999</v>
+        <v>230389.2090963476</v>
       </c>
       <c r="AF133">
-        <v>679575.6128</v>
+        <v>261155.5549953813</v>
       </c>
       <c r="AG133">
-        <v>770326.6443</v>
+        <v>296030.4615567514</v>
       </c>
       <c r="AH133">
-        <v>873196.6359</v>
+        <v>335562.5890237425</v>
       </c>
       <c r="AI133">
-        <v>989803.9625</v>
+        <v>380373.8661225176</v>
       </c>
       <c r="AJ133">
-        <v>1121983.118</v>
+        <v>431169.2744085745</v>
       </c>
       <c r="AK133">
-        <v>1271813.576</v>
+        <v>488747.9392064207</v>
       </c>
       <c r="AL133">
-        <v>1441652.504</v>
+        <v>554015.7014189446</v>
       </c>
       <c r="AM133">
-        <v>1634171.849</v>
+        <v>627999.3692313725</v>
       </c>
       <c r="AN133">
-        <v>1852400.371</v>
+        <v>711862.8712542218</v>
       </c>
       <c r="AO133">
-        <v>2099771.29</v>
+        <v>806925.5668900863</v>
       </c>
       <c r="AP133">
-        <v>2380176.306</v>
+        <v>914683.005794122</v>
       </c>
       <c r="AQ133">
-        <v>2698026.816</v>
+        <v>1036830.453084943</v>
       </c>
       <c r="AR133">
-        <v>3058323.319</v>
+        <v>1175289.561139416</v>
       </c>
       <c r="AS133">
-        <v>3466734.084</v>
+        <v>1332238.601085399</v>
       </c>
     </row>
     <row r="134" spans="1:45">
@@ -17375,112 +17375,112 @@
         <v>1</v>
       </c>
       <c r="J134">
-        <v>50493.79028</v>
+        <v>22193.18559058245</v>
       </c>
       <c r="K134">
-        <v>81527.6719</v>
+        <v>35833.29243480222</v>
       </c>
       <c r="L134">
-        <v>77150.27766000001</v>
+        <v>33909.32669103935</v>
       </c>
       <c r="M134">
-        <v>53913.77221</v>
+        <v>23696.34653904846</v>
       </c>
       <c r="N134">
-        <v>49651.10226</v>
+        <v>21822.80476713636</v>
       </c>
       <c r="O134">
-        <v>46900.52511</v>
+        <v>20613.86266093555</v>
       </c>
       <c r="P134">
-        <v>46900.53</v>
+        <v>20613.86481020335</v>
       </c>
       <c r="Q134">
-        <v>47352.21259</v>
+        <v>20812.3897276698</v>
       </c>
       <c r="R134">
-        <v>47808.24518</v>
+        <v>21012.82657047961</v>
       </c>
       <c r="S134">
-        <v>48268.66965</v>
+        <v>21215.19374585885</v>
       </c>
       <c r="T134">
-        <v>48733.52832</v>
+        <v>21419.50985442374</v>
       </c>
       <c r="U134">
-        <v>49202.86387</v>
+        <v>21625.7936550188</v>
       </c>
       <c r="V134">
-        <v>49676.71943</v>
+        <v>21834.06410427392</v>
       </c>
       <c r="W134">
-        <v>50155.13853</v>
+        <v>22044.34033462822</v>
       </c>
       <c r="X134">
-        <v>50638.16511</v>
+        <v>22256.64165872531</v>
       </c>
       <c r="Y134">
-        <v>51125.84356</v>
+        <v>22470.98758699413</v>
       </c>
       <c r="Z134">
-        <v>51618.21866</v>
+        <v>22687.39780127764</v>
       </c>
       <c r="AA134">
-        <v>52115.33566</v>
+        <v>22905.89218999465</v>
       </c>
       <c r="AB134">
-        <v>52617.24022</v>
+        <v>23126.49082176842</v>
       </c>
       <c r="AC134">
-        <v>53123.97844</v>
+        <v>23349.21395861236</v>
       </c>
       <c r="AD134">
-        <v>53635.59689</v>
+        <v>23574.0820691157</v>
       </c>
       <c r="AE134">
-        <v>54152.14255</v>
+        <v>23801.11580207219</v>
       </c>
       <c r="AF134">
-        <v>54673.66288</v>
+        <v>24030.33601724657</v>
       </c>
       <c r="AG134">
-        <v>55200.20579</v>
+        <v>24261.76377218902</v>
       </c>
       <c r="AH134">
-        <v>55731.81965</v>
+        <v>24495.42032663031</v>
       </c>
       <c r="AI134">
-        <v>56268.5533</v>
+        <v>24731.32714687705</v>
       </c>
       <c r="AJ134">
-        <v>56810.45604</v>
+        <v>24969.50590141648</v>
       </c>
       <c r="AK134">
-        <v>57357.57766</v>
+        <v>25209.9784741021</v>
       </c>
       <c r="AL134">
-        <v>57909.96842</v>
+        <v>25452.7669553633</v>
       </c>
       <c r="AM134">
-        <v>58467.67906</v>
+        <v>25697.89364660053</v>
       </c>
       <c r="AN134">
-        <v>59030.76081</v>
+        <v>25945.38106458051</v>
       </c>
       <c r="AO134">
-        <v>59599.2654</v>
+        <v>26195.25194583153</v>
       </c>
       <c r="AP134">
-        <v>60173.24507</v>
+        <v>26447.52925103864</v>
       </c>
       <c r="AQ134">
-        <v>60752.75253</v>
+        <v>26702.23614746272</v>
       </c>
       <c r="AR134">
-        <v>61337.84103</v>
+        <v>26959.3960397071</v>
       </c>
       <c r="AS134">
-        <v>61928.56431</v>
+        <v>27219.03254774145</v>
       </c>
     </row>
     <row r="135" spans="1:45">
@@ -17497,112 +17497,112 @@
         <v>1</v>
       </c>
       <c r="J135">
-        <v>6978.867111</v>
+        <v>6144.834924584877</v>
       </c>
       <c r="K135">
-        <v>6615.291246</v>
+        <v>5824.709374484235</v>
       </c>
       <c r="L135">
-        <v>6082.123108</v>
+        <v>5355.259226924563</v>
       </c>
       <c r="M135">
-        <v>4993.741643</v>
+        <v>4396.94832473509</v>
       </c>
       <c r="N135">
-        <v>4528.242526</v>
+        <v>3987.080191983791</v>
       </c>
       <c r="O135">
-        <v>4992.019769</v>
+        <v>4395.432228881329</v>
       </c>
       <c r="P135">
-        <v>4992.02</v>
+        <v>4395.432432274924</v>
       </c>
       <c r="Q135">
-        <v>5236.611709</v>
+        <v>4610.793414483358</v>
       </c>
       <c r="R135">
-        <v>5493.187565</v>
+        <v>4836.706339271541</v>
       </c>
       <c r="S135">
-        <v>5762.33475</v>
+        <v>5073.688215546976</v>
       </c>
       <c r="T135">
-        <v>6044.669216</v>
+        <v>5322.281383964855</v>
       </c>
       <c r="U135">
-        <v>6340.837095</v>
+        <v>5583.054758421423</v>
       </c>
       <c r="V135">
-        <v>6651.516174</v>
+        <v>5856.605124779311</v>
       </c>
       <c r="W135">
-        <v>6977.417454</v>
+        <v>6143.558513554178</v>
       </c>
       <c r="X135">
-        <v>7319.286769</v>
+        <v>6444.571625430855</v>
       </c>
       <c r="Y135">
-        <v>7677.906497</v>
+        <v>6760.333337784734</v>
       </c>
       <c r="Z135">
-        <v>8054.097351</v>
+        <v>7091.566281642492</v>
       </c>
       <c r="AA135">
-        <v>8448.720256000001</v>
+        <v>7439.028494365107</v>
       </c>
       <c r="AB135">
-        <v>8862.678318</v>
+        <v>7803.515153336119</v>
       </c>
       <c r="AC135">
-        <v>9296.918892</v>
+        <v>8185.860396818572</v>
       </c>
       <c r="AD135">
-        <v>9752.435751999999</v>
+        <v>8586.939234622114</v>
       </c>
       <c r="AE135">
-        <v>10230.27136</v>
+        <v>9007.669545938776</v>
       </c>
       <c r="AF135">
-        <v>10731.51926</v>
+        <v>9449.014187240233</v>
       </c>
       <c r="AG135">
-        <v>11257.32658</v>
+        <v>9911.983195268158</v>
       </c>
       <c r="AH135">
-        <v>11808.89663</v>
+        <v>10397.63607455179</v>
       </c>
       <c r="AI135">
-        <v>12387.49171</v>
+        <v>10907.0842698288</v>
       </c>
       <c r="AJ135">
-        <v>12994.43595</v>
+        <v>11441.4936666418</v>
       </c>
       <c r="AK135">
-        <v>13631.11835</v>
+        <v>12002.08726803335</v>
       </c>
       <c r="AL135">
-        <v>14298.99599</v>
+        <v>12590.14802092441</v>
       </c>
       <c r="AM135">
-        <v>14999.59732</v>
+        <v>13207.02171293225</v>
       </c>
       <c r="AN135">
-        <v>15734.52569</v>
+        <v>13854.12008050628</v>
       </c>
       <c r="AO135">
-        <v>16505.46302</v>
+        <v>14532.92404033285</v>
       </c>
       <c r="AP135">
-        <v>17314.1736</v>
+        <v>15244.98703520384</v>
       </c>
       <c r="AQ135">
-        <v>18162.5082</v>
+        <v>15991.93865283778</v>
       </c>
       <c r="AR135">
-        <v>19052.40826</v>
+        <v>16775.48831514029</v>
       </c>
       <c r="AS135">
-        <v>19985.91035</v>
+        <v>17597.42920519731</v>
       </c>
     </row>
     <row r="136" spans="1:45">
@@ -17619,112 +17619,112 @@
         <v>1</v>
       </c>
       <c r="J136">
-        <v>99844.36679</v>
+        <v>119562.2470599845</v>
       </c>
       <c r="K136">
-        <v>140230.6057</v>
+        <v>167924.2090777014</v>
       </c>
       <c r="L136">
-        <v>45881.38812</v>
+        <v>54942.32712593958</v>
       </c>
       <c r="M136">
-        <v>23835.14788</v>
+        <v>28542.25963026738</v>
       </c>
       <c r="N136">
-        <v>137504.0383</v>
+        <v>164659.1823607695</v>
       </c>
       <c r="O136">
-        <v>63447.27928</v>
+        <v>75977.23862092706</v>
       </c>
       <c r="P136">
-        <v>63447.28</v>
+        <v>75977.2394831171</v>
       </c>
       <c r="Q136">
-        <v>107794.7367</v>
+        <v>129082.7049682106</v>
       </c>
       <c r="R136">
-        <v>183139.5334</v>
+        <v>219307.0559992189</v>
       </c>
       <c r="S136">
-        <v>311147.74</v>
+        <v>372595.1113524591</v>
       </c>
       <c r="T136">
-        <v>528629.2604</v>
+        <v>633026.2213792911</v>
       </c>
       <c r="U136">
-        <v>898122.8498</v>
+        <v>1075489.679691772</v>
       </c>
       <c r="V136">
-        <v>1525879.693</v>
+        <v>1827219.809225647</v>
       </c>
       <c r="W136">
-        <v>2592416.88</v>
+        <v>3104383.326311785</v>
       </c>
       <c r="X136">
-        <v>4404426.714</v>
+        <v>5274240.018412396</v>
       </c>
       <c r="Y136">
-        <v>7482968.818</v>
+        <v>8960751.570908692</v>
       </c>
       <c r="Z136">
-        <v>12713305.49</v>
+        <v>15224007.33074385</v>
       </c>
       <c r="AA136">
-        <v>21599466.8</v>
+        <v>25865062.4860709</v>
       </c>
       <c r="AB136">
-        <v>36696747.85</v>
+        <v>43943847.54793291</v>
       </c>
       <c r="AC136">
-        <v>62346506.77</v>
+        <v>74659078.77847673</v>
       </c>
       <c r="AD136">
-        <v>105924561</v>
+        <v>126843195.4567799</v>
       </c>
       <c r="AE136">
-        <v>179962169.5</v>
+        <v>215502206.714028</v>
       </c>
       <c r="AF136">
-        <v>305749508.5</v>
+        <v>366130803.8603049</v>
       </c>
       <c r="AG136">
-        <v>519457851.7</v>
+        <v>622043586.4231914</v>
       </c>
       <c r="AH136">
-        <v>882540943.2</v>
+        <v>1056830562.242581</v>
       </c>
       <c r="AI136">
-        <v>1499406572</v>
+        <v>1795518613.302314</v>
       </c>
       <c r="AJ136">
-        <v>2547439962</v>
+        <v>3050524089.633736</v>
       </c>
       <c r="AK136">
-        <v>4328012484</v>
+        <v>5182735035.809076</v>
       </c>
       <c r="AL136">
-        <v>7353143682</v>
+        <v>8805287767.751169</v>
       </c>
       <c r="AM136">
-        <v>12492737072</v>
+        <v>14959879703.57372</v>
       </c>
       <c r="AN136">
-        <v>21224728674</v>
+        <v>25416318767.78138</v>
       </c>
       <c r="AO136">
-        <v>36060080724</v>
+        <v>43181447478.09335</v>
       </c>
       <c r="AP136">
-        <v>61264831311</v>
+        <v>73363787390.23355</v>
       </c>
       <c r="AQ136">
-        <v>104000000000</v>
+        <v>124538560301.4688</v>
       </c>
       <c r="AR136">
-        <v>177000000000</v>
+        <v>211955049743.846</v>
       </c>
       <c r="AS136">
-        <v>300000000000</v>
+        <v>359245847023.4678</v>
       </c>
     </row>
     <row r="137" spans="1:45">
@@ -17741,112 +17741,112 @@
         <v>1</v>
       </c>
       <c r="J137">
-        <v>453038.4103</v>
+        <v>380491.634963544</v>
       </c>
       <c r="K137">
-        <v>462878.1583</v>
+        <v>388755.706439669</v>
       </c>
       <c r="L137">
-        <v>440801.3604</v>
+        <v>370214.1507199934</v>
       </c>
       <c r="M137">
-        <v>509570.857</v>
+        <v>427971.3245093565</v>
       </c>
       <c r="N137">
-        <v>488469.3812</v>
+        <v>410248.9088272757</v>
       </c>
       <c r="O137">
-        <v>507138.6028</v>
+        <v>425928.5564875631</v>
       </c>
       <c r="P137">
-        <v>507138.6</v>
+        <v>425928.5541359378</v>
       </c>
       <c r="Q137">
-        <v>530684.6213999999</v>
+        <v>445704.0609708659</v>
       </c>
       <c r="R137">
-        <v>555323.865</v>
+        <v>466397.7281489335</v>
       </c>
       <c r="S137">
-        <v>581107.088</v>
+        <v>488052.1849253541</v>
       </c>
       <c r="T137">
-        <v>608087.4044999999</v>
+        <v>510712.0400359195</v>
       </c>
       <c r="U137">
-        <v>636320.3946</v>
+        <v>534423.9733263992</v>
       </c>
       <c r="V137">
-        <v>665864.2188</v>
+        <v>559236.8318332302</v>
       </c>
       <c r="W137">
-        <v>696779.7381</v>
+        <v>585201.7306514441</v>
       </c>
       <c r="X137">
-        <v>729130.6391</v>
+        <v>612372.1580019256</v>
       </c>
       <c r="Y137">
-        <v>762983.5654</v>
+        <v>640804.0855898265</v>
       </c>
       <c r="Z137">
-        <v>798408.2548</v>
+        <v>670556.0838342052</v>
       </c>
       <c r="AA137">
-        <v>835477.6829</v>
+        <v>701689.4424728084</v>
       </c>
       <c r="AB137">
-        <v>874268.2136</v>
+        <v>734268.2969619298</v>
       </c>
       <c r="AC137">
-        <v>914859.7561999999</v>
+        <v>768359.7604193855</v>
       </c>
       <c r="AD137">
-        <v>957335.9301999999</v>
+        <v>804034.0620344598</v>
       </c>
       <c r="AE137">
-        <v>1001784.238</v>
+        <v>841364.6921127918</v>
       </c>
       <c r="AF137">
-        <v>1048296.243</v>
+        <v>880428.5516565408</v>
       </c>
       <c r="AG137">
-        <v>1096967.761</v>
+        <v>921306.1131147718</v>
       </c>
       <c r="AH137">
-        <v>1147899.058</v>
+        <v>964081.586508984</v>
       </c>
       <c r="AI137">
-        <v>1201195.052</v>
+        <v>1008843.088918104</v>
       </c>
       <c r="AJ137">
-        <v>1256965.534</v>
+        <v>1055682.830088909</v>
       </c>
       <c r="AK137">
-        <v>1315325.394</v>
+        <v>1104697.302245782</v>
       </c>
       <c r="AL137">
-        <v>1376394.853</v>
+        <v>1155987.474939665</v>
       </c>
       <c r="AM137">
-        <v>1440299.716</v>
+        <v>1209659.007534197</v>
       </c>
       <c r="AN137">
-        <v>1507171.628</v>
+        <v>1265822.464211455</v>
       </c>
       <c r="AO137">
-        <v>1577148.347</v>
+        <v>1324593.543255422</v>
       </c>
       <c r="AP137">
-        <v>1650374.027</v>
+        <v>1386093.314734109</v>
       </c>
       <c r="AQ137">
-        <v>1726999.514</v>
+        <v>1450448.469099941</v>
       </c>
       <c r="AR137">
-        <v>1807182.658</v>
+        <v>1517791.579228008</v>
       </c>
       <c r="AS137">
-        <v>1891088.639</v>
+        <v>1588261.374212431</v>
       </c>
     </row>
     <row r="138" spans="1:45">
@@ -17863,112 +17863,112 @@
         <v>1</v>
       </c>
       <c r="J138">
-        <v>448252.5694</v>
+        <v>739788.146291133</v>
       </c>
       <c r="K138">
-        <v>334143.8102</v>
+        <v>551465.0596947904</v>
       </c>
       <c r="L138">
-        <v>492534.6393</v>
+        <v>812870.4945955828</v>
       </c>
       <c r="M138">
-        <v>528982.8348</v>
+        <v>873023.9545538691</v>
       </c>
       <c r="N138">
-        <v>344565.3709</v>
+        <v>568664.6199383229</v>
       </c>
       <c r="O138">
-        <v>342390.0566</v>
+        <v>565074.5195274058</v>
       </c>
       <c r="P138">
-        <v>342390.1</v>
+        <v>565074.5911540014</v>
       </c>
       <c r="Q138">
-        <v>405285.6097</v>
+        <v>668876.2327001502</v>
       </c>
       <c r="R138">
-        <v>479734.7396</v>
+        <v>791745.7655517532</v>
       </c>
       <c r="S138">
-        <v>567859.8372</v>
+        <v>937185.8746458144</v>
       </c>
       <c r="T138">
-        <v>672173.1158</v>
+        <v>1109342.672569669</v>
       </c>
       <c r="U138">
-        <v>795648.2709999999</v>
+        <v>1313123.894171336</v>
       </c>
       <c r="V138">
-        <v>941805.2527</v>
+        <v>1554338.802775382</v>
       </c>
       <c r="W138">
-        <v>1114810.61</v>
+        <v>1839863.797638696</v>
       </c>
       <c r="X138">
-        <v>1319596.266</v>
+        <v>2177838.437788642</v>
       </c>
       <c r="Y138">
-        <v>1562000.12</v>
+        <v>2577897.489417776</v>
       </c>
       <c r="Z138">
-        <v>1848932.464</v>
+        <v>3051445.576744656</v>
       </c>
       <c r="AA138">
-        <v>2188572.978</v>
+        <v>3611982.29958765</v>
       </c>
       <c r="AB138">
-        <v>2590603.916</v>
+        <v>4275487.079432657</v>
       </c>
       <c r="AC138">
-        <v>3066486.116</v>
+        <v>5060874.681476251</v>
       </c>
       <c r="AD138">
-        <v>3629785.719</v>
+        <v>5990534.425909389</v>
       </c>
       <c r="AE138">
-        <v>4296560.906</v>
+        <v>7090968.451851313</v>
       </c>
       <c r="AF138">
-        <v>5085819.673</v>
+        <v>8393547.221147612</v>
       </c>
       <c r="AG138">
-        <v>6020061.699</v>
+        <v>9935403.80777449</v>
       </c>
       <c r="AH138">
-        <v>7125919.751</v>
+        <v>11760492.4613549</v>
       </c>
       <c r="AI138">
-        <v>8434918.915999999</v>
+        <v>13920841.63028035</v>
       </c>
       <c r="AJ138">
-        <v>9984375.296</v>
+        <v>16478037.15211191</v>
       </c>
       <c r="AK138">
-        <v>11818459.79</v>
+        <v>19504977.90065851</v>
       </c>
       <c r="AL138">
-        <v>13989457.3</v>
+        <v>23087953.95738329</v>
       </c>
       <c r="AM138">
-        <v>16559257.2</v>
+        <v>27329106.45519235</v>
       </c>
       <c r="AN138">
-        <v>19601117.71</v>
+        <v>32349339.47021164</v>
       </c>
       <c r="AO138">
-        <v>23201754.2</v>
+        <v>38291766.52193108</v>
       </c>
       <c r="AP138">
-        <v>27463811.3</v>
+        <v>45325790.50001197</v>
       </c>
       <c r="AQ138">
-        <v>32508788.98</v>
+        <v>53651932.81518715</v>
       </c>
       <c r="AR138">
-        <v>38480506.19</v>
+        <v>63507549.72971845</v>
       </c>
       <c r="AS138">
-        <v>45549200.79</v>
+        <v>75173598.8096641</v>
       </c>
     </row>
     <row r="139" spans="1:45">
@@ -17985,112 +17985,112 @@
         <v>1</v>
       </c>
       <c r="J139">
-        <v>188071.4111</v>
+        <v>316601.135860063</v>
       </c>
       <c r="K139">
-        <v>228983.7753</v>
+        <v>385473.3844420304</v>
       </c>
       <c r="L139">
-        <v>214598.4164</v>
+        <v>361256.9395243441</v>
       </c>
       <c r="M139">
-        <v>242605.4607</v>
+        <v>408404.2543958658</v>
       </c>
       <c r="N139">
-        <v>191638.3032</v>
+        <v>322605.6746878693</v>
       </c>
       <c r="O139">
-        <v>146097.7466</v>
+        <v>245942.2846333696</v>
       </c>
       <c r="P139">
-        <v>146097.7</v>
+        <v>245942.2061865028</v>
       </c>
       <c r="Q139">
-        <v>150324.3269</v>
+        <v>253057.348618678</v>
       </c>
       <c r="R139">
-        <v>154673.2307</v>
+        <v>260378.3331041618</v>
       </c>
       <c r="S139">
-        <v>159147.949</v>
+        <v>267911.1148711925</v>
       </c>
       <c r="T139">
-        <v>163752.1214</v>
+        <v>275661.8208557426</v>
       </c>
       <c r="U139">
-        <v>168489.4932</v>
+        <v>283636.7559301327</v>
       </c>
       <c r="V139">
-        <v>173363.9178</v>
+        <v>291842.4069432134</v>
       </c>
       <c r="W139">
-        <v>178379.3602</v>
+        <v>300285.4486122974</v>
       </c>
       <c r="X139">
-        <v>183539.9001</v>
+        <v>308972.7487417277</v>
       </c>
       <c r="Y139">
-        <v>188849.7351</v>
+        <v>317911.3736097873</v>
       </c>
       <c r="Z139">
-        <v>194313.1844</v>
+        <v>327108.5941973127</v>
       </c>
       <c r="AA139">
-        <v>199934.692</v>
+        <v>336571.8915746033</v>
       </c>
       <c r="AB139">
-        <v>205718.8306</v>
+        <v>346308.9634667173</v>
       </c>
       <c r="AC139">
-        <v>211670.3052</v>
+        <v>356327.7303137446</v>
       </c>
       <c r="AD139">
-        <v>217793.9568</v>
+        <v>366636.3414994204</v>
       </c>
       <c r="AE139">
-        <v>224094.7664</v>
+        <v>377243.1820847622</v>
       </c>
       <c r="AF139">
-        <v>230577.8594</v>
+        <v>388156.8802150701</v>
       </c>
       <c r="AG139">
-        <v>237248.5092</v>
+        <v>399386.3131801992</v>
       </c>
       <c r="AH139">
-        <v>244112.1417</v>
+        <v>410940.6149899018</v>
       </c>
       <c r="AI139">
-        <v>251174.3402</v>
+        <v>422829.1846225312</v>
       </c>
       <c r="AJ139">
-        <v>258440.849</v>
+        <v>435061.6920853157</v>
       </c>
       <c r="AK139">
-        <v>265917.579</v>
+        <v>447648.0878414488</v>
       </c>
       <c r="AL139">
-        <v>273610.6117</v>
+        <v>460598.6095437269</v>
       </c>
       <c r="AM139">
-        <v>281526.205</v>
+        <v>473923.7917983215</v>
       </c>
       <c r="AN139">
-        <v>289670.7976</v>
+        <v>487634.4735717804</v>
       </c>
       <c r="AO139">
-        <v>298051.0143</v>
+        <v>501741.8071130954</v>
       </c>
       <c r="AP139">
-        <v>306673.6719</v>
+        <v>516257.2678858168</v>
       </c>
       <c r="AQ139">
-        <v>315545.7841</v>
+        <v>531192.662816758</v>
       </c>
       <c r="AR139">
-        <v>324674.5678</v>
+        <v>546560.1409014739</v>
       </c>
       <c r="AS139">
-        <v>334067.4485</v>
+        <v>562372.2022946691</v>
       </c>
     </row>
     <row r="140" spans="1:45">
@@ -18107,112 +18107,112 @@
         <v>1</v>
       </c>
       <c r="J140">
-        <v>82221.10382</v>
+        <v>143637.2880039326</v>
       </c>
       <c r="K140">
-        <v>93925.43016</v>
+        <v>164084.3218587816</v>
       </c>
       <c r="L140">
-        <v>84163.35982</v>
+        <v>147030.3388325874</v>
       </c>
       <c r="M140">
-        <v>99505.70206</v>
+        <v>173832.8545930937</v>
       </c>
       <c r="N140">
-        <v>87730.22728000001</v>
+        <v>153261.5269925699</v>
       </c>
       <c r="O140">
-        <v>87324.71145</v>
+        <v>152553.1055367916</v>
       </c>
       <c r="P140">
-        <v>87324.71000000001</v>
+        <v>152553.1030036942</v>
       </c>
       <c r="Q140">
-        <v>93226.63770000001</v>
+        <v>162863.5567611524</v>
       </c>
       <c r="R140">
-        <v>99527.45308000001</v>
+        <v>173870.8528365977</v>
       </c>
       <c r="S140">
-        <v>106254.1154</v>
+        <v>185622.0880800246</v>
       </c>
       <c r="T140">
-        <v>113435.4058</v>
+        <v>198167.5420997475</v>
       </c>
       <c r="U140">
-        <v>121102.051</v>
+        <v>211560.8933618173</v>
       </c>
       <c r="V140">
-        <v>129286.854</v>
+        <v>225859.4475181832</v>
       </c>
       <c r="W140">
-        <v>138024.8351</v>
+        <v>241124.3837635212</v>
       </c>
       <c r="X140">
-        <v>147353.3813</v>
+        <v>257421.0158316188</v>
       </c>
       <c r="Y140">
-        <v>157312.4067</v>
+        <v>274819.0722083603</v>
       </c>
       <c r="Z140">
-        <v>167944.5228</v>
+        <v>293392.9936396543</v>
       </c>
       <c r="AA140">
-        <v>179295.221</v>
+        <v>313222.251952318</v>
       </c>
       <c r="AB140">
-        <v>191413.0675</v>
+        <v>334391.6905373125</v>
       </c>
       <c r="AC140">
-        <v>204349.9107</v>
+        <v>356991.886670025</v>
       </c>
       <c r="AD140">
-        <v>218161.1035</v>
+        <v>381119.5398603107</v>
       </c>
       <c r="AE140">
-        <v>232905.7394</v>
+        <v>406877.8843106349</v>
       </c>
       <c r="AF140">
-        <v>248646.9063</v>
+        <v>434377.1322954727</v>
       </c>
       <c r="AG140">
-        <v>265451.9557</v>
+        <v>463734.9444439512</v>
       </c>
       <c r="AH140">
-        <v>283392.7912</v>
+        <v>495076.9337388923</v>
       </c>
       <c r="AI140">
-        <v>302546.1759</v>
+        <v>528537.2025334692</v>
       </c>
       <c r="AJ140">
-        <v>322994.0612</v>
+        <v>564258.9169528886</v>
       </c>
       <c r="AK140">
-        <v>344823.9373</v>
+        <v>602394.9192051856</v>
       </c>
       <c r="AL140">
-        <v>368129.2073</v>
+        <v>643108.381120363</v>
       </c>
       <c r="AM140">
-        <v>393009.5873</v>
+        <v>686573.5031105883</v>
       </c>
       <c r="AN140">
-        <v>419571.5326</v>
+        <v>732976.2587261453</v>
       </c>
       <c r="AO140">
-        <v>447928.6935</v>
+        <v>782515.1909215116</v>
       </c>
       <c r="AP140">
-        <v>478202.4014</v>
+        <v>835402.2612544385</v>
       </c>
       <c r="AQ140">
-        <v>510522.1881</v>
+        <v>891863.7570842275</v>
       </c>
       <c r="AR140">
-        <v>545026.3398</v>
+        <v>952141.259389648</v>
       </c>
       <c r="AS140">
-        <v>581862.4891</v>
+        <v>1016492.67697148</v>
       </c>
     </row>
     <row r="141" spans="1:45">
@@ -18961,112 +18961,112 @@
         <v>1</v>
       </c>
       <c r="J147">
-        <v>6740.876602</v>
+        <v>2998.461197674138</v>
       </c>
       <c r="K147">
-        <v>6199.723652</v>
+        <v>2757.746789387764</v>
       </c>
       <c r="L147">
-        <v>5118.865148</v>
+        <v>2276.961800168625</v>
       </c>
       <c r="M147">
-        <v>4888.411757</v>
+        <v>2174.452053798115</v>
       </c>
       <c r="N147">
-        <v>3788.307612</v>
+        <v>1685.106262895446</v>
       </c>
       <c r="O147">
-        <v>4678.671665</v>
+        <v>2081.155949360895</v>
       </c>
       <c r="P147">
-        <v>4678.672</v>
+        <v>2081.156098374823</v>
       </c>
       <c r="Q147">
-        <v>5147.073885</v>
+        <v>2289.509545561976</v>
       </c>
       <c r="R147">
-        <v>5662.369487</v>
+        <v>2518.722147891874</v>
       </c>
       <c r="S147">
-        <v>6229.253539</v>
+        <v>2770.882205679903</v>
       </c>
       <c r="T147">
-        <v>6852.89078</v>
+        <v>3048.287086227373</v>
       </c>
       <c r="U147">
-        <v>7538.963016</v>
+        <v>3353.464157387107</v>
       </c>
       <c r="V147">
-        <v>8293.720880000001</v>
+        <v>3689.193811327361</v>
       </c>
       <c r="W147">
-        <v>9124.040784999999</v>
+        <v>4058.534798234063</v>
       </c>
       <c r="X147">
-        <v>10037.48757</v>
+        <v>4464.852092360179</v>
       </c>
       <c r="Y147">
-        <v>11042.38342</v>
+        <v>4911.847548861308</v>
       </c>
       <c r="Z147">
-        <v>12147.88371</v>
+        <v>5403.593640549</v>
       </c>
       <c r="AA147">
-        <v>13364.06035</v>
+        <v>5944.570531221611</v>
       </c>
       <c r="AB147">
-        <v>14701.99365</v>
+        <v>6539.706938841925</v>
       </c>
       <c r="AC147">
-        <v>16173.87318</v>
+        <v>7194.424999849956</v>
       </c>
       <c r="AD147">
-        <v>17793.10887</v>
+        <v>7914.689688408946</v>
       </c>
       <c r="AE147">
-        <v>19574.45317</v>
+        <v>8707.063155335081</v>
       </c>
       <c r="AF147">
-        <v>21534.13548</v>
+        <v>9578.764524940336</v>
       </c>
       <c r="AG147">
-        <v>23690.00998</v>
+        <v>10537.73565243245</v>
       </c>
       <c r="AH147">
-        <v>26061.7183</v>
+        <v>11592.71348240948</v>
       </c>
       <c r="AI147">
-        <v>28670.8685</v>
+        <v>12753.30966233102</v>
       </c>
       <c r="AJ147">
-        <v>31541.2319</v>
+        <v>14030.09809598525</v>
       </c>
       <c r="AK147">
-        <v>34698.95966</v>
+        <v>15434.71128210547</v>
       </c>
       <c r="AL147">
-        <v>38172.82107</v>
+        <v>16979.94630997887</v>
       </c>
       <c r="AM147">
-        <v>41994.46561</v>
+        <v>18679.88142837183</v>
       </c>
       <c r="AN147">
-        <v>46198.71136</v>
+        <v>20550.00433540163</v>
       </c>
       <c r="AO147">
-        <v>50823.86214</v>
+        <v>22607.35324802044</v>
       </c>
       <c r="AP147">
-        <v>55912.05657</v>
+        <v>24870.67217008023</v>
       </c>
       <c r="AQ147">
-        <v>61509.65193</v>
+        <v>27360.58164005346</v>
       </c>
       <c r="AR147">
-        <v>67667.64653</v>
+        <v>30099.76660868329</v>
       </c>
       <c r="AS147">
-        <v>74442.14432000001</v>
+        <v>33113.18310573315</v>
       </c>
     </row>
     <row r="148" spans="1:45">
@@ -19083,112 +19083,112 @@
         <v>1</v>
       </c>
       <c r="J148">
-        <v>17640.2972</v>
+        <v>24568.6851562611</v>
       </c>
       <c r="K148">
-        <v>26026.08555</v>
+        <v>36248.06852618483</v>
       </c>
       <c r="L148">
-        <v>23327.48714</v>
+        <v>32489.5709256752</v>
       </c>
       <c r="M148">
-        <v>23820.92913</v>
+        <v>33176.81676726958</v>
       </c>
       <c r="N148">
-        <v>21821.11512</v>
+        <v>30391.55752669567</v>
       </c>
       <c r="O148">
-        <v>20988.94898</v>
+        <v>29232.55052927609</v>
       </c>
       <c r="P148">
-        <v>20988.95</v>
+        <v>29232.55194989041</v>
       </c>
       <c r="Q148">
-        <v>21836.5874</v>
+        <v>30413.10668608112</v>
       </c>
       <c r="R148">
-        <v>22718.45657</v>
+        <v>31641.33803281508</v>
       </c>
       <c r="S148">
-        <v>23635.93998</v>
+        <v>32919.17143782046</v>
       </c>
       <c r="T148">
-        <v>24590.4759</v>
+        <v>34248.61006478543</v>
       </c>
       <c r="U148">
-        <v>25583.56069</v>
+        <v>35631.73798277661</v>
       </c>
       <c r="V148">
-        <v>26616.75114</v>
+        <v>37070.72342529544</v>
       </c>
       <c r="W148">
-        <v>27691.66692</v>
+        <v>38567.82220253809</v>
       </c>
       <c r="X148">
-        <v>28809.99311</v>
+        <v>40125.38122507604</v>
       </c>
       <c r="Y148">
-        <v>29973.48283</v>
+        <v>41745.84216681269</v>
       </c>
       <c r="Z148">
-        <v>31183.96001</v>
+        <v>43431.74532292612</v>
       </c>
       <c r="AA148">
-        <v>32443.32223</v>
+        <v>45185.73356530505</v>
       </c>
       <c r="AB148">
-        <v>33753.54371</v>
+        <v>47010.55650689871</v>
       </c>
       <c r="AC148">
-        <v>35116.6784</v>
+        <v>48909.07480534254</v>
       </c>
       <c r="AD148">
-        <v>36534.8632</v>
+        <v>50884.26464764266</v>
       </c>
       <c r="AE148">
-        <v>38010.3213</v>
+        <v>52939.22240199134</v>
       </c>
       <c r="AF148">
-        <v>39545.36568</v>
+        <v>55077.16949242403</v>
       </c>
       <c r="AG148">
-        <v>41142.40273</v>
+        <v>57301.45744060747</v>
       </c>
       <c r="AH148">
-        <v>42803.93602</v>
+        <v>59615.57311654158</v>
       </c>
       <c r="AI148">
-        <v>44532.57023</v>
+        <v>62023.14421210294</v>
       </c>
       <c r="AJ148">
-        <v>46331.01521</v>
+        <v>64527.94489564688</v>
       </c>
       <c r="AK148">
-        <v>48202.09028</v>
+        <v>67133.90180087177</v>
       </c>
       <c r="AL148">
-        <v>50148.7286</v>
+        <v>69845.10011317646</v>
       </c>
       <c r="AM148">
-        <v>52173.98178</v>
+        <v>72665.78999027993</v>
       </c>
       <c r="AN148">
-        <v>54281.02468</v>
+        <v>75600.39324746514</v>
       </c>
       <c r="AO148">
-        <v>56473.16037</v>
+        <v>78653.51026566442</v>
       </c>
       <c r="AP148">
-        <v>58753.82532</v>
+        <v>81829.92721987935</v>
       </c>
       <c r="AQ148">
-        <v>61126.59478</v>
+        <v>85134.62357222491</v>
       </c>
       <c r="AR148">
-        <v>63595.18838</v>
+        <v>88572.77987138074</v>
       </c>
       <c r="AS148">
-        <v>66163.47597</v>
+        <v>92149.7858863045</v>
       </c>
     </row>
     <row r="149" spans="1:45">
@@ -19205,112 +19205,112 @@
         <v>1</v>
       </c>
       <c r="J149">
-        <v>1424850.75</v>
+        <v>2707216.425</v>
       </c>
       <c r="K149">
-        <v>1424850.75</v>
+        <v>2707216.425</v>
       </c>
       <c r="L149">
-        <v>1424850.75</v>
+        <v>2707216.425</v>
       </c>
       <c r="M149">
-        <v>1424850.75</v>
+        <v>2707216.425</v>
       </c>
       <c r="N149">
-        <v>1424850.75</v>
+        <v>2707216.425</v>
       </c>
       <c r="O149">
-        <v>1424850.75</v>
+        <v>2707216.425</v>
       </c>
       <c r="P149">
-        <v>1424850.75</v>
+        <v>2707216.425</v>
       </c>
       <c r="Q149">
-        <v>1424850.75</v>
+        <v>2707216.425</v>
       </c>
       <c r="R149">
-        <v>1424850.75</v>
+        <v>2707216.425</v>
       </c>
       <c r="S149">
-        <v>1424850.75</v>
+        <v>2707216.425</v>
       </c>
       <c r="T149">
-        <v>1424850.75</v>
+        <v>2707216.425</v>
       </c>
       <c r="U149">
-        <v>1424850.75</v>
+        <v>2707216.425</v>
       </c>
       <c r="V149">
-        <v>1424850.75</v>
+        <v>2707216.425</v>
       </c>
       <c r="W149">
-        <v>1424850.75</v>
+        <v>2707216.425</v>
       </c>
       <c r="X149">
-        <v>1424850.75</v>
+        <v>2707216.425</v>
       </c>
       <c r="Y149">
-        <v>1424850.75</v>
+        <v>2707216.425</v>
       </c>
       <c r="Z149">
-        <v>1424850.75</v>
+        <v>2707216.425</v>
       </c>
       <c r="AA149">
-        <v>1424850.75</v>
+        <v>2707216.425</v>
       </c>
       <c r="AB149">
-        <v>1424850.75</v>
+        <v>2707216.425</v>
       </c>
       <c r="AC149">
-        <v>1424850.75</v>
+        <v>2707216.425</v>
       </c>
       <c r="AD149">
-        <v>1424850.75</v>
+        <v>2707216.425</v>
       </c>
       <c r="AE149">
-        <v>1424850.75</v>
+        <v>2707216.425</v>
       </c>
       <c r="AF149">
-        <v>1424850.75</v>
+        <v>2707216.425</v>
       </c>
       <c r="AG149">
-        <v>1424850.75</v>
+        <v>2707216.425</v>
       </c>
       <c r="AH149">
-        <v>1424850.75</v>
+        <v>2707216.425</v>
       </c>
       <c r="AI149">
-        <v>1424850.75</v>
+        <v>2707216.425</v>
       </c>
       <c r="AJ149">
-        <v>1424850.75</v>
+        <v>2707216.425</v>
       </c>
       <c r="AK149">
-        <v>1424850.75</v>
+        <v>2707216.425</v>
       </c>
       <c r="AL149">
-        <v>1424850.75</v>
+        <v>2707216.425</v>
       </c>
       <c r="AM149">
-        <v>1424850.75</v>
+        <v>2707216.425</v>
       </c>
       <c r="AN149">
-        <v>1424850.75</v>
+        <v>2707216.425</v>
       </c>
       <c r="AO149">
-        <v>1424850.75</v>
+        <v>2707216.425</v>
       </c>
       <c r="AP149">
-        <v>1424850.75</v>
+        <v>2707216.425</v>
       </c>
       <c r="AQ149">
-        <v>1424850.75</v>
+        <v>2707216.425</v>
       </c>
       <c r="AR149">
-        <v>1424850.75</v>
+        <v>2707216.425</v>
       </c>
       <c r="AS149">
-        <v>1424850.75</v>
+        <v>2707216.425</v>
       </c>
     </row>
     <row r="150" spans="1:45">
@@ -29385,112 +29385,112 @@
         <v>1</v>
       </c>
       <c r="J22">
-        <v>2E-06</v>
+        <v>2.190818243968932E-06</v>
       </c>
       <c r="K22">
-        <v>2E-06</v>
+        <v>2.190818243968932E-06</v>
       </c>
       <c r="L22">
-        <v>2E-06</v>
+        <v>2.190818243968932E-06</v>
       </c>
       <c r="M22">
-        <v>2E-06</v>
+        <v>2.190818243968932E-06</v>
       </c>
       <c r="N22">
-        <v>2E-06</v>
+        <v>2.190818243968932E-06</v>
       </c>
       <c r="O22">
-        <v>2E-06</v>
+        <v>2.190818243968932E-06</v>
       </c>
       <c r="P22">
-        <v>2E-06</v>
+        <v>2.190818243968932E-06</v>
       </c>
       <c r="Q22">
-        <v>2E-06</v>
+        <v>2.190818243968932E-06</v>
       </c>
       <c r="R22">
-        <v>2E-06</v>
+        <v>2.190818243968932E-06</v>
       </c>
       <c r="S22">
-        <v>2E-06</v>
+        <v>2.190818243968932E-06</v>
       </c>
       <c r="T22">
-        <v>2E-06</v>
+        <v>2.190818243968932E-06</v>
       </c>
       <c r="U22">
-        <v>2E-06</v>
+        <v>2.190818243968932E-06</v>
       </c>
       <c r="V22">
-        <v>2E-06</v>
+        <v>2.190818243968932E-06</v>
       </c>
       <c r="W22">
-        <v>1.921739130434783E-06</v>
+        <v>2.105090573552757E-06</v>
       </c>
       <c r="X22">
-        <v>1.843478260869565E-06</v>
+        <v>2.019362903136581E-06</v>
       </c>
       <c r="Y22">
-        <v>1.765217391304348E-06</v>
+        <v>1.933635232720406E-06</v>
       </c>
       <c r="Z22">
-        <v>1.68695652173913E-06</v>
+        <v>1.84790756230423E-06</v>
       </c>
       <c r="AA22">
-        <v>1.608695652173913E-06</v>
+        <v>1.762179891888054E-06</v>
       </c>
       <c r="AB22">
-        <v>1.530434782608695E-06</v>
+        <v>1.676452221471879E-06</v>
       </c>
       <c r="AC22">
-        <v>1.452173913043478E-06</v>
+        <v>1.590724551055703E-06</v>
       </c>
       <c r="AD22">
-        <v>1.373913043478261E-06</v>
+        <v>1.504996880639528E-06</v>
       </c>
       <c r="AE22">
-        <v>1.295652173913043E-06</v>
+        <v>1.419269210223352E-06</v>
       </c>
       <c r="AF22">
-        <v>1.217391304347826E-06</v>
+        <v>1.333541539807176E-06</v>
       </c>
       <c r="AG22">
-        <v>1.139130434782609E-06</v>
+        <v>1.247813869391001E-06</v>
       </c>
       <c r="AH22">
-        <v>1.060869565217391E-06</v>
+        <v>1.162086198974825E-06</v>
       </c>
       <c r="AI22">
-        <v>9.826086956521739E-07</v>
+        <v>1.076358528558649E-06</v>
       </c>
       <c r="AJ22">
-        <v>9.043478260869564E-07</v>
+        <v>9.906308581424737E-07</v>
       </c>
       <c r="AK22">
-        <v>8.260869565217391E-07</v>
+        <v>9.049031877262982E-07</v>
       </c>
       <c r="AL22">
-        <v>7.478260869565217E-07</v>
+        <v>8.191755173101225E-07</v>
       </c>
       <c r="AM22">
-        <v>6.695652173913045E-07</v>
+        <v>7.334478468939471E-07</v>
       </c>
       <c r="AN22">
-        <v>5.913043478260868E-07</v>
+        <v>6.477201764777712E-07</v>
       </c>
       <c r="AO22">
-        <v>5.130434782608695E-07</v>
+        <v>5.619925060615957E-07</v>
       </c>
       <c r="AP22">
-        <v>4.347826086956522E-07</v>
+        <v>4.762648356454202E-07</v>
       </c>
       <c r="AQ22">
-        <v>3.565217391304348E-07</v>
+        <v>3.905371652292446E-07</v>
       </c>
       <c r="AR22">
-        <v>2.782608695652173E-07</v>
+        <v>3.048094948130688E-07</v>
       </c>
       <c r="AS22">
-        <v>2E-07</v>
+        <v>2.190818243968932E-07</v>
       </c>
     </row>
     <row r="23" spans="1:45">
@@ -29510,112 +29510,112 @@
         <v>1</v>
       </c>
       <c r="J23">
-        <v>6E-07</v>
+        <v>6.572454731906799E-07</v>
       </c>
       <c r="K23">
-        <v>6E-07</v>
+        <v>6.572454731906799E-07</v>
       </c>
       <c r="L23">
-        <v>6E-07</v>
+        <v>6.572454731906799E-07</v>
       </c>
       <c r="M23">
-        <v>6E-07</v>
+        <v>6.572454731906799E-07</v>
       </c>
       <c r="N23">
-        <v>6E-07</v>
+        <v>6.572454731906799E-07</v>
       </c>
       <c r="O23">
-        <v>6E-07</v>
+        <v>6.572454731906799E-07</v>
       </c>
       <c r="P23">
-        <v>6E-07</v>
+        <v>6.572454731906799E-07</v>
       </c>
       <c r="Q23">
-        <v>6E-07</v>
+        <v>6.572454731906799E-07</v>
       </c>
       <c r="R23">
-        <v>6E-07</v>
+        <v>6.572454731906799E-07</v>
       </c>
       <c r="S23">
-        <v>6E-07</v>
+        <v>6.572454731906799E-07</v>
       </c>
       <c r="T23">
-        <v>6E-07</v>
+        <v>6.572454731906799E-07</v>
       </c>
       <c r="U23">
-        <v>6E-07</v>
+        <v>6.572454731906799E-07</v>
       </c>
       <c r="V23">
-        <v>6E-07</v>
+        <v>6.572454731906799E-07</v>
       </c>
       <c r="W23">
-        <v>5.765217391304348E-07</v>
+        <v>6.315271720658272E-07</v>
       </c>
       <c r="X23">
-        <v>5.530434782608695E-07</v>
+        <v>6.058088709409745E-07</v>
       </c>
       <c r="Y23">
-        <v>5.295652173913042E-07</v>
+        <v>5.800905698161218E-07</v>
       </c>
       <c r="Z23">
-        <v>5.060869565217392E-07</v>
+        <v>5.543722686912691E-07</v>
       </c>
       <c r="AA23">
-        <v>4.826086956521739E-07</v>
+        <v>5.286539675664164E-07</v>
       </c>
       <c r="AB23">
-        <v>4.591304347826087E-07</v>
+        <v>5.029356664415637E-07</v>
       </c>
       <c r="AC23">
-        <v>4.356521739130435E-07</v>
+        <v>4.77217365316711E-07</v>
       </c>
       <c r="AD23">
-        <v>4.121739130434782E-07</v>
+        <v>4.514990641918583E-07</v>
       </c>
       <c r="AE23">
-        <v>3.886956521739131E-07</v>
+        <v>4.257807630670057E-07</v>
       </c>
       <c r="AF23">
-        <v>3.652173913043478E-07</v>
+        <v>4.00062461942153E-07</v>
       </c>
       <c r="AG23">
-        <v>3.417391304347826E-07</v>
+        <v>3.743441608173002E-07</v>
       </c>
       <c r="AH23">
-        <v>3.182608695652174E-07</v>
+        <v>3.486258596924476E-07</v>
       </c>
       <c r="AI23">
-        <v>2.947826086956522E-07</v>
+        <v>3.229075585675949E-07</v>
       </c>
       <c r="AJ23">
-        <v>2.713043478260869E-07</v>
+        <v>2.971892574427422E-07</v>
       </c>
       <c r="AK23">
-        <v>2.478260869565217E-07</v>
+        <v>2.714709563178895E-07</v>
       </c>
       <c r="AL23">
-        <v>2.243478260869565E-07</v>
+        <v>2.457526551930368E-07</v>
       </c>
       <c r="AM23">
-        <v>2.008695652173913E-07</v>
+        <v>2.200343540681842E-07</v>
       </c>
       <c r="AN23">
-        <v>1.773913043478261E-07</v>
+        <v>1.943160529433314E-07</v>
       </c>
       <c r="AO23">
-        <v>1.539130434782609E-07</v>
+        <v>1.685977518184787E-07</v>
       </c>
       <c r="AP23">
-        <v>1.304347826086957E-07</v>
+        <v>1.428794506936261E-07</v>
       </c>
       <c r="AQ23">
-        <v>1.069565217391305E-07</v>
+        <v>1.171611495687734E-07</v>
       </c>
       <c r="AR23">
-        <v>8.347826086956519E-08</v>
+        <v>9.144284844392066E-08</v>
       </c>
       <c r="AS23">
-        <v>5.999999999999999E-08</v>
+        <v>6.572454731906799E-08</v>
       </c>
     </row>
     <row r="24" spans="1:45">
@@ -29635,112 +29635,112 @@
         <v>1</v>
       </c>
       <c r="J24">
-        <v>1</v>
+        <v>0.733243641135974</v>
       </c>
       <c r="K24">
-        <v>1</v>
+        <v>0.733243641135974</v>
       </c>
       <c r="L24">
-        <v>1</v>
+        <v>0.733243641135974</v>
       </c>
       <c r="M24">
-        <v>1</v>
+        <v>0.733243641135974</v>
       </c>
       <c r="N24">
-        <v>1</v>
+        <v>0.733243641135974</v>
       </c>
       <c r="O24">
-        <v>1</v>
+        <v>0.733243641135974</v>
       </c>
       <c r="P24">
-        <v>1</v>
+        <v>0.733243641135974</v>
       </c>
       <c r="Q24">
-        <v>1</v>
+        <v>0.733243641135974</v>
       </c>
       <c r="R24">
-        <v>1</v>
+        <v>0.733243641135974</v>
       </c>
       <c r="S24">
-        <v>1</v>
+        <v>0.733243641135974</v>
       </c>
       <c r="T24">
-        <v>1</v>
+        <v>0.733243641135974</v>
       </c>
       <c r="U24">
-        <v>1</v>
+        <v>0.733243641135974</v>
       </c>
       <c r="V24">
-        <v>1</v>
+        <v>0.733243641135974</v>
       </c>
       <c r="W24">
-        <v>0.9608695652173913</v>
+        <v>0.7045514986567403</v>
       </c>
       <c r="X24">
-        <v>0.9217391304347826</v>
+        <v>0.6758593561775065</v>
       </c>
       <c r="Y24">
-        <v>0.8826086956521739</v>
+        <v>0.6471672136982727</v>
       </c>
       <c r="Z24">
-        <v>0.8434782608695652</v>
+        <v>0.618475071219039</v>
       </c>
       <c r="AA24">
-        <v>0.8043478260869565</v>
+        <v>0.5897829287398051</v>
       </c>
       <c r="AB24">
-        <v>0.7652173913043477</v>
+        <v>0.5610907862605714</v>
       </c>
       <c r="AC24">
-        <v>0.7260869565217392</v>
+        <v>0.5323986437813375</v>
       </c>
       <c r="AD24">
-        <v>0.6869565217391305</v>
+        <v>0.5037065013021039</v>
       </c>
       <c r="AE24">
-        <v>0.6478260869565218</v>
+        <v>0.4750143588228701</v>
       </c>
       <c r="AF24">
-        <v>0.6086956521739131</v>
+        <v>0.4463222163436364</v>
       </c>
       <c r="AG24">
-        <v>0.5695652173913044</v>
+        <v>0.4176300738644025</v>
       </c>
       <c r="AH24">
-        <v>0.5304347826086957</v>
+        <v>0.3889379313851688</v>
       </c>
       <c r="AI24">
-        <v>0.491304347826087</v>
+        <v>0.3602457889059351</v>
       </c>
       <c r="AJ24">
-        <v>0.4521739130434782</v>
+        <v>0.3315536464267013</v>
       </c>
       <c r="AK24">
-        <v>0.4130434782608696</v>
+        <v>0.3028615039474675</v>
       </c>
       <c r="AL24">
-        <v>0.3739130434782609</v>
+        <v>0.2741693614682337</v>
       </c>
       <c r="AM24">
-        <v>0.3347826086956522</v>
+        <v>0.245477218989</v>
       </c>
       <c r="AN24">
-        <v>0.2956521739130434</v>
+        <v>0.2167850765097662</v>
       </c>
       <c r="AO24">
-        <v>0.2565217391304348</v>
+        <v>0.1880929340305324</v>
       </c>
       <c r="AP24">
-        <v>0.2173913043478261</v>
+        <v>0.1594007915512987</v>
       </c>
       <c r="AQ24">
-        <v>0.1782608695652174</v>
+        <v>0.130708649072065</v>
       </c>
       <c r="AR24">
-        <v>0.1391304347826087</v>
+        <v>0.1020165065928312</v>
       </c>
       <c r="AS24">
-        <v>0.1</v>
+        <v>0.0733243641135974</v>
       </c>
     </row>
     <row r="25" spans="1:45">
@@ -29760,112 +29760,112 @@
         <v>1</v>
       </c>
       <c r="J25">
-        <v>0.03741</v>
+        <v>0.0274306446148967</v>
       </c>
       <c r="K25">
-        <v>0.03741</v>
+        <v>0.0274306446148967</v>
       </c>
       <c r="L25">
-        <v>0.03741</v>
+        <v>0.0274306446148967</v>
       </c>
       <c r="M25">
-        <v>0.03741</v>
+        <v>0.0274306446148967</v>
       </c>
       <c r="N25">
-        <v>0.03741</v>
+        <v>0.0274306446148967</v>
       </c>
       <c r="O25">
-        <v>0.03741</v>
+        <v>0.0274306446148967</v>
       </c>
       <c r="P25">
-        <v>0.03741</v>
+        <v>0.0274306446148967</v>
       </c>
       <c r="Q25">
-        <v>0.03741</v>
+        <v>0.0274306446148967</v>
       </c>
       <c r="R25">
-        <v>0.03741</v>
+        <v>0.0274306446148967</v>
       </c>
       <c r="S25">
-        <v>0.03741</v>
+        <v>0.0274306446148967</v>
       </c>
       <c r="T25">
-        <v>0.03741</v>
+        <v>0.0274306446148967</v>
       </c>
       <c r="U25">
-        <v>0.03741</v>
+        <v>0.0274306446148967</v>
       </c>
       <c r="V25">
-        <v>0.03741</v>
+        <v>0.0274306446148967</v>
       </c>
       <c r="W25">
-        <v>0.03594613043478261</v>
+        <v>0.02635727156474857</v>
       </c>
       <c r="X25">
-        <v>0.03448226086956522</v>
+        <v>0.02528389851460044</v>
       </c>
       <c r="Y25">
-        <v>0.03301839130434783</v>
+        <v>0.02421052546445231</v>
       </c>
       <c r="Z25">
-        <v>0.03155452173913043</v>
+        <v>0.02313715241430417</v>
       </c>
       <c r="AA25">
-        <v>0.03009065217391305</v>
+        <v>0.02206377936415604</v>
       </c>
       <c r="AB25">
-        <v>0.02862678260869565</v>
+        <v>0.02099040631400791</v>
       </c>
       <c r="AC25">
-        <v>0.02716291304347826</v>
+        <v>0.01991703326385978</v>
       </c>
       <c r="AD25">
-        <v>0.02569904347826087</v>
+        <v>0.01884366021371165</v>
       </c>
       <c r="AE25">
-        <v>0.02423517391304348</v>
+        <v>0.01777028716356352</v>
       </c>
       <c r="AF25">
-        <v>0.02277130434782609</v>
+        <v>0.01669691411341538</v>
       </c>
       <c r="AG25">
-        <v>0.0213074347826087</v>
+        <v>0.01562354106326725</v>
       </c>
       <c r="AH25">
-        <v>0.0198435652173913</v>
+        <v>0.01455016801311912</v>
       </c>
       <c r="AI25">
-        <v>0.01837969565217391</v>
+        <v>0.01347679496297099</v>
       </c>
       <c r="AJ25">
-        <v>0.01691582608695652</v>
+        <v>0.01240342191282286</v>
       </c>
       <c r="AK25">
-        <v>0.01545195652173913</v>
+        <v>0.01133004886267472</v>
       </c>
       <c r="AL25">
-        <v>0.01398808695652174</v>
+        <v>0.01025667581252659</v>
       </c>
       <c r="AM25">
-        <v>0.01252421739130435</v>
+        <v>0.009183302762378462</v>
       </c>
       <c r="AN25">
-        <v>0.01106034782608696</v>
+        <v>0.008109929712230329</v>
       </c>
       <c r="AO25">
-        <v>0.009596478260869564</v>
+        <v>0.007036556662082197</v>
       </c>
       <c r="AP25">
-        <v>0.008132608695652174</v>
+        <v>0.005963183611934066</v>
       </c>
       <c r="AQ25">
-        <v>0.006668739130434784</v>
+        <v>0.004889810561785935</v>
       </c>
       <c r="AR25">
-        <v>0.00520486956521739</v>
+        <v>0.003816437511637801</v>
       </c>
       <c r="AS25">
-        <v>0.003741</v>
+        <v>0.00274306446148967</v>
       </c>
     </row>
     <row r="26" spans="1:45">
@@ -29885,112 +29885,112 @@
         <v>1</v>
       </c>
       <c r="J26">
-        <v>0.0007</v>
+        <v>0.0005132705487951</v>
       </c>
       <c r="K26">
-        <v>0.0007</v>
+        <v>0.0005132705487951</v>
       </c>
       <c r="L26">
-        <v>0.0007</v>
+        <v>0.0005132705487951</v>
       </c>
       <c r="M26">
-        <v>0.0007</v>
+        <v>0.0005132705487951</v>
       </c>
       <c r="N26">
-        <v>0.0007</v>
+        <v>0.0005132705487951</v>
       </c>
       <c r="O26">
-        <v>0.0007</v>
+        <v>0.0005132705487951</v>
       </c>
       <c r="P26">
-        <v>0.0007</v>
+        <v>0.0005132705487951</v>
       </c>
       <c r="Q26">
-        <v>0.0007</v>
+        <v>0.0005132705487951</v>
       </c>
       <c r="R26">
-        <v>0.0007</v>
+        <v>0.0005132705487951</v>
       </c>
       <c r="S26">
-        <v>0.0007</v>
+        <v>0.0005132705487951</v>
       </c>
       <c r="T26">
-        <v>0.0007</v>
+        <v>0.0005132705487951</v>
       </c>
       <c r="U26">
-        <v>0.0007</v>
+        <v>0.0005132705487951</v>
       </c>
       <c r="V26">
-        <v>0.0007</v>
+        <v>0.0005132705487951</v>
       </c>
       <c r="W26">
-        <v>0.000672608695652174</v>
+        <v>0.0004931860490596395</v>
       </c>
       <c r="X26">
-        <v>0.0006452173913043479</v>
+        <v>0.0004731015493241792</v>
       </c>
       <c r="Y26">
-        <v>0.0006178260869565217</v>
+        <v>0.0004530170495887187</v>
       </c>
       <c r="Z26">
-        <v>0.0005904347826086957</v>
+        <v>0.0004329325498532582</v>
       </c>
       <c r="AA26">
-        <v>0.0005630434782608697</v>
+        <v>0.0004128480501177978</v>
       </c>
       <c r="AB26">
-        <v>0.0005356521739130435</v>
+        <v>0.0003927635503823373</v>
       </c>
       <c r="AC26">
-        <v>0.0005082608695652173</v>
+        <v>0.0003726790506468769</v>
       </c>
       <c r="AD26">
-        <v>0.0004808695652173913</v>
+        <v>0.0003525945509114165</v>
       </c>
       <c r="AE26">
-        <v>0.0004534782608695653</v>
+        <v>0.0003325100511759561</v>
       </c>
       <c r="AF26">
-        <v>0.0004260869565217391</v>
+        <v>0.0003124255514404957</v>
       </c>
       <c r="AG26">
-        <v>0.000398695652173913</v>
+        <v>0.0002923410517050352</v>
       </c>
       <c r="AH26">
-        <v>0.000371304347826087</v>
+        <v>0.0002722565519695748</v>
       </c>
       <c r="AI26">
-        <v>0.0003439130434782609</v>
+        <v>0.0002521720522341144</v>
       </c>
       <c r="AJ26">
-        <v>0.0003165217391304348</v>
+        <v>0.0002320875524986539</v>
       </c>
       <c r="AK26">
-        <v>0.0002891304347826087</v>
+        <v>0.0002120030527631935</v>
       </c>
       <c r="AL26">
-        <v>0.0002617391304347826</v>
+        <v>0.0001919185530277331</v>
       </c>
       <c r="AM26">
-        <v>0.0002343478260869566</v>
+        <v>0.0001718340532922726</v>
       </c>
       <c r="AN26">
-        <v>0.0002069565217391304</v>
+        <v>0.0001517495535568122</v>
       </c>
       <c r="AO26">
-        <v>0.0001795652173913044</v>
+        <v>0.0001316650538213517</v>
       </c>
       <c r="AP26">
-        <v>0.0001521739130434783</v>
+        <v>0.0001115805540858913</v>
       </c>
       <c r="AQ26">
-        <v>0.0001247826086956522</v>
+        <v>9.149605435043089E-05</v>
       </c>
       <c r="AR26">
-        <v>9.739130434782608E-05</v>
+        <v>7.141155461497042E-05</v>
       </c>
       <c r="AS26">
-        <v>7.000000000000001E-05</v>
+        <v>5.132705487951E-05</v>
       </c>
     </row>
     <row r="27" spans="1:45">
